--- a/salon_data.xlsx
+++ b/salon_data.xlsx
@@ -19,11 +19,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;USD &quot;[$-en-US]#,##0"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -122,7 +123,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -144,11 +145,55 @@
         <color rgb="00BBBBBB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -231,6 +276,11 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -902,14 +952,14 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COGS (10%) covers professional colour products (Schwarzkopf/Milbon/Redken).</t>
+          <t xml:space="preserve">  • Latitude/Longitude (Cities!Q/R): Used by the Leaflet map on the dashboard. Enter decimal degrees. Negative = South/West.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Utilisation: 65% Year 1 (ramp-up), 75% Year 2 (steady state).</t>
+          <t xml:space="preserve">  • Underserved Gap % (Cities!S): Estimated % of premium-capable residents without a nearby premium salon. Drives map marker radius.</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:S50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1398,6 +1448,9 @@
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="9" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1420,24 +1473,40 @@
           <t>IDENTITY</t>
         </is>
       </c>
+      <c r="B3" s="29" t="n"/>
+      <c r="C3" s="29" t="n"/>
+      <c r="D3" s="30" t="n"/>
       <c r="E3" s="14" t="inlineStr">
         <is>
           <t>SPACE &amp; TIME</t>
         </is>
       </c>
+      <c r="F3" s="29" t="n"/>
+      <c r="G3" s="30" t="n"/>
       <c r="H3" s="14" t="inlineStr">
         <is>
           <t>PRICING</t>
         </is>
       </c>
+      <c r="I3" s="30" t="n"/>
       <c r="J3" s="14" t="inlineStr">
         <is>
           <t>COSTS &amp; CAPEX</t>
         </is>
       </c>
+      <c r="K3" s="29" t="n"/>
+      <c r="L3" s="29" t="n"/>
+      <c r="M3" s="29" t="n"/>
+      <c r="N3" s="30" t="n"/>
       <c r="O3" s="14" t="inlineStr">
         <is>
           <t>UTILISATION</t>
+        </is>
+      </c>
+      <c r="P3" s="30" t="n"/>
+      <c r="Q3" s="14" t="inlineStr">
+        <is>
+          <t>GEOGRAPHY</t>
         </is>
       </c>
     </row>
@@ -1534,6 +1603,22 @@
 (%)</t>
         </is>
       </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="R4" s="8" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="S4" s="8" t="inlineStr">
+        <is>
+          <t>Underserved
+Gap (%)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
@@ -1592,6 +1677,15 @@
       <c r="P5" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q5" s="31" t="n">
+        <v>10.776</v>
+      </c>
+      <c r="R5" s="31" t="n">
+        <v>106.701</v>
+      </c>
+      <c r="S5" s="19" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
@@ -1650,6 +1744,15 @@
       <c r="P6" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q6" s="31" t="n">
+        <v>21.028</v>
+      </c>
+      <c r="R6" s="31" t="n">
+        <v>105.852</v>
+      </c>
+      <c r="S6" s="19" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
@@ -1708,6 +1811,15 @@
       <c r="P7" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q7" s="31" t="n">
+        <v>16.068</v>
+      </c>
+      <c r="R7" s="31" t="n">
+        <v>108.212</v>
+      </c>
+      <c r="S7" s="19" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
@@ -1766,6 +1878,15 @@
       <c r="P8" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q8" s="31" t="n">
+        <v>20.865</v>
+      </c>
+      <c r="R8" s="31" t="n">
+        <v>106.683</v>
+      </c>
+      <c r="S8" s="19" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
@@ -1824,6 +1945,15 @@
       <c r="P9" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q9" s="31" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="R9" s="31" t="n">
+        <v>106.653</v>
+      </c>
+      <c r="S9" s="19" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
@@ -1882,6 +2012,15 @@
       <c r="P10" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q10" s="31" t="n">
+        <v>10.945</v>
+      </c>
+      <c r="R10" s="31" t="n">
+        <v>106.824</v>
+      </c>
+      <c r="S10" s="19" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
@@ -1940,6 +2079,15 @@
       <c r="P11" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q11" s="31" t="n">
+        <v>3.148</v>
+      </c>
+      <c r="R11" s="31" t="n">
+        <v>101.686</v>
+      </c>
+      <c r="S11" s="19" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
@@ -1998,6 +2146,15 @@
       <c r="P12" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q12" s="31" t="n">
+        <v>1.492</v>
+      </c>
+      <c r="R12" s="31" t="n">
+        <v>103.743</v>
+      </c>
+      <c r="S12" s="19" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
@@ -2056,6 +2213,15 @@
       <c r="P13" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q13" s="31" t="n">
+        <v>5.414</v>
+      </c>
+      <c r="R13" s="31" t="n">
+        <v>100.33</v>
+      </c>
+      <c r="S13" s="19" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
@@ -2114,6 +2280,15 @@
       <c r="P14" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q14" s="31" t="n">
+        <v>5.978</v>
+      </c>
+      <c r="R14" s="31" t="n">
+        <v>116.073</v>
+      </c>
+      <c r="S14" s="19" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
@@ -2172,6 +2347,15 @@
       <c r="P15" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q15" s="31" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="R15" s="31" t="n">
+        <v>110.36</v>
+      </c>
+      <c r="S15" s="19" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
@@ -2230,6 +2414,15 @@
       <c r="P16" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q16" s="31" t="n">
+        <v>1.283</v>
+      </c>
+      <c r="R16" s="31" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="S16" s="19" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
@@ -2288,6 +2481,15 @@
       <c r="P17" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q17" s="31" t="n">
+        <v>22.279</v>
+      </c>
+      <c r="R17" s="31" t="n">
+        <v>114.165</v>
+      </c>
+      <c r="S17" s="19" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
@@ -2346,6 +2548,15 @@
       <c r="P18" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q18" s="31" t="n">
+        <v>13.745</v>
+      </c>
+      <c r="R18" s="31" t="n">
+        <v>100.532</v>
+      </c>
+      <c r="S18" s="19" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
@@ -2404,6 +2615,15 @@
       <c r="P19" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q19" s="31" t="n">
+        <v>22.197</v>
+      </c>
+      <c r="R19" s="31" t="n">
+        <v>113.545</v>
+      </c>
+      <c r="S19" s="19" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -2462,6 +2682,15 @@
       <c r="P20" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q20" s="31" t="n">
+        <v>25.187</v>
+      </c>
+      <c r="R20" s="31" t="n">
+        <v>55.274</v>
+      </c>
+      <c r="S20" s="19" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
@@ -2520,6 +2749,15 @@
       <c r="P21" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q21" s="31" t="n">
+        <v>25.033</v>
+      </c>
+      <c r="R21" s="31" t="n">
+        <v>121.565</v>
+      </c>
+      <c r="S21" s="19" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
@@ -2578,6 +2816,15 @@
       <c r="P22" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q22" s="31" t="n">
+        <v>24.163</v>
+      </c>
+      <c r="R22" s="31" t="n">
+        <v>120.647</v>
+      </c>
+      <c r="S22" s="19" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
@@ -2636,6 +2883,15 @@
       <c r="P23" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q23" s="31" t="n">
+        <v>22.627</v>
+      </c>
+      <c r="R23" s="31" t="n">
+        <v>120.302</v>
+      </c>
+      <c r="S23" s="19" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
@@ -2694,6 +2950,15 @@
       <c r="P24" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q24" s="31" t="n">
+        <v>22.993</v>
+      </c>
+      <c r="R24" s="31" t="n">
+        <v>120.202</v>
+      </c>
+      <c r="S24" s="19" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
@@ -2752,6 +3017,15 @@
       <c r="P25" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q25" s="31" t="n">
+        <v>33.589</v>
+      </c>
+      <c r="R25" s="31" t="n">
+        <v>130.398</v>
+      </c>
+      <c r="S25" s="19" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
@@ -2810,6 +3084,15 @@
       <c r="P26" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q26" s="31" t="n">
+        <v>26.213</v>
+      </c>
+      <c r="R26" s="31" t="n">
+        <v>127.679</v>
+      </c>
+      <c r="S26" s="19" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
@@ -2868,6 +3151,15 @@
       <c r="P27" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q27" s="31" t="n">
+        <v>35.158</v>
+      </c>
+      <c r="R27" s="31" t="n">
+        <v>129.06</v>
+      </c>
+      <c r="S27" s="19" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
@@ -2926,6 +3218,15 @@
       <c r="P28" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q28" s="31" t="n">
+        <v>-33.869</v>
+      </c>
+      <c r="R28" s="31" t="n">
+        <v>151.207</v>
+      </c>
+      <c r="S28" s="19" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
@@ -2984,6 +3285,15 @@
       <c r="P29" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q29" s="31" t="n">
+        <v>-37.814</v>
+      </c>
+      <c r="R29" s="31" t="n">
+        <v>144.963</v>
+      </c>
+      <c r="S29" s="19" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
@@ -3042,6 +3352,15 @@
       <c r="P30" s="21" t="n">
         <v>0.75</v>
       </c>
+      <c r="Q30" s="31" t="n">
+        <v>-27.47</v>
+      </c>
+      <c r="R30" s="31" t="n">
+        <v>153.026</v>
+      </c>
+      <c r="S30" s="19" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
@@ -3100,13 +3419,42 @@
       <c r="P31" s="21" t="n">
         <v>0.75</v>
       </c>
-    </row>
+      <c r="Q31" s="31" t="n">
+        <v>-31.953</v>
+      </c>
+      <c r="R31" s="31" t="n">
+        <v>115.857</v>
+      </c>
+      <c r="S31" s="19" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="O3:P3"/>
     <mergeCell ref="J3:N3"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
+    <mergeCell ref="Q3:S3"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="E3:G3"/>
     <mergeCell ref="H3:I3"/>
@@ -3177,16 +3525,26 @@
           <t>IDENTITY</t>
         </is>
       </c>
+      <c r="B3" s="30" t="n"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
           <t>SPACE → STAFF</t>
         </is>
       </c>
+      <c r="D3" s="29" t="n"/>
+      <c r="E3" s="29" t="n"/>
+      <c r="F3" s="29" t="n"/>
+      <c r="G3" s="29" t="n"/>
+      <c r="H3" s="30" t="n"/>
       <c r="I3" s="14" t="inlineStr">
         <is>
           <t>COUNTRY RATES</t>
         </is>
       </c>
+      <c r="J3" s="29" t="n"/>
+      <c r="K3" s="29" t="n"/>
+      <c r="L3" s="29" t="n"/>
+      <c r="M3" s="30" t="n"/>
       <c r="N3" s="14" t="inlineStr">
         <is>
           <t>STAFF COST</t>
@@ -3197,21 +3555,33 @@
           <t>MONTHLY OPEX</t>
         </is>
       </c>
+      <c r="P3" s="29" t="n"/>
+      <c r="Q3" s="29" t="n"/>
+      <c r="R3" s="30" t="n"/>
       <c r="S3" s="14" t="inlineStr">
         <is>
           <t>CAPACITY</t>
         </is>
       </c>
+      <c r="T3" s="29" t="n"/>
+      <c r="U3" s="30" t="n"/>
       <c r="V3" s="14" t="inlineStr">
         <is>
           <t>UNIT ECONOMICS</t>
         </is>
       </c>
+      <c r="W3" s="29" t="n"/>
+      <c r="X3" s="29" t="n"/>
+      <c r="Y3" s="30" t="n"/>
       <c r="Z3" s="14" t="inlineStr">
         <is>
           <t>CAPEX &amp; PAYBACK</t>
         </is>
       </c>
+      <c r="AA3" s="29" t="n"/>
+      <c r="AB3" s="29" t="n"/>
+      <c r="AC3" s="29" t="n"/>
+      <c r="AD3" s="30" t="n"/>
       <c r="AE3" s="14" t="inlineStr">
         <is>
           <t>VIABLE?</t>

--- a/salon_data.xlsx
+++ b/salon_data.xlsx
@@ -23,8 +23,8 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;USD &quot;[$-en-US]#,##0"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -123,7 +123,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -145,55 +145,11 @@
         <color rgb="00BBBBBB"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BBBBBB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BBBBBB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BBBBBB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BBBBBB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BBBBBB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BBBBBB"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -256,6 +212,9 @@
     <xf numFmtId="9" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -268,7 +227,7 @@
     <xf numFmtId="166" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -276,11 +235,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -660,10 +614,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -717,256 +671,263 @@
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">   - Latitude, Longitude, and Underserved Gap % (for map visualization)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="14" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Biz Reg Fee (one-time license fee) and Admin &amp; SW (monthly admin overhead)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="14" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">   - Year 1 and Year 2 utilisation targets</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>• Model sheet:      All formulas. Do NOT edit directly. Reads from Cities + Country.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="8" customHeight="1">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>⚙️ KEY FORMULAS</t>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>• Model sheet:      All calculations. Do NOT edit directly. Reads from Cities + Country.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="8" customHeight="1">
       <c r="A13" s="2" t="inlineStr"/>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Stations         = IF(sqft ≤ 750 → 3, sqft ≤ 850 → 4, else 5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Max Capacity     = stations × sessions/day × working_days/month</t>
-        </is>
-      </c>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>⚙️ KEY FORMULAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="8" customHeight="1">
+      <c r="A15" s="2" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Y2 Clients       = INT(max_capacity × util_Y2)</t>
+          <t xml:space="preserve">  Styling Stations = IF(sqft ≤ 750 → 3, sqft ≤ 850 → 4, else 5)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Staff Cost       = seniors×senior_rate + juniors×junior_rate + assistants×asst_rate + manager_rate</t>
+          <t xml:space="preserve">  Color Bar Seats  = Stations - 1  (Provides overflow capacity for concurrent color processing)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total OPEX       = Rent + Staff_Cost + Utilities(200+stations×80) + Mktg+Misc(650+stations×80)</t>
+          <t xml:space="preserve">  Total Seats      = Stations + Color Bar Seats</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Breakeven        = CEILING(OPEX / (ticket × (1 − COGS%)), 1)</t>
+          <t xml:space="preserve">  Max Capacity     = Stations × sessions/day × working_days/month</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CAPEX Low        = FLOOR((fitout+equip+other+rent×dep_months) × 0.92, $5,000)</t>
+          <t xml:space="preserve">  Total Staff Cost = seniors×senior_rate + juniors×junior_rate + assistants×asst_rate + manager_rate</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CAPEX High       = CEILING((fitout+equip+other+rent×dep_months) × 1.08, $5,000)</t>
+          <t xml:space="preserve">  Depreciation     = Equipment Cost / 60  (Straight-line over 5 years / 60 months)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Y2 Monthly PAT   = (Y2_clients × ticket × (1−COGS%) − OPEX) × (1 − tax_rate)</t>
+          <t xml:space="preserve">  Total Cash OPEX  = Rent + Staff_Cost + Utilities(200+stations×80) + Mktg+Misc(650+stations×80) + Admin/SW</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Payback          = CEILING(CAPEX_mid / Y2_PAT, 1 month)</t>
+          <t xml:space="preserve">  Accounting BE    = CEILING((Total Cash OPEX + Depreciation) / (ticket × (1 − COGS%)), 1)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PAT/OPEX         = Y2_PAT / OPEX</t>
+          <t xml:space="preserve">  CAPEX Base       = Fitout + Equipment + Other + Biz_Reg_Fee + Rent × Deposit_Months</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Viable?          = YES if Breakeven &lt; 80% of Max Capacity</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="8" customHeight="1">
-      <c r="A26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+          <t xml:space="preserve">  Y2 Monthly PAT   = (Y2_clients × ticket × (1−COGS%) − Cash OPEX − Depreciation) × (1 − tax_rate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Y2 Monthly CF    = Y2_PAT + Depreciation (Add back non-cash depreciation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Payback          = If Y1 Cash Flow covers CAPEX: CAPEX/Y1_CF. Else: 12 + (CAPEX - Y1_CF*12)/Y2_CF</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Viable?          = YES if Accounting Breakeven &lt; 80% of Max Capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1">
+      <c r="A29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>🔄 UPDATE WORKFLOW</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="8" customHeight="1">
-      <c r="A28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. Edit values in Country or Cities sheet (yellow cells).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. Review the Model sheet to check that all formulas recalculate correctly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. Save the Excel file.</t>
-        </is>
-      </c>
+    <row r="31" ht="8" customHeight="1">
+      <c r="A31" s="2" t="inlineStr"/>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Open a terminal and run:</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="14" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       cd c:\Users\vince\Projects\HairSpa\Oasis_Salon_Web</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="14" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       python excel_to_json.py</t>
+          <t xml:space="preserve">  1. Edit values in Country or Cities sheet (yellow cells).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. Review the Model sheet to check that all formulas recalculate correctly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Save the Excel file.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. This regenerates city_data.json AND updates the citiesDb in script.js.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+          <t xml:space="preserve">  4. Open a terminal and run:</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="14" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       python excel_to_json.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. This regenerates city_data.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  6. Commit and push:</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="14" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="39" ht="14" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">       git add -A &amp;&amp; git commit -m "Update financials" &amp;&amp; git push</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="8" customHeight="1">
-      <c r="A38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>📌 NOTES</t>
         </is>
       </c>
     </row>
     <row r="40" ht="8" customHeight="1">
       <c r="A40" s="2" t="inlineStr"/>
     </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Taipei vs Taichung CAPEX: Taipei (USD 75-95k) &gt; Taichung (USD 65-80k) because</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="14" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Taipei has: higher rent ($2,200 vs $1,800) + higher Da'an district fitout (NTD 1.8M vs 1.5M) + 850 sqft vs 800 sqft.</t>
-        </is>
-      </c>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>📌 NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="8" customHeight="1">
+      <c r="A42" s="2" t="inlineStr"/>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Fukuoka uses 22 working days/month (Japanese boutique: closed Mon + limited Sun).</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Dubai uses 12 deposit months (UAE annual lease pre-payment norm).</t>
+          <t xml:space="preserve">  • Taipei vs Taichung CAPEX: Taipei (USD 80-100k) &gt; Taichung (USD 65-85k) because</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="14" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Taipei has: higher rent ($2,200 vs $1,800) + higher Da'an district fitout (USD 55.8k vs 46.5k) + 850 sqft vs 800 sqft.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • All staff rates are in USD/month at mid-2025 exchange rates.</t>
+          <t xml:space="preserve">  • Japan (Fukuoka, Okinawa) uses 22 working days/month due to standard Monday closures in the Japanese market.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Latitude/Longitude (Cities!Q/R): Used by the Leaflet map on the dashboard. Enter decimal degrees. Negative = South/West.</t>
+          <t xml:space="preserve">  • Dubai uses 12 deposit months (UAE annual lease pre-payment norm).</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Underserved Gap % (Cities!S): Estimated % of premium-capable residents without a nearby premium salon. Drives map marker radius.</t>
+          <t xml:space="preserve">  • South Korea corporate tax is set to 22.0% (incorporating 20.0% national + 2.0% local income taxes).</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Payback period is calculated at Year 2 (75%) utilisation.</t>
+          <t xml:space="preserve">  • Biz Reg Fee covers company setup, legal counsel, bank creation, and local salon permit fees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Equipment depreciation over 5 years reduces taxable income (tax shield) and is added back for cash flow payback.</t>
         </is>
       </c>
     </row>
@@ -986,7 +947,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -1130,7 +1091,7 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
@@ -1429,7 +1390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S50"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1451,6 +1412,8 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1473,40 +1436,34 @@
           <t>IDENTITY</t>
         </is>
       </c>
-      <c r="B3" s="29" t="n"/>
-      <c r="C3" s="29" t="n"/>
-      <c r="D3" s="30" t="n"/>
       <c r="E3" s="14" t="inlineStr">
         <is>
           <t>SPACE &amp; TIME</t>
         </is>
       </c>
-      <c r="F3" s="29" t="n"/>
-      <c r="G3" s="30" t="n"/>
       <c r="H3" s="14" t="inlineStr">
         <is>
           <t>PRICING</t>
         </is>
       </c>
-      <c r="I3" s="30" t="n"/>
       <c r="J3" s="14" t="inlineStr">
         <is>
           <t>COSTS &amp; CAPEX</t>
         </is>
       </c>
-      <c r="K3" s="29" t="n"/>
-      <c r="L3" s="29" t="n"/>
-      <c r="M3" s="29" t="n"/>
-      <c r="N3" s="30" t="n"/>
       <c r="O3" s="14" t="inlineStr">
         <is>
           <t>UTILISATION</t>
         </is>
       </c>
-      <c r="P3" s="30" t="n"/>
       <c r="Q3" s="14" t="inlineStr">
         <is>
           <t>GEOGRAPHY</t>
+        </is>
+      </c>
+      <c r="T3" s="14" t="inlineStr">
+        <is>
+          <t>BUSINESS FEES &amp; ADMIN</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1573,19 @@
       <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Underserved
-Gap (%)</t>
+Gap %</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>Biz Reg Fee
+(USD)</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>Admin &amp; SW
+(USD/mo)</t>
         </is>
       </c>
     </row>
@@ -1677,15 +1646,21 @@
       <c r="P5" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q5" s="31" t="n">
+      <c r="Q5" s="22" t="n">
         <v>10.776</v>
       </c>
-      <c r="R5" s="31" t="n">
+      <c r="R5" s="22" t="n">
         <v>106.701</v>
       </c>
       <c r="S5" s="19" t="n">
         <v>65</v>
       </c>
+      <c r="T5" s="20" t="n">
+        <v>2500</v>
+      </c>
+      <c r="U5" s="20" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
@@ -1744,15 +1719,21 @@
       <c r="P6" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q6" s="31" t="n">
+      <c r="Q6" s="22" t="n">
         <v>21.028</v>
       </c>
-      <c r="R6" s="31" t="n">
+      <c r="R6" s="22" t="n">
         <v>105.852</v>
       </c>
       <c r="S6" s="19" t="n">
         <v>55</v>
       </c>
+      <c r="T6" s="20" t="n">
+        <v>2500</v>
+      </c>
+      <c r="U6" s="20" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
@@ -1811,15 +1792,21 @@
       <c r="P7" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q7" s="31" t="n">
+      <c r="Q7" s="22" t="n">
         <v>16.068</v>
       </c>
-      <c r="R7" s="31" t="n">
+      <c r="R7" s="22" t="n">
         <v>108.212</v>
       </c>
       <c r="S7" s="19" t="n">
         <v>70</v>
       </c>
+      <c r="T7" s="20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U7" s="20" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
@@ -1878,15 +1865,21 @@
       <c r="P8" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q8" s="31" t="n">
+      <c r="Q8" s="22" t="n">
         <v>20.865</v>
       </c>
-      <c r="R8" s="31" t="n">
+      <c r="R8" s="22" t="n">
         <v>106.683</v>
       </c>
       <c r="S8" s="19" t="n">
         <v>72</v>
       </c>
+      <c r="T8" s="20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U8" s="20" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
@@ -1945,15 +1938,21 @@
       <c r="P9" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q9" s="31" t="n">
+      <c r="Q9" s="22" t="n">
         <v>10.98</v>
       </c>
-      <c r="R9" s="31" t="n">
+      <c r="R9" s="22" t="n">
         <v>106.653</v>
       </c>
       <c r="S9" s="19" t="n">
         <v>75</v>
       </c>
+      <c r="T9" s="20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U9" s="20" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
@@ -2012,15 +2011,21 @@
       <c r="P10" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q10" s="31" t="n">
+      <c r="Q10" s="22" t="n">
         <v>10.945</v>
       </c>
-      <c r="R10" s="31" t="n">
+      <c r="R10" s="22" t="n">
         <v>106.824</v>
       </c>
       <c r="S10" s="19" t="n">
         <v>73</v>
       </c>
+      <c r="T10" s="20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U10" s="20" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
@@ -2079,15 +2084,21 @@
       <c r="P11" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q11" s="31" t="n">
+      <c r="Q11" s="22" t="n">
         <v>3.148</v>
       </c>
-      <c r="R11" s="31" t="n">
+      <c r="R11" s="22" t="n">
         <v>101.686</v>
       </c>
       <c r="S11" s="19" t="n">
         <v>40</v>
       </c>
+      <c r="T11" s="20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U11" s="20" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
@@ -2146,15 +2157,21 @@
       <c r="P12" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q12" s="31" t="n">
+      <c r="Q12" s="22" t="n">
         <v>1.492</v>
       </c>
-      <c r="R12" s="31" t="n">
+      <c r="R12" s="22" t="n">
         <v>103.743</v>
       </c>
       <c r="S12" s="19" t="n">
         <v>55</v>
       </c>
+      <c r="T12" s="20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U12" s="20" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
@@ -2213,15 +2230,21 @@
       <c r="P13" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q13" s="31" t="n">
+      <c r="Q13" s="22" t="n">
         <v>5.414</v>
       </c>
-      <c r="R13" s="31" t="n">
+      <c r="R13" s="22" t="n">
         <v>100.33</v>
       </c>
       <c r="S13" s="19" t="n">
         <v>50</v>
       </c>
+      <c r="T13" s="20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U13" s="20" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
@@ -2280,15 +2303,21 @@
       <c r="P14" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q14" s="31" t="n">
+      <c r="Q14" s="22" t="n">
         <v>5.978</v>
       </c>
-      <c r="R14" s="31" t="n">
+      <c r="R14" s="22" t="n">
         <v>116.073</v>
       </c>
       <c r="S14" s="19" t="n">
         <v>68</v>
       </c>
+      <c r="T14" s="20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U14" s="20" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
@@ -2347,15 +2376,21 @@
       <c r="P15" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q15" s="31" t="n">
+      <c r="Q15" s="22" t="n">
         <v>1.553</v>
       </c>
-      <c r="R15" s="31" t="n">
+      <c r="R15" s="22" t="n">
         <v>110.36</v>
       </c>
       <c r="S15" s="19" t="n">
         <v>65</v>
       </c>
+      <c r="T15" s="20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U15" s="20" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
@@ -2414,15 +2449,21 @@
       <c r="P16" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q16" s="31" t="n">
+      <c r="Q16" s="22" t="n">
         <v>1.283</v>
       </c>
-      <c r="R16" s="31" t="n">
+      <c r="R16" s="22" t="n">
         <v>103.85</v>
       </c>
       <c r="S16" s="19" t="n">
         <v>25</v>
       </c>
+      <c r="T16" s="20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U16" s="20" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
@@ -2481,15 +2522,21 @@
       <c r="P17" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q17" s="31" t="n">
+      <c r="Q17" s="22" t="n">
         <v>22.279</v>
       </c>
-      <c r="R17" s="31" t="n">
+      <c r="R17" s="22" t="n">
         <v>114.165</v>
       </c>
       <c r="S17" s="19" t="n">
         <v>22</v>
       </c>
+      <c r="T17" s="20" t="n">
+        <v>1200</v>
+      </c>
+      <c r="U17" s="20" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
@@ -2548,15 +2595,21 @@
       <c r="P18" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q18" s="31" t="n">
+      <c r="Q18" s="22" t="n">
         <v>13.745</v>
       </c>
-      <c r="R18" s="31" t="n">
+      <c r="R18" s="22" t="n">
         <v>100.532</v>
       </c>
       <c r="S18" s="19" t="n">
         <v>45</v>
       </c>
+      <c r="T18" s="20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="U18" s="20" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
@@ -2615,15 +2668,21 @@
       <c r="P19" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q19" s="31" t="n">
+      <c r="Q19" s="22" t="n">
         <v>22.197</v>
       </c>
-      <c r="R19" s="31" t="n">
+      <c r="R19" s="22" t="n">
         <v>113.545</v>
       </c>
       <c r="S19" s="19" t="n">
         <v>38</v>
       </c>
+      <c r="T19" s="20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U19" s="20" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -2682,15 +2741,21 @@
       <c r="P20" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q20" s="31" t="n">
+      <c r="Q20" s="22" t="n">
         <v>25.187</v>
       </c>
-      <c r="R20" s="31" t="n">
+      <c r="R20" s="22" t="n">
         <v>55.274</v>
       </c>
       <c r="S20" s="19" t="n">
         <v>30</v>
       </c>
+      <c r="T20" s="20" t="n">
+        <v>6000</v>
+      </c>
+      <c r="U20" s="20" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
@@ -2749,15 +2814,21 @@
       <c r="P21" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q21" s="31" t="n">
+      <c r="Q21" s="22" t="n">
         <v>25.033</v>
       </c>
-      <c r="R21" s="31" t="n">
+      <c r="R21" s="22" t="n">
         <v>121.565</v>
       </c>
       <c r="S21" s="19" t="n">
         <v>35</v>
       </c>
+      <c r="T21" s="20" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U21" s="20" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
@@ -2816,15 +2887,21 @@
       <c r="P22" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q22" s="31" t="n">
+      <c r="Q22" s="22" t="n">
         <v>24.163</v>
       </c>
-      <c r="R22" s="31" t="n">
+      <c r="R22" s="22" t="n">
         <v>120.647</v>
       </c>
       <c r="S22" s="19" t="n">
         <v>42</v>
       </c>
+      <c r="T22" s="20" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U22" s="20" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
@@ -2883,15 +2960,21 @@
       <c r="P23" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q23" s="31" t="n">
+      <c r="Q23" s="22" t="n">
         <v>22.627</v>
       </c>
-      <c r="R23" s="31" t="n">
+      <c r="R23" s="22" t="n">
         <v>120.302</v>
       </c>
       <c r="S23" s="19" t="n">
         <v>48</v>
       </c>
+      <c r="T23" s="20" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U23" s="20" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
@@ -2950,15 +3033,21 @@
       <c r="P24" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q24" s="31" t="n">
+      <c r="Q24" s="22" t="n">
         <v>22.993</v>
       </c>
-      <c r="R24" s="31" t="n">
+      <c r="R24" s="22" t="n">
         <v>120.202</v>
       </c>
       <c r="S24" s="19" t="n">
         <v>55</v>
       </c>
+      <c r="T24" s="20" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U24" s="20" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
@@ -3017,15 +3106,21 @@
       <c r="P25" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q25" s="31" t="n">
+      <c r="Q25" s="22" t="n">
         <v>33.589</v>
       </c>
-      <c r="R25" s="31" t="n">
+      <c r="R25" s="22" t="n">
         <v>130.398</v>
       </c>
       <c r="S25" s="19" t="n">
         <v>38</v>
       </c>
+      <c r="T25" s="20" t="n">
+        <v>2500</v>
+      </c>
+      <c r="U25" s="20" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
@@ -3055,7 +3150,7 @@
         <v>3</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H26" s="20" t="n">
         <v>120</v>
@@ -3084,15 +3179,21 @@
       <c r="P26" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q26" s="31" t="n">
+      <c r="Q26" s="22" t="n">
         <v>26.213</v>
       </c>
-      <c r="R26" s="31" t="n">
+      <c r="R26" s="22" t="n">
         <v>127.679</v>
       </c>
       <c r="S26" s="19" t="n">
         <v>52</v>
       </c>
+      <c r="T26" s="20" t="n">
+        <v>2500</v>
+      </c>
+      <c r="U26" s="20" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
@@ -3151,15 +3252,21 @@
       <c r="P27" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q27" s="31" t="n">
+      <c r="Q27" s="22" t="n">
         <v>35.158</v>
       </c>
-      <c r="R27" s="31" t="n">
+      <c r="R27" s="22" t="n">
         <v>129.06</v>
       </c>
       <c r="S27" s="19" t="n">
         <v>45</v>
       </c>
+      <c r="T27" s="20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="U27" s="20" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
@@ -3218,15 +3325,21 @@
       <c r="P28" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q28" s="31" t="n">
+      <c r="Q28" s="22" t="n">
         <v>-33.869</v>
       </c>
-      <c r="R28" s="31" t="n">
+      <c r="R28" s="22" t="n">
         <v>151.207</v>
       </c>
       <c r="S28" s="19" t="n">
         <v>30</v>
       </c>
+      <c r="T28" s="20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U28" s="20" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
@@ -3285,15 +3398,21 @@
       <c r="P29" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q29" s="31" t="n">
+      <c r="Q29" s="22" t="n">
         <v>-37.814</v>
       </c>
-      <c r="R29" s="31" t="n">
+      <c r="R29" s="22" t="n">
         <v>144.963</v>
       </c>
       <c r="S29" s="19" t="n">
         <v>32</v>
       </c>
+      <c r="T29" s="20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U29" s="20" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
@@ -3352,15 +3471,21 @@
       <c r="P30" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q30" s="31" t="n">
+      <c r="Q30" s="22" t="n">
         <v>-27.47</v>
       </c>
-      <c r="R30" s="31" t="n">
+      <c r="R30" s="22" t="n">
         <v>153.026</v>
       </c>
       <c r="S30" s="19" t="n">
         <v>36</v>
       </c>
+      <c r="T30" s="20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U30" s="20" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
@@ -3419,44 +3544,32 @@
       <c r="P31" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q31" s="31" t="n">
+      <c r="Q31" s="22" t="n">
         <v>-31.953</v>
       </c>
-      <c r="R31" s="31" t="n">
+      <c r="R31" s="22" t="n">
         <v>115.857</v>
       </c>
       <c r="S31" s="19" t="n">
         <v>38</v>
       </c>
-    </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
+      <c r="T31" s="20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U31" s="20" t="n">
+        <v>300</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="O3:P3"/>
     <mergeCell ref="J3:N3"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A2:U2"/>
     <mergeCell ref="Q3:S3"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="E3:G3"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="T3:U3"/>
     <mergeCell ref="H3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3469,40 +3582,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE31"/>
+  <dimension ref="A1:AL31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="12" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3513,7 +3633,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>🔒 Do not edit this sheet directly — change inputs in Cities sheet. BLUE = formula cells.</t>
         </is>
@@ -3525,64 +3645,57 @@
           <t>IDENTITY</t>
         </is>
       </c>
-      <c r="B3" s="30" t="n"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>SPACE → STAFF</t>
-        </is>
-      </c>
-      <c r="D3" s="29" t="n"/>
-      <c r="E3" s="29" t="n"/>
-      <c r="F3" s="29" t="n"/>
-      <c r="G3" s="29" t="n"/>
-      <c r="H3" s="30" t="n"/>
-      <c r="I3" s="14" t="inlineStr">
+          <t>SPACE &amp; SEATS</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>STAFFING MODEL</t>
+        </is>
+      </c>
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t>COUNTRY RATES</t>
         </is>
       </c>
-      <c r="J3" s="29" t="n"/>
-      <c r="K3" s="29" t="n"/>
-      <c r="L3" s="29" t="n"/>
-      <c r="M3" s="30" t="n"/>
-      <c r="N3" s="14" t="inlineStr">
+      <c r="P3" s="14" t="inlineStr">
         <is>
           <t>STAFF COST</t>
         </is>
       </c>
-      <c r="O3" s="14" t="inlineStr">
+      <c r="Q3" s="14" t="inlineStr">
         <is>
           <t>MONTHLY OPEX</t>
         </is>
       </c>
-      <c r="P3" s="29" t="n"/>
-      <c r="Q3" s="29" t="n"/>
-      <c r="R3" s="30" t="n"/>
-      <c r="S3" s="14" t="inlineStr">
+      <c r="W3" s="14" t="inlineStr">
         <is>
           <t>CAPACITY</t>
         </is>
       </c>
-      <c r="T3" s="29" t="n"/>
-      <c r="U3" s="30" t="n"/>
-      <c r="V3" s="14" t="inlineStr">
+      <c r="Z3" s="14" t="inlineStr">
         <is>
           <t>UNIT ECONOMICS</t>
         </is>
       </c>
-      <c r="W3" s="29" t="n"/>
-      <c r="X3" s="29" t="n"/>
-      <c r="Y3" s="30" t="n"/>
-      <c r="Z3" s="14" t="inlineStr">
+      <c r="AC3" s="14" t="inlineStr">
+        <is>
+          <t>PROFIT &amp; CASH FLOW</t>
+        </is>
+      </c>
+      <c r="AG3" s="14" t="inlineStr">
         <is>
           <t>CAPEX &amp; PAYBACK</t>
         </is>
       </c>
-      <c r="AA3" s="29" t="n"/>
-      <c r="AB3" s="29" t="n"/>
-      <c r="AC3" s="29" t="n"/>
-      <c r="AD3" s="30" t="n"/>
-      <c r="AE3" s="14" t="inlineStr">
+      <c r="AK3" s="14" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="AL3" s="14" t="inlineStr">
         <is>
           <t>VIABLE?</t>
         </is>
@@ -3606,159 +3719,201 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
+          <t>Color Bar
+Seats</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Total
+Seats</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
           <t>Wash
 Basins</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Seniors</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Juniors</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Assistants</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Total
 Staff</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Tax Rate</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Senior
 (USD/mo)</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>Junior
 (USD/mo)</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr">
         <is>
           <t>Assistant
 (USD/mo)</t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr">
+      <c r="O4" s="8" t="inlineStr">
         <is>
           <t>Manager
 (USD/mo)</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="P4" s="8" t="inlineStr">
         <is>
           <t>Total Staff
 Cost (USD/mo)</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>Rent
 (USD/mo)</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>Utilities
 (USD/mo)</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Mktg+Misc
 (USD/mo)</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
-        <is>
-          <t>Total OPEX
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>Admin &amp; SW
 (USD/mo)</t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>Monthly
+Deprec (USD)</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>Total Cash
+OPEX (USD/mo)</t>
+        </is>
+      </c>
+      <c r="W4" s="8" t="inlineStr">
         <is>
           <t>Max
 Capacity</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="X4" s="8" t="inlineStr">
         <is>
           <t>Y1 Clients
 (65%)</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
+      <c r="Y4" s="8" t="inlineStr">
         <is>
           <t>Y2 Clients
 (75%)</t>
         </is>
       </c>
-      <c r="V4" s="8" t="inlineStr">
+      <c r="Z4" s="8" t="inlineStr">
         <is>
           <t>Breakeven
 (clients/mo)</t>
         </is>
       </c>
-      <c r="W4" s="8" t="inlineStr">
+      <c r="AA4" s="8" t="inlineStr">
         <is>
           <t>COGS/session</t>
         </is>
       </c>
-      <c r="X4" s="8" t="inlineStr">
+      <c r="AB4" s="8" t="inlineStr">
         <is>
           <t>GM/session
 (90%)</t>
         </is>
       </c>
-      <c r="Y4" s="8" t="inlineStr">
+      <c r="AC4" s="8" t="inlineStr">
+        <is>
+          <t>Y1 Monthly
+PAT (USD)</t>
+        </is>
+      </c>
+      <c r="AD4" s="8" t="inlineStr">
         <is>
           <t>Y2 Monthly
 PAT (USD)</t>
         </is>
       </c>
-      <c r="Z4" s="8" t="inlineStr">
+      <c r="AE4" s="8" t="inlineStr">
+        <is>
+          <t>Y1 Monthly
+CashFlow (USD)</t>
+        </is>
+      </c>
+      <c r="AF4" s="8" t="inlineStr">
+        <is>
+          <t>Y2 Monthly
+CashFlow (USD)</t>
+        </is>
+      </c>
+      <c r="AG4" s="8" t="inlineStr">
         <is>
           <t>CAPEX Low</t>
         </is>
       </c>
-      <c r="AA4" s="8" t="inlineStr">
+      <c r="AH4" s="8" t="inlineStr">
         <is>
           <t>CAPEX High</t>
         </is>
       </c>
-      <c r="AB4" s="8" t="inlineStr">
+      <c r="AI4" s="8" t="inlineStr">
         <is>
           <t>CAPEX Mid</t>
         </is>
       </c>
-      <c r="AC4" s="8" t="inlineStr">
+      <c r="AJ4" s="8" t="inlineStr">
         <is>
           <t>Payback
 (months)</t>
         </is>
       </c>
-      <c r="AD4" s="8" t="inlineStr">
+      <c r="AK4" s="8" t="inlineStr">
         <is>
           <t>PAT/OPEX
 (%)</t>
         </is>
       </c>
-      <c r="AE4" s="8" t="inlineStr">
+      <c r="AL4" s="8" t="inlineStr">
         <is>
           <t>VIABLE?
 (BE &lt; 80%cap)</t>
@@ -3774,120 +3929,148 @@
         <f>Cities!D5</f>
         <v/>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="24">
         <f>IF(Cities!E5&lt;=750,3,IF(Cities!E5&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="24">
+        <f>C5-1</f>
+        <v/>
+      </c>
+      <c r="E5" s="24">
+        <f>C5+D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="24">
         <f>IF(C5&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E5" s="23">
+      <c r="G5" s="24">
         <f>IF(C5&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F5" s="23">
-        <f>C5-E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="23">
+      <c r="H5" s="24">
+        <f>C5-G5</f>
+        <v/>
+      </c>
+      <c r="I5" s="24">
         <f>CEILING(C5/2,1)</f>
         <v/>
       </c>
-      <c r="H5" s="23">
-        <f>E5+F5+G5+1</f>
-        <v/>
-      </c>
-      <c r="I5" s="24">
+      <c r="J5" s="24">
+        <f>G5+H5+I5+1</f>
+        <v/>
+      </c>
+      <c r="K5" s="25">
         <f>VLOOKUP(Cities!D5,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J5" s="25">
+      <c r="L5" s="26">
         <f>VLOOKUP(Cities!D5,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K5" s="25">
+      <c r="M5" s="26">
         <f>VLOOKUP(Cities!D5,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L5" s="25">
+      <c r="N5" s="26">
         <f>VLOOKUP(Cities!D5,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M5" s="25">
+      <c r="O5" s="26">
         <f>VLOOKUP(Cities!D5,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N5" s="25">
-        <f>E5*J5+F5*K5+G5*L5+M5</f>
-        <v/>
-      </c>
-      <c r="O5" s="25">
+      <c r="P5" s="26">
+        <f>G5*L5+H5*M5+I5*N5+O5</f>
+        <v/>
+      </c>
+      <c r="Q5" s="26">
         <f>Cities!J5</f>
         <v/>
       </c>
-      <c r="P5" s="25">
+      <c r="R5" s="26">
         <f>200+C5*80</f>
         <v/>
       </c>
-      <c r="Q5" s="25">
+      <c r="S5" s="26">
         <f>350+C5*50+300+C5*30</f>
         <v/>
       </c>
-      <c r="R5" s="25">
-        <f>O5+N5+P5+Q5</f>
-        <v/>
-      </c>
-      <c r="S5" s="23">
+      <c r="T5" s="26">
+        <f>Cities!U5</f>
+        <v/>
+      </c>
+      <c r="U5" s="26">
+        <f>Cities!L5/60</f>
+        <v/>
+      </c>
+      <c r="V5" s="26">
+        <f>Q5+P5+R5+S5+T5</f>
+        <v/>
+      </c>
+      <c r="W5" s="24">
         <f>C5*Cities!F5*Cities!G5</f>
         <v/>
       </c>
-      <c r="T5" s="23">
-        <f>INT(S5*Cities!O5)</f>
-        <v/>
-      </c>
-      <c r="U5" s="23">
-        <f>INT(S5*Cities!P5)</f>
-        <v/>
-      </c>
-      <c r="V5" s="23">
-        <f>CEILING(R5/(Cities!H5*(1-Cities!I5)),1)</f>
-        <v/>
-      </c>
-      <c r="W5" s="26">
+      <c r="X5" s="24">
+        <f>INT(W5*Cities!O5)</f>
+        <v/>
+      </c>
+      <c r="Y5" s="24">
+        <f>INT(W5*Cities!P5)</f>
+        <v/>
+      </c>
+      <c r="Z5" s="24">
+        <f>CEILING((V5+U5)/AB5,1)</f>
+        <v/>
+      </c>
+      <c r="AA5" s="27">
         <f>Cities!H5*Cities!I5</f>
         <v/>
       </c>
-      <c r="X5" s="26">
-        <f>Cities!H5-W5</f>
-        <v/>
-      </c>
-      <c r="Y5" s="25">
-        <f>(U5*Cities!H5*(1-Cities!I5)-R5)*(1-I5)</f>
-        <v/>
-      </c>
-      <c r="Z5" s="25">
-        <f>FLOOR((Cities!K5+Cities!L5+Cities!M5+Cities!J5*Cities!N5)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA5" s="25">
-        <f>CEILING((Cities!K5+Cities!L5+Cities!M5+Cities!J5*Cities!N5)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB5" s="25">
-        <f>(Z5+AA5)/2</f>
-        <v/>
-      </c>
-      <c r="AC5" s="23">
-        <f>IF(Y5&gt;0,CEILING(AB5/Y5,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD5" s="27">
-        <f>IF(R5&gt;0,Y5/R5,0)</f>
-        <v/>
-      </c>
-      <c r="AE5" s="28">
-        <f>IF(V5&lt;S5*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB5" s="27">
+        <f>Cities!H5-AA5</f>
+        <v/>
+      </c>
+      <c r="AC5" s="26">
+        <f>IF((X5*AB5-V5-U5)&gt;0, (X5*AB5-V5-U5)*(1-K5), X5*AB5-V5-U5)</f>
+        <v/>
+      </c>
+      <c r="AD5" s="26">
+        <f>IF((Y5*AB5-V5-U5)&gt;0, (Y5*AB5-V5-U5)*(1-K5), Y5*AB5-V5-U5)</f>
+        <v/>
+      </c>
+      <c r="AE5" s="26">
+        <f>AC5+U5</f>
+        <v/>
+      </c>
+      <c r="AF5" s="26">
+        <f>AD5+U5</f>
+        <v/>
+      </c>
+      <c r="AG5" s="26">
+        <f>FLOOR((Cities!K5+Cities!L5+Cities!M5+Cities!T5+Cities!J5*Cities!N5)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH5" s="26">
+        <f>CEILING((Cities!K5+Cities!L5+Cities!M5+Cities!T5+Cities!J5*Cities!N5)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI5" s="26">
+        <f>(AG5+AH5)/2</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="24">
+        <f>IF(AE5*12&gt;=AI5, IF(AE5&gt;0,CEILING(AI5/AE5,1),999), IF(AF5&gt;0,12+CEILING((AI5-AE5*12)/AF5,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK5" s="28">
+        <f>IF(V5&gt;0,AD5/V5,0)</f>
+        <v/>
+      </c>
+      <c r="AL5" s="29">
+        <f>IF(Z5&lt;W5*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -3900,120 +4083,148 @@
         <f>Cities!D6</f>
         <v/>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="24">
         <f>IF(Cities!E6&lt;=750,3,IF(Cities!E6&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="24">
+        <f>C6-1</f>
+        <v/>
+      </c>
+      <c r="E6" s="24">
+        <f>C6+D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="24">
         <f>IF(C6&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E6" s="23">
+      <c r="G6" s="24">
         <f>IF(C6&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F6" s="23">
-        <f>C6-E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="23">
+      <c r="H6" s="24">
+        <f>C6-G6</f>
+        <v/>
+      </c>
+      <c r="I6" s="24">
         <f>CEILING(C6/2,1)</f>
         <v/>
       </c>
-      <c r="H6" s="23">
-        <f>E6+F6+G6+1</f>
-        <v/>
-      </c>
-      <c r="I6" s="24">
+      <c r="J6" s="24">
+        <f>G6+H6+I6+1</f>
+        <v/>
+      </c>
+      <c r="K6" s="25">
         <f>VLOOKUP(Cities!D6,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J6" s="25">
+      <c r="L6" s="26">
         <f>VLOOKUP(Cities!D6,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K6" s="25">
+      <c r="M6" s="26">
         <f>VLOOKUP(Cities!D6,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L6" s="25">
+      <c r="N6" s="26">
         <f>VLOOKUP(Cities!D6,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M6" s="25">
+      <c r="O6" s="26">
         <f>VLOOKUP(Cities!D6,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N6" s="25">
-        <f>E6*J6+F6*K6+G6*L6+M6</f>
-        <v/>
-      </c>
-      <c r="O6" s="25">
+      <c r="P6" s="26">
+        <f>G6*L6+H6*M6+I6*N6+O6</f>
+        <v/>
+      </c>
+      <c r="Q6" s="26">
         <f>Cities!J6</f>
         <v/>
       </c>
-      <c r="P6" s="25">
+      <c r="R6" s="26">
         <f>200+C6*80</f>
         <v/>
       </c>
-      <c r="Q6" s="25">
+      <c r="S6" s="26">
         <f>350+C6*50+300+C6*30</f>
         <v/>
       </c>
-      <c r="R6" s="25">
-        <f>O6+N6+P6+Q6</f>
-        <v/>
-      </c>
-      <c r="S6" s="23">
+      <c r="T6" s="26">
+        <f>Cities!U6</f>
+        <v/>
+      </c>
+      <c r="U6" s="26">
+        <f>Cities!L6/60</f>
+        <v/>
+      </c>
+      <c r="V6" s="26">
+        <f>Q6+P6+R6+S6+T6</f>
+        <v/>
+      </c>
+      <c r="W6" s="24">
         <f>C6*Cities!F6*Cities!G6</f>
         <v/>
       </c>
-      <c r="T6" s="23">
-        <f>INT(S6*Cities!O6)</f>
-        <v/>
-      </c>
-      <c r="U6" s="23">
-        <f>INT(S6*Cities!P6)</f>
-        <v/>
-      </c>
-      <c r="V6" s="23">
-        <f>CEILING(R6/(Cities!H6*(1-Cities!I6)),1)</f>
-        <v/>
-      </c>
-      <c r="W6" s="26">
+      <c r="X6" s="24">
+        <f>INT(W6*Cities!O6)</f>
+        <v/>
+      </c>
+      <c r="Y6" s="24">
+        <f>INT(W6*Cities!P6)</f>
+        <v/>
+      </c>
+      <c r="Z6" s="24">
+        <f>CEILING((V6+U6)/AB6,1)</f>
+        <v/>
+      </c>
+      <c r="AA6" s="27">
         <f>Cities!H6*Cities!I6</f>
         <v/>
       </c>
-      <c r="X6" s="26">
-        <f>Cities!H6-W6</f>
-        <v/>
-      </c>
-      <c r="Y6" s="25">
-        <f>(U6*Cities!H6*(1-Cities!I6)-R6)*(1-I6)</f>
-        <v/>
-      </c>
-      <c r="Z6" s="25">
-        <f>FLOOR((Cities!K6+Cities!L6+Cities!M6+Cities!J6*Cities!N6)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA6" s="25">
-        <f>CEILING((Cities!K6+Cities!L6+Cities!M6+Cities!J6*Cities!N6)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB6" s="25">
-        <f>(Z6+AA6)/2</f>
-        <v/>
-      </c>
-      <c r="AC6" s="23">
-        <f>IF(Y6&gt;0,CEILING(AB6/Y6,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD6" s="27">
-        <f>IF(R6&gt;0,Y6/R6,0)</f>
-        <v/>
-      </c>
-      <c r="AE6" s="28">
-        <f>IF(V6&lt;S6*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB6" s="27">
+        <f>Cities!H6-AA6</f>
+        <v/>
+      </c>
+      <c r="AC6" s="26">
+        <f>IF((X6*AB6-V6-U6)&gt;0, (X6*AB6-V6-U6)*(1-K6), X6*AB6-V6-U6)</f>
+        <v/>
+      </c>
+      <c r="AD6" s="26">
+        <f>IF((Y6*AB6-V6-U6)&gt;0, (Y6*AB6-V6-U6)*(1-K6), Y6*AB6-V6-U6)</f>
+        <v/>
+      </c>
+      <c r="AE6" s="26">
+        <f>AC6+U6</f>
+        <v/>
+      </c>
+      <c r="AF6" s="26">
+        <f>AD6+U6</f>
+        <v/>
+      </c>
+      <c r="AG6" s="26">
+        <f>FLOOR((Cities!K6+Cities!L6+Cities!M6+Cities!T6+Cities!J6*Cities!N6)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH6" s="26">
+        <f>CEILING((Cities!K6+Cities!L6+Cities!M6+Cities!T6+Cities!J6*Cities!N6)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI6" s="26">
+        <f>(AG6+AH6)/2</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="24">
+        <f>IF(AE6*12&gt;=AI6, IF(AE6&gt;0,CEILING(AI6/AE6,1),999), IF(AF6&gt;0,12+CEILING((AI6-AE6*12)/AF6,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK6" s="28">
+        <f>IF(V6&gt;0,AD6/V6,0)</f>
+        <v/>
+      </c>
+      <c r="AL6" s="29">
+        <f>IF(Z6&lt;W6*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -4026,120 +4237,148 @@
         <f>Cities!D7</f>
         <v/>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="24">
         <f>IF(Cities!E7&lt;=750,3,IF(Cities!E7&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="24">
+        <f>C7-1</f>
+        <v/>
+      </c>
+      <c r="E7" s="24">
+        <f>C7+D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="24">
         <f>IF(C7&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E7" s="23">
+      <c r="G7" s="24">
         <f>IF(C7&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F7" s="23">
-        <f>C7-E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="23">
+      <c r="H7" s="24">
+        <f>C7-G7</f>
+        <v/>
+      </c>
+      <c r="I7" s="24">
         <f>CEILING(C7/2,1)</f>
         <v/>
       </c>
-      <c r="H7" s="23">
-        <f>E7+F7+G7+1</f>
-        <v/>
-      </c>
-      <c r="I7" s="24">
+      <c r="J7" s="24">
+        <f>G7+H7+I7+1</f>
+        <v/>
+      </c>
+      <c r="K7" s="25">
         <f>VLOOKUP(Cities!D7,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J7" s="25">
+      <c r="L7" s="26">
         <f>VLOOKUP(Cities!D7,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K7" s="25">
+      <c r="M7" s="26">
         <f>VLOOKUP(Cities!D7,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L7" s="25">
+      <c r="N7" s="26">
         <f>VLOOKUP(Cities!D7,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M7" s="25">
+      <c r="O7" s="26">
         <f>VLOOKUP(Cities!D7,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N7" s="25">
-        <f>E7*J7+F7*K7+G7*L7+M7</f>
-        <v/>
-      </c>
-      <c r="O7" s="25">
+      <c r="P7" s="26">
+        <f>G7*L7+H7*M7+I7*N7+O7</f>
+        <v/>
+      </c>
+      <c r="Q7" s="26">
         <f>Cities!J7</f>
         <v/>
       </c>
-      <c r="P7" s="25">
+      <c r="R7" s="26">
         <f>200+C7*80</f>
         <v/>
       </c>
-      <c r="Q7" s="25">
+      <c r="S7" s="26">
         <f>350+C7*50+300+C7*30</f>
         <v/>
       </c>
-      <c r="R7" s="25">
-        <f>O7+N7+P7+Q7</f>
-        <v/>
-      </c>
-      <c r="S7" s="23">
+      <c r="T7" s="26">
+        <f>Cities!U7</f>
+        <v/>
+      </c>
+      <c r="U7" s="26">
+        <f>Cities!L7/60</f>
+        <v/>
+      </c>
+      <c r="V7" s="26">
+        <f>Q7+P7+R7+S7+T7</f>
+        <v/>
+      </c>
+      <c r="W7" s="24">
         <f>C7*Cities!F7*Cities!G7</f>
         <v/>
       </c>
-      <c r="T7" s="23">
-        <f>INT(S7*Cities!O7)</f>
-        <v/>
-      </c>
-      <c r="U7" s="23">
-        <f>INT(S7*Cities!P7)</f>
-        <v/>
-      </c>
-      <c r="V7" s="23">
-        <f>CEILING(R7/(Cities!H7*(1-Cities!I7)),1)</f>
-        <v/>
-      </c>
-      <c r="W7" s="26">
+      <c r="X7" s="24">
+        <f>INT(W7*Cities!O7)</f>
+        <v/>
+      </c>
+      <c r="Y7" s="24">
+        <f>INT(W7*Cities!P7)</f>
+        <v/>
+      </c>
+      <c r="Z7" s="24">
+        <f>CEILING((V7+U7)/AB7,1)</f>
+        <v/>
+      </c>
+      <c r="AA7" s="27">
         <f>Cities!H7*Cities!I7</f>
         <v/>
       </c>
-      <c r="X7" s="26">
-        <f>Cities!H7-W7</f>
-        <v/>
-      </c>
-      <c r="Y7" s="25">
-        <f>(U7*Cities!H7*(1-Cities!I7)-R7)*(1-I7)</f>
-        <v/>
-      </c>
-      <c r="Z7" s="25">
-        <f>FLOOR((Cities!K7+Cities!L7+Cities!M7+Cities!J7*Cities!N7)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA7" s="25">
-        <f>CEILING((Cities!K7+Cities!L7+Cities!M7+Cities!J7*Cities!N7)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB7" s="25">
-        <f>(Z7+AA7)/2</f>
-        <v/>
-      </c>
-      <c r="AC7" s="23">
-        <f>IF(Y7&gt;0,CEILING(AB7/Y7,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD7" s="27">
-        <f>IF(R7&gt;0,Y7/R7,0)</f>
-        <v/>
-      </c>
-      <c r="AE7" s="28">
-        <f>IF(V7&lt;S7*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB7" s="27">
+        <f>Cities!H7-AA7</f>
+        <v/>
+      </c>
+      <c r="AC7" s="26">
+        <f>IF((X7*AB7-V7-U7)&gt;0, (X7*AB7-V7-U7)*(1-K7), X7*AB7-V7-U7)</f>
+        <v/>
+      </c>
+      <c r="AD7" s="26">
+        <f>IF((Y7*AB7-V7-U7)&gt;0, (Y7*AB7-V7-U7)*(1-K7), Y7*AB7-V7-U7)</f>
+        <v/>
+      </c>
+      <c r="AE7" s="26">
+        <f>AC7+U7</f>
+        <v/>
+      </c>
+      <c r="AF7" s="26">
+        <f>AD7+U7</f>
+        <v/>
+      </c>
+      <c r="AG7" s="26">
+        <f>FLOOR((Cities!K7+Cities!L7+Cities!M7+Cities!T7+Cities!J7*Cities!N7)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH7" s="26">
+        <f>CEILING((Cities!K7+Cities!L7+Cities!M7+Cities!T7+Cities!J7*Cities!N7)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI7" s="26">
+        <f>(AG7+AH7)/2</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="24">
+        <f>IF(AE7*12&gt;=AI7, IF(AE7&gt;0,CEILING(AI7/AE7,1),999), IF(AF7&gt;0,12+CEILING((AI7-AE7*12)/AF7,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK7" s="28">
+        <f>IF(V7&gt;0,AD7/V7,0)</f>
+        <v/>
+      </c>
+      <c r="AL7" s="29">
+        <f>IF(Z7&lt;W7*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -4152,120 +4391,148 @@
         <f>Cities!D8</f>
         <v/>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="24">
         <f>IF(Cities!E8&lt;=750,3,IF(Cities!E8&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="24">
+        <f>C8-1</f>
+        <v/>
+      </c>
+      <c r="E8" s="24">
+        <f>C8+D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="24">
         <f>IF(C8&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E8" s="23">
+      <c r="G8" s="24">
         <f>IF(C8&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F8" s="23">
-        <f>C8-E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="23">
+      <c r="H8" s="24">
+        <f>C8-G8</f>
+        <v/>
+      </c>
+      <c r="I8" s="24">
         <f>CEILING(C8/2,1)</f>
         <v/>
       </c>
-      <c r="H8" s="23">
-        <f>E8+F8+G8+1</f>
-        <v/>
-      </c>
-      <c r="I8" s="24">
+      <c r="J8" s="24">
+        <f>G8+H8+I8+1</f>
+        <v/>
+      </c>
+      <c r="K8" s="25">
         <f>VLOOKUP(Cities!D8,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J8" s="25">
+      <c r="L8" s="26">
         <f>VLOOKUP(Cities!D8,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K8" s="25">
+      <c r="M8" s="26">
         <f>VLOOKUP(Cities!D8,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L8" s="25">
+      <c r="N8" s="26">
         <f>VLOOKUP(Cities!D8,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M8" s="25">
+      <c r="O8" s="26">
         <f>VLOOKUP(Cities!D8,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N8" s="25">
-        <f>E8*J8+F8*K8+G8*L8+M8</f>
-        <v/>
-      </c>
-      <c r="O8" s="25">
+      <c r="P8" s="26">
+        <f>G8*L8+H8*M8+I8*N8+O8</f>
+        <v/>
+      </c>
+      <c r="Q8" s="26">
         <f>Cities!J8</f>
         <v/>
       </c>
-      <c r="P8" s="25">
+      <c r="R8" s="26">
         <f>200+C8*80</f>
         <v/>
       </c>
-      <c r="Q8" s="25">
+      <c r="S8" s="26">
         <f>350+C8*50+300+C8*30</f>
         <v/>
       </c>
-      <c r="R8" s="25">
-        <f>O8+N8+P8+Q8</f>
-        <v/>
-      </c>
-      <c r="S8" s="23">
+      <c r="T8" s="26">
+        <f>Cities!U8</f>
+        <v/>
+      </c>
+      <c r="U8" s="26">
+        <f>Cities!L8/60</f>
+        <v/>
+      </c>
+      <c r="V8" s="26">
+        <f>Q8+P8+R8+S8+T8</f>
+        <v/>
+      </c>
+      <c r="W8" s="24">
         <f>C8*Cities!F8*Cities!G8</f>
         <v/>
       </c>
-      <c r="T8" s="23">
-        <f>INT(S8*Cities!O8)</f>
-        <v/>
-      </c>
-      <c r="U8" s="23">
-        <f>INT(S8*Cities!P8)</f>
-        <v/>
-      </c>
-      <c r="V8" s="23">
-        <f>CEILING(R8/(Cities!H8*(1-Cities!I8)),1)</f>
-        <v/>
-      </c>
-      <c r="W8" s="26">
+      <c r="X8" s="24">
+        <f>INT(W8*Cities!O8)</f>
+        <v/>
+      </c>
+      <c r="Y8" s="24">
+        <f>INT(W8*Cities!P8)</f>
+        <v/>
+      </c>
+      <c r="Z8" s="24">
+        <f>CEILING((V8+U8)/AB8,1)</f>
+        <v/>
+      </c>
+      <c r="AA8" s="27">
         <f>Cities!H8*Cities!I8</f>
         <v/>
       </c>
-      <c r="X8" s="26">
-        <f>Cities!H8-W8</f>
-        <v/>
-      </c>
-      <c r="Y8" s="25">
-        <f>(U8*Cities!H8*(1-Cities!I8)-R8)*(1-I8)</f>
-        <v/>
-      </c>
-      <c r="Z8" s="25">
-        <f>FLOOR((Cities!K8+Cities!L8+Cities!M8+Cities!J8*Cities!N8)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA8" s="25">
-        <f>CEILING((Cities!K8+Cities!L8+Cities!M8+Cities!J8*Cities!N8)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB8" s="25">
-        <f>(Z8+AA8)/2</f>
-        <v/>
-      </c>
-      <c r="AC8" s="23">
-        <f>IF(Y8&gt;0,CEILING(AB8/Y8,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD8" s="27">
-        <f>IF(R8&gt;0,Y8/R8,0)</f>
-        <v/>
-      </c>
-      <c r="AE8" s="28">
-        <f>IF(V8&lt;S8*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB8" s="27">
+        <f>Cities!H8-AA8</f>
+        <v/>
+      </c>
+      <c r="AC8" s="26">
+        <f>IF((X8*AB8-V8-U8)&gt;0, (X8*AB8-V8-U8)*(1-K8), X8*AB8-V8-U8)</f>
+        <v/>
+      </c>
+      <c r="AD8" s="26">
+        <f>IF((Y8*AB8-V8-U8)&gt;0, (Y8*AB8-V8-U8)*(1-K8), Y8*AB8-V8-U8)</f>
+        <v/>
+      </c>
+      <c r="AE8" s="26">
+        <f>AC8+U8</f>
+        <v/>
+      </c>
+      <c r="AF8" s="26">
+        <f>AD8+U8</f>
+        <v/>
+      </c>
+      <c r="AG8" s="26">
+        <f>FLOOR((Cities!K8+Cities!L8+Cities!M8+Cities!T8+Cities!J8*Cities!N8)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH8" s="26">
+        <f>CEILING((Cities!K8+Cities!L8+Cities!M8+Cities!T8+Cities!J8*Cities!N8)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI8" s="26">
+        <f>(AG8+AH8)/2</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="24">
+        <f>IF(AE8*12&gt;=AI8, IF(AE8&gt;0,CEILING(AI8/AE8,1),999), IF(AF8&gt;0,12+CEILING((AI8-AE8*12)/AF8,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK8" s="28">
+        <f>IF(V8&gt;0,AD8/V8,0)</f>
+        <v/>
+      </c>
+      <c r="AL8" s="29">
+        <f>IF(Z8&lt;W8*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -4278,120 +4545,148 @@
         <f>Cities!D9</f>
         <v/>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="24">
         <f>IF(Cities!E9&lt;=750,3,IF(Cities!E9&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="24">
+        <f>C9-1</f>
+        <v/>
+      </c>
+      <c r="E9" s="24">
+        <f>C9+D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="24">
         <f>IF(C9&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E9" s="23">
+      <c r="G9" s="24">
         <f>IF(C9&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F9" s="23">
-        <f>C9-E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="23">
+      <c r="H9" s="24">
+        <f>C9-G9</f>
+        <v/>
+      </c>
+      <c r="I9" s="24">
         <f>CEILING(C9/2,1)</f>
         <v/>
       </c>
-      <c r="H9" s="23">
-        <f>E9+F9+G9+1</f>
-        <v/>
-      </c>
-      <c r="I9" s="24">
+      <c r="J9" s="24">
+        <f>G9+H9+I9+1</f>
+        <v/>
+      </c>
+      <c r="K9" s="25">
         <f>VLOOKUP(Cities!D9,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J9" s="25">
+      <c r="L9" s="26">
         <f>VLOOKUP(Cities!D9,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K9" s="25">
+      <c r="M9" s="26">
         <f>VLOOKUP(Cities!D9,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L9" s="25">
+      <c r="N9" s="26">
         <f>VLOOKUP(Cities!D9,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M9" s="25">
+      <c r="O9" s="26">
         <f>VLOOKUP(Cities!D9,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N9" s="25">
-        <f>E9*J9+F9*K9+G9*L9+M9</f>
-        <v/>
-      </c>
-      <c r="O9" s="25">
+      <c r="P9" s="26">
+        <f>G9*L9+H9*M9+I9*N9+O9</f>
+        <v/>
+      </c>
+      <c r="Q9" s="26">
         <f>Cities!J9</f>
         <v/>
       </c>
-      <c r="P9" s="25">
+      <c r="R9" s="26">
         <f>200+C9*80</f>
         <v/>
       </c>
-      <c r="Q9" s="25">
+      <c r="S9" s="26">
         <f>350+C9*50+300+C9*30</f>
         <v/>
       </c>
-      <c r="R9" s="25">
-        <f>O9+N9+P9+Q9</f>
-        <v/>
-      </c>
-      <c r="S9" s="23">
+      <c r="T9" s="26">
+        <f>Cities!U9</f>
+        <v/>
+      </c>
+      <c r="U9" s="26">
+        <f>Cities!L9/60</f>
+        <v/>
+      </c>
+      <c r="V9" s="26">
+        <f>Q9+P9+R9+S9+T9</f>
+        <v/>
+      </c>
+      <c r="W9" s="24">
         <f>C9*Cities!F9*Cities!G9</f>
         <v/>
       </c>
-      <c r="T9" s="23">
-        <f>INT(S9*Cities!O9)</f>
-        <v/>
-      </c>
-      <c r="U9" s="23">
-        <f>INT(S9*Cities!P9)</f>
-        <v/>
-      </c>
-      <c r="V9" s="23">
-        <f>CEILING(R9/(Cities!H9*(1-Cities!I9)),1)</f>
-        <v/>
-      </c>
-      <c r="W9" s="26">
+      <c r="X9" s="24">
+        <f>INT(W9*Cities!O9)</f>
+        <v/>
+      </c>
+      <c r="Y9" s="24">
+        <f>INT(W9*Cities!P9)</f>
+        <v/>
+      </c>
+      <c r="Z9" s="24">
+        <f>CEILING((V9+U9)/AB9,1)</f>
+        <v/>
+      </c>
+      <c r="AA9" s="27">
         <f>Cities!H9*Cities!I9</f>
         <v/>
       </c>
-      <c r="X9" s="26">
-        <f>Cities!H9-W9</f>
-        <v/>
-      </c>
-      <c r="Y9" s="25">
-        <f>(U9*Cities!H9*(1-Cities!I9)-R9)*(1-I9)</f>
-        <v/>
-      </c>
-      <c r="Z9" s="25">
-        <f>FLOOR((Cities!K9+Cities!L9+Cities!M9+Cities!J9*Cities!N9)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA9" s="25">
-        <f>CEILING((Cities!K9+Cities!L9+Cities!M9+Cities!J9*Cities!N9)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB9" s="25">
-        <f>(Z9+AA9)/2</f>
-        <v/>
-      </c>
-      <c r="AC9" s="23">
-        <f>IF(Y9&gt;0,CEILING(AB9/Y9,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD9" s="27">
-        <f>IF(R9&gt;0,Y9/R9,0)</f>
-        <v/>
-      </c>
-      <c r="AE9" s="28">
-        <f>IF(V9&lt;S9*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB9" s="27">
+        <f>Cities!H9-AA9</f>
+        <v/>
+      </c>
+      <c r="AC9" s="26">
+        <f>IF((X9*AB9-V9-U9)&gt;0, (X9*AB9-V9-U9)*(1-K9), X9*AB9-V9-U9)</f>
+        <v/>
+      </c>
+      <c r="AD9" s="26">
+        <f>IF((Y9*AB9-V9-U9)&gt;0, (Y9*AB9-V9-U9)*(1-K9), Y9*AB9-V9-U9)</f>
+        <v/>
+      </c>
+      <c r="AE9" s="26">
+        <f>AC9+U9</f>
+        <v/>
+      </c>
+      <c r="AF9" s="26">
+        <f>AD9+U9</f>
+        <v/>
+      </c>
+      <c r="AG9" s="26">
+        <f>FLOOR((Cities!K9+Cities!L9+Cities!M9+Cities!T9+Cities!J9*Cities!N9)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH9" s="26">
+        <f>CEILING((Cities!K9+Cities!L9+Cities!M9+Cities!T9+Cities!J9*Cities!N9)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI9" s="26">
+        <f>(AG9+AH9)/2</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="24">
+        <f>IF(AE9*12&gt;=AI9, IF(AE9&gt;0,CEILING(AI9/AE9,1),999), IF(AF9&gt;0,12+CEILING((AI9-AE9*12)/AF9,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK9" s="28">
+        <f>IF(V9&gt;0,AD9/V9,0)</f>
+        <v/>
+      </c>
+      <c r="AL9" s="29">
+        <f>IF(Z9&lt;W9*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -4404,120 +4699,148 @@
         <f>Cities!D10</f>
         <v/>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="24">
         <f>IF(Cities!E10&lt;=750,3,IF(Cities!E10&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="24">
+        <f>C10-1</f>
+        <v/>
+      </c>
+      <c r="E10" s="24">
+        <f>C10+D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="24">
         <f>IF(C10&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E10" s="23">
+      <c r="G10" s="24">
         <f>IF(C10&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F10" s="23">
-        <f>C10-E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="23">
+      <c r="H10" s="24">
+        <f>C10-G10</f>
+        <v/>
+      </c>
+      <c r="I10" s="24">
         <f>CEILING(C10/2,1)</f>
         <v/>
       </c>
-      <c r="H10" s="23">
-        <f>E10+F10+G10+1</f>
-        <v/>
-      </c>
-      <c r="I10" s="24">
+      <c r="J10" s="24">
+        <f>G10+H10+I10+1</f>
+        <v/>
+      </c>
+      <c r="K10" s="25">
         <f>VLOOKUP(Cities!D10,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J10" s="25">
+      <c r="L10" s="26">
         <f>VLOOKUP(Cities!D10,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K10" s="25">
+      <c r="M10" s="26">
         <f>VLOOKUP(Cities!D10,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L10" s="25">
+      <c r="N10" s="26">
         <f>VLOOKUP(Cities!D10,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M10" s="25">
+      <c r="O10" s="26">
         <f>VLOOKUP(Cities!D10,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N10" s="25">
-        <f>E10*J10+F10*K10+G10*L10+M10</f>
-        <v/>
-      </c>
-      <c r="O10" s="25">
+      <c r="P10" s="26">
+        <f>G10*L10+H10*M10+I10*N10+O10</f>
+        <v/>
+      </c>
+      <c r="Q10" s="26">
         <f>Cities!J10</f>
         <v/>
       </c>
-      <c r="P10" s="25">
+      <c r="R10" s="26">
         <f>200+C10*80</f>
         <v/>
       </c>
-      <c r="Q10" s="25">
+      <c r="S10" s="26">
         <f>350+C10*50+300+C10*30</f>
         <v/>
       </c>
-      <c r="R10" s="25">
-        <f>O10+N10+P10+Q10</f>
-        <v/>
-      </c>
-      <c r="S10" s="23">
+      <c r="T10" s="26">
+        <f>Cities!U10</f>
+        <v/>
+      </c>
+      <c r="U10" s="26">
+        <f>Cities!L10/60</f>
+        <v/>
+      </c>
+      <c r="V10" s="26">
+        <f>Q10+P10+R10+S10+T10</f>
+        <v/>
+      </c>
+      <c r="W10" s="24">
         <f>C10*Cities!F10*Cities!G10</f>
         <v/>
       </c>
-      <c r="T10" s="23">
-        <f>INT(S10*Cities!O10)</f>
-        <v/>
-      </c>
-      <c r="U10" s="23">
-        <f>INT(S10*Cities!P10)</f>
-        <v/>
-      </c>
-      <c r="V10" s="23">
-        <f>CEILING(R10/(Cities!H10*(1-Cities!I10)),1)</f>
-        <v/>
-      </c>
-      <c r="W10" s="26">
+      <c r="X10" s="24">
+        <f>INT(W10*Cities!O10)</f>
+        <v/>
+      </c>
+      <c r="Y10" s="24">
+        <f>INT(W10*Cities!P10)</f>
+        <v/>
+      </c>
+      <c r="Z10" s="24">
+        <f>CEILING((V10+U10)/AB10,1)</f>
+        <v/>
+      </c>
+      <c r="AA10" s="27">
         <f>Cities!H10*Cities!I10</f>
         <v/>
       </c>
-      <c r="X10" s="26">
-        <f>Cities!H10-W10</f>
-        <v/>
-      </c>
-      <c r="Y10" s="25">
-        <f>(U10*Cities!H10*(1-Cities!I10)-R10)*(1-I10)</f>
-        <v/>
-      </c>
-      <c r="Z10" s="25">
-        <f>FLOOR((Cities!K10+Cities!L10+Cities!M10+Cities!J10*Cities!N10)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA10" s="25">
-        <f>CEILING((Cities!K10+Cities!L10+Cities!M10+Cities!J10*Cities!N10)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB10" s="25">
-        <f>(Z10+AA10)/2</f>
-        <v/>
-      </c>
-      <c r="AC10" s="23">
-        <f>IF(Y10&gt;0,CEILING(AB10/Y10,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD10" s="27">
-        <f>IF(R10&gt;0,Y10/R10,0)</f>
-        <v/>
-      </c>
-      <c r="AE10" s="28">
-        <f>IF(V10&lt;S10*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB10" s="27">
+        <f>Cities!H10-AA10</f>
+        <v/>
+      </c>
+      <c r="AC10" s="26">
+        <f>IF((X10*AB10-V10-U10)&gt;0, (X10*AB10-V10-U10)*(1-K10), X10*AB10-V10-U10)</f>
+        <v/>
+      </c>
+      <c r="AD10" s="26">
+        <f>IF((Y10*AB10-V10-U10)&gt;0, (Y10*AB10-V10-U10)*(1-K10), Y10*AB10-V10-U10)</f>
+        <v/>
+      </c>
+      <c r="AE10" s="26">
+        <f>AC10+U10</f>
+        <v/>
+      </c>
+      <c r="AF10" s="26">
+        <f>AD10+U10</f>
+        <v/>
+      </c>
+      <c r="AG10" s="26">
+        <f>FLOOR((Cities!K10+Cities!L10+Cities!M10+Cities!T10+Cities!J10*Cities!N10)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH10" s="26">
+        <f>CEILING((Cities!K10+Cities!L10+Cities!M10+Cities!T10+Cities!J10*Cities!N10)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI10" s="26">
+        <f>(AG10+AH10)/2</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="24">
+        <f>IF(AE10*12&gt;=AI10, IF(AE10&gt;0,CEILING(AI10/AE10,1),999), IF(AF10&gt;0,12+CEILING((AI10-AE10*12)/AF10,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK10" s="28">
+        <f>IF(V10&gt;0,AD10/V10,0)</f>
+        <v/>
+      </c>
+      <c r="AL10" s="29">
+        <f>IF(Z10&lt;W10*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -4530,120 +4853,148 @@
         <f>Cities!D11</f>
         <v/>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="24">
         <f>IF(Cities!E11&lt;=750,3,IF(Cities!E11&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="24">
+        <f>C11-1</f>
+        <v/>
+      </c>
+      <c r="E11" s="24">
+        <f>C11+D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="24">
         <f>IF(C11&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E11" s="23">
+      <c r="G11" s="24">
         <f>IF(C11&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F11" s="23">
-        <f>C11-E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="23">
+      <c r="H11" s="24">
+        <f>C11-G11</f>
+        <v/>
+      </c>
+      <c r="I11" s="24">
         <f>CEILING(C11/2,1)</f>
         <v/>
       </c>
-      <c r="H11" s="23">
-        <f>E11+F11+G11+1</f>
-        <v/>
-      </c>
-      <c r="I11" s="24">
+      <c r="J11" s="24">
+        <f>G11+H11+I11+1</f>
+        <v/>
+      </c>
+      <c r="K11" s="25">
         <f>VLOOKUP(Cities!D11,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J11" s="25">
+      <c r="L11" s="26">
         <f>VLOOKUP(Cities!D11,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K11" s="25">
+      <c r="M11" s="26">
         <f>VLOOKUP(Cities!D11,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L11" s="25">
+      <c r="N11" s="26">
         <f>VLOOKUP(Cities!D11,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M11" s="25">
+      <c r="O11" s="26">
         <f>VLOOKUP(Cities!D11,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N11" s="25">
-        <f>E11*J11+F11*K11+G11*L11+M11</f>
-        <v/>
-      </c>
-      <c r="O11" s="25">
+      <c r="P11" s="26">
+        <f>G11*L11+H11*M11+I11*N11+O11</f>
+        <v/>
+      </c>
+      <c r="Q11" s="26">
         <f>Cities!J11</f>
         <v/>
       </c>
-      <c r="P11" s="25">
+      <c r="R11" s="26">
         <f>200+C11*80</f>
         <v/>
       </c>
-      <c r="Q11" s="25">
+      <c r="S11" s="26">
         <f>350+C11*50+300+C11*30</f>
         <v/>
       </c>
-      <c r="R11" s="25">
-        <f>O11+N11+P11+Q11</f>
-        <v/>
-      </c>
-      <c r="S11" s="23">
+      <c r="T11" s="26">
+        <f>Cities!U11</f>
+        <v/>
+      </c>
+      <c r="U11" s="26">
+        <f>Cities!L11/60</f>
+        <v/>
+      </c>
+      <c r="V11" s="26">
+        <f>Q11+P11+R11+S11+T11</f>
+        <v/>
+      </c>
+      <c r="W11" s="24">
         <f>C11*Cities!F11*Cities!G11</f>
         <v/>
       </c>
-      <c r="T11" s="23">
-        <f>INT(S11*Cities!O11)</f>
-        <v/>
-      </c>
-      <c r="U11" s="23">
-        <f>INT(S11*Cities!P11)</f>
-        <v/>
-      </c>
-      <c r="V11" s="23">
-        <f>CEILING(R11/(Cities!H11*(1-Cities!I11)),1)</f>
-        <v/>
-      </c>
-      <c r="W11" s="26">
+      <c r="X11" s="24">
+        <f>INT(W11*Cities!O11)</f>
+        <v/>
+      </c>
+      <c r="Y11" s="24">
+        <f>INT(W11*Cities!P11)</f>
+        <v/>
+      </c>
+      <c r="Z11" s="24">
+        <f>CEILING((V11+U11)/AB11,1)</f>
+        <v/>
+      </c>
+      <c r="AA11" s="27">
         <f>Cities!H11*Cities!I11</f>
         <v/>
       </c>
-      <c r="X11" s="26">
-        <f>Cities!H11-W11</f>
-        <v/>
-      </c>
-      <c r="Y11" s="25">
-        <f>(U11*Cities!H11*(1-Cities!I11)-R11)*(1-I11)</f>
-        <v/>
-      </c>
-      <c r="Z11" s="25">
-        <f>FLOOR((Cities!K11+Cities!L11+Cities!M11+Cities!J11*Cities!N11)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA11" s="25">
-        <f>CEILING((Cities!K11+Cities!L11+Cities!M11+Cities!J11*Cities!N11)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB11" s="25">
-        <f>(Z11+AA11)/2</f>
-        <v/>
-      </c>
-      <c r="AC11" s="23">
-        <f>IF(Y11&gt;0,CEILING(AB11/Y11,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD11" s="27">
-        <f>IF(R11&gt;0,Y11/R11,0)</f>
-        <v/>
-      </c>
-      <c r="AE11" s="28">
-        <f>IF(V11&lt;S11*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB11" s="27">
+        <f>Cities!H11-AA11</f>
+        <v/>
+      </c>
+      <c r="AC11" s="26">
+        <f>IF((X11*AB11-V11-U11)&gt;0, (X11*AB11-V11-U11)*(1-K11), X11*AB11-V11-U11)</f>
+        <v/>
+      </c>
+      <c r="AD11" s="26">
+        <f>IF((Y11*AB11-V11-U11)&gt;0, (Y11*AB11-V11-U11)*(1-K11), Y11*AB11-V11-U11)</f>
+        <v/>
+      </c>
+      <c r="AE11" s="26">
+        <f>AC11+U11</f>
+        <v/>
+      </c>
+      <c r="AF11" s="26">
+        <f>AD11+U11</f>
+        <v/>
+      </c>
+      <c r="AG11" s="26">
+        <f>FLOOR((Cities!K11+Cities!L11+Cities!M11+Cities!T11+Cities!J11*Cities!N11)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH11" s="26">
+        <f>CEILING((Cities!K11+Cities!L11+Cities!M11+Cities!T11+Cities!J11*Cities!N11)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI11" s="26">
+        <f>(AG11+AH11)/2</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="24">
+        <f>IF(AE11*12&gt;=AI11, IF(AE11&gt;0,CEILING(AI11/AE11,1),999), IF(AF11&gt;0,12+CEILING((AI11-AE11*12)/AF11,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK11" s="28">
+        <f>IF(V11&gt;0,AD11/V11,0)</f>
+        <v/>
+      </c>
+      <c r="AL11" s="29">
+        <f>IF(Z11&lt;W11*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -4656,120 +5007,148 @@
         <f>Cities!D12</f>
         <v/>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="24">
         <f>IF(Cities!E12&lt;=750,3,IF(Cities!E12&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="24">
+        <f>C12-1</f>
+        <v/>
+      </c>
+      <c r="E12" s="24">
+        <f>C12+D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="24">
         <f>IF(C12&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E12" s="23">
+      <c r="G12" s="24">
         <f>IF(C12&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F12" s="23">
-        <f>C12-E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="23">
+      <c r="H12" s="24">
+        <f>C12-G12</f>
+        <v/>
+      </c>
+      <c r="I12" s="24">
         <f>CEILING(C12/2,1)</f>
         <v/>
       </c>
-      <c r="H12" s="23">
-        <f>E12+F12+G12+1</f>
-        <v/>
-      </c>
-      <c r="I12" s="24">
+      <c r="J12" s="24">
+        <f>G12+H12+I12+1</f>
+        <v/>
+      </c>
+      <c r="K12" s="25">
         <f>VLOOKUP(Cities!D12,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J12" s="25">
+      <c r="L12" s="26">
         <f>VLOOKUP(Cities!D12,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K12" s="25">
+      <c r="M12" s="26">
         <f>VLOOKUP(Cities!D12,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L12" s="25">
+      <c r="N12" s="26">
         <f>VLOOKUP(Cities!D12,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M12" s="25">
+      <c r="O12" s="26">
         <f>VLOOKUP(Cities!D12,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N12" s="25">
-        <f>E12*J12+F12*K12+G12*L12+M12</f>
-        <v/>
-      </c>
-      <c r="O12" s="25">
+      <c r="P12" s="26">
+        <f>G12*L12+H12*M12+I12*N12+O12</f>
+        <v/>
+      </c>
+      <c r="Q12" s="26">
         <f>Cities!J12</f>
         <v/>
       </c>
-      <c r="P12" s="25">
+      <c r="R12" s="26">
         <f>200+C12*80</f>
         <v/>
       </c>
-      <c r="Q12" s="25">
+      <c r="S12" s="26">
         <f>350+C12*50+300+C12*30</f>
         <v/>
       </c>
-      <c r="R12" s="25">
-        <f>O12+N12+P12+Q12</f>
-        <v/>
-      </c>
-      <c r="S12" s="23">
+      <c r="T12" s="26">
+        <f>Cities!U12</f>
+        <v/>
+      </c>
+      <c r="U12" s="26">
+        <f>Cities!L12/60</f>
+        <v/>
+      </c>
+      <c r="V12" s="26">
+        <f>Q12+P12+R12+S12+T12</f>
+        <v/>
+      </c>
+      <c r="W12" s="24">
         <f>C12*Cities!F12*Cities!G12</f>
         <v/>
       </c>
-      <c r="T12" s="23">
-        <f>INT(S12*Cities!O12)</f>
-        <v/>
-      </c>
-      <c r="U12" s="23">
-        <f>INT(S12*Cities!P12)</f>
-        <v/>
-      </c>
-      <c r="V12" s="23">
-        <f>CEILING(R12/(Cities!H12*(1-Cities!I12)),1)</f>
-        <v/>
-      </c>
-      <c r="W12" s="26">
+      <c r="X12" s="24">
+        <f>INT(W12*Cities!O12)</f>
+        <v/>
+      </c>
+      <c r="Y12" s="24">
+        <f>INT(W12*Cities!P12)</f>
+        <v/>
+      </c>
+      <c r="Z12" s="24">
+        <f>CEILING((V12+U12)/AB12,1)</f>
+        <v/>
+      </c>
+      <c r="AA12" s="27">
         <f>Cities!H12*Cities!I12</f>
         <v/>
       </c>
-      <c r="X12" s="26">
-        <f>Cities!H12-W12</f>
-        <v/>
-      </c>
-      <c r="Y12" s="25">
-        <f>(U12*Cities!H12*(1-Cities!I12)-R12)*(1-I12)</f>
-        <v/>
-      </c>
-      <c r="Z12" s="25">
-        <f>FLOOR((Cities!K12+Cities!L12+Cities!M12+Cities!J12*Cities!N12)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA12" s="25">
-        <f>CEILING((Cities!K12+Cities!L12+Cities!M12+Cities!J12*Cities!N12)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB12" s="25">
-        <f>(Z12+AA12)/2</f>
-        <v/>
-      </c>
-      <c r="AC12" s="23">
-        <f>IF(Y12&gt;0,CEILING(AB12/Y12,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD12" s="27">
-        <f>IF(R12&gt;0,Y12/R12,0)</f>
-        <v/>
-      </c>
-      <c r="AE12" s="28">
-        <f>IF(V12&lt;S12*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB12" s="27">
+        <f>Cities!H12-AA12</f>
+        <v/>
+      </c>
+      <c r="AC12" s="26">
+        <f>IF((X12*AB12-V12-U12)&gt;0, (X12*AB12-V12-U12)*(1-K12), X12*AB12-V12-U12)</f>
+        <v/>
+      </c>
+      <c r="AD12" s="26">
+        <f>IF((Y12*AB12-V12-U12)&gt;0, (Y12*AB12-V12-U12)*(1-K12), Y12*AB12-V12-U12)</f>
+        <v/>
+      </c>
+      <c r="AE12" s="26">
+        <f>AC12+U12</f>
+        <v/>
+      </c>
+      <c r="AF12" s="26">
+        <f>AD12+U12</f>
+        <v/>
+      </c>
+      <c r="AG12" s="26">
+        <f>FLOOR((Cities!K12+Cities!L12+Cities!M12+Cities!T12+Cities!J12*Cities!N12)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH12" s="26">
+        <f>CEILING((Cities!K12+Cities!L12+Cities!M12+Cities!T12+Cities!J12*Cities!N12)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI12" s="26">
+        <f>(AG12+AH12)/2</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="24">
+        <f>IF(AE12*12&gt;=AI12, IF(AE12&gt;0,CEILING(AI12/AE12,1),999), IF(AF12&gt;0,12+CEILING((AI12-AE12*12)/AF12,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK12" s="28">
+        <f>IF(V12&gt;0,AD12/V12,0)</f>
+        <v/>
+      </c>
+      <c r="AL12" s="29">
+        <f>IF(Z12&lt;W12*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -4782,120 +5161,148 @@
         <f>Cities!D13</f>
         <v/>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="24">
         <f>IF(Cities!E13&lt;=750,3,IF(Cities!E13&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="24">
+        <f>C13-1</f>
+        <v/>
+      </c>
+      <c r="E13" s="24">
+        <f>C13+D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="24">
         <f>IF(C13&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E13" s="23">
+      <c r="G13" s="24">
         <f>IF(C13&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F13" s="23">
-        <f>C13-E13</f>
-        <v/>
-      </c>
-      <c r="G13" s="23">
+      <c r="H13" s="24">
+        <f>C13-G13</f>
+        <v/>
+      </c>
+      <c r="I13" s="24">
         <f>CEILING(C13/2,1)</f>
         <v/>
       </c>
-      <c r="H13" s="23">
-        <f>E13+F13+G13+1</f>
-        <v/>
-      </c>
-      <c r="I13" s="24">
+      <c r="J13" s="24">
+        <f>G13+H13+I13+1</f>
+        <v/>
+      </c>
+      <c r="K13" s="25">
         <f>VLOOKUP(Cities!D13,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J13" s="25">
+      <c r="L13" s="26">
         <f>VLOOKUP(Cities!D13,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K13" s="25">
+      <c r="M13" s="26">
         <f>VLOOKUP(Cities!D13,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L13" s="25">
+      <c r="N13" s="26">
         <f>VLOOKUP(Cities!D13,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M13" s="25">
+      <c r="O13" s="26">
         <f>VLOOKUP(Cities!D13,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N13" s="25">
-        <f>E13*J13+F13*K13+G13*L13+M13</f>
-        <v/>
-      </c>
-      <c r="O13" s="25">
+      <c r="P13" s="26">
+        <f>G13*L13+H13*M13+I13*N13+O13</f>
+        <v/>
+      </c>
+      <c r="Q13" s="26">
         <f>Cities!J13</f>
         <v/>
       </c>
-      <c r="P13" s="25">
+      <c r="R13" s="26">
         <f>200+C13*80</f>
         <v/>
       </c>
-      <c r="Q13" s="25">
+      <c r="S13" s="26">
         <f>350+C13*50+300+C13*30</f>
         <v/>
       </c>
-      <c r="R13" s="25">
-        <f>O13+N13+P13+Q13</f>
-        <v/>
-      </c>
-      <c r="S13" s="23">
+      <c r="T13" s="26">
+        <f>Cities!U13</f>
+        <v/>
+      </c>
+      <c r="U13" s="26">
+        <f>Cities!L13/60</f>
+        <v/>
+      </c>
+      <c r="V13" s="26">
+        <f>Q13+P13+R13+S13+T13</f>
+        <v/>
+      </c>
+      <c r="W13" s="24">
         <f>C13*Cities!F13*Cities!G13</f>
         <v/>
       </c>
-      <c r="T13" s="23">
-        <f>INT(S13*Cities!O13)</f>
-        <v/>
-      </c>
-      <c r="U13" s="23">
-        <f>INT(S13*Cities!P13)</f>
-        <v/>
-      </c>
-      <c r="V13" s="23">
-        <f>CEILING(R13/(Cities!H13*(1-Cities!I13)),1)</f>
-        <v/>
-      </c>
-      <c r="W13" s="26">
+      <c r="X13" s="24">
+        <f>INT(W13*Cities!O13)</f>
+        <v/>
+      </c>
+      <c r="Y13" s="24">
+        <f>INT(W13*Cities!P13)</f>
+        <v/>
+      </c>
+      <c r="Z13" s="24">
+        <f>CEILING((V13+U13)/AB13,1)</f>
+        <v/>
+      </c>
+      <c r="AA13" s="27">
         <f>Cities!H13*Cities!I13</f>
         <v/>
       </c>
-      <c r="X13" s="26">
-        <f>Cities!H13-W13</f>
-        <v/>
-      </c>
-      <c r="Y13" s="25">
-        <f>(U13*Cities!H13*(1-Cities!I13)-R13)*(1-I13)</f>
-        <v/>
-      </c>
-      <c r="Z13" s="25">
-        <f>FLOOR((Cities!K13+Cities!L13+Cities!M13+Cities!J13*Cities!N13)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA13" s="25">
-        <f>CEILING((Cities!K13+Cities!L13+Cities!M13+Cities!J13*Cities!N13)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB13" s="25">
-        <f>(Z13+AA13)/2</f>
-        <v/>
-      </c>
-      <c r="AC13" s="23">
-        <f>IF(Y13&gt;0,CEILING(AB13/Y13,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD13" s="27">
-        <f>IF(R13&gt;0,Y13/R13,0)</f>
-        <v/>
-      </c>
-      <c r="AE13" s="28">
-        <f>IF(V13&lt;S13*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB13" s="27">
+        <f>Cities!H13-AA13</f>
+        <v/>
+      </c>
+      <c r="AC13" s="26">
+        <f>IF((X13*AB13-V13-U13)&gt;0, (X13*AB13-V13-U13)*(1-K13), X13*AB13-V13-U13)</f>
+        <v/>
+      </c>
+      <c r="AD13" s="26">
+        <f>IF((Y13*AB13-V13-U13)&gt;0, (Y13*AB13-V13-U13)*(1-K13), Y13*AB13-V13-U13)</f>
+        <v/>
+      </c>
+      <c r="AE13" s="26">
+        <f>AC13+U13</f>
+        <v/>
+      </c>
+      <c r="AF13" s="26">
+        <f>AD13+U13</f>
+        <v/>
+      </c>
+      <c r="AG13" s="26">
+        <f>FLOOR((Cities!K13+Cities!L13+Cities!M13+Cities!T13+Cities!J13*Cities!N13)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH13" s="26">
+        <f>CEILING((Cities!K13+Cities!L13+Cities!M13+Cities!T13+Cities!J13*Cities!N13)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI13" s="26">
+        <f>(AG13+AH13)/2</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="24">
+        <f>IF(AE13*12&gt;=AI13, IF(AE13&gt;0,CEILING(AI13/AE13,1),999), IF(AF13&gt;0,12+CEILING((AI13-AE13*12)/AF13,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK13" s="28">
+        <f>IF(V13&gt;0,AD13/V13,0)</f>
+        <v/>
+      </c>
+      <c r="AL13" s="29">
+        <f>IF(Z13&lt;W13*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -4908,120 +5315,148 @@
         <f>Cities!D14</f>
         <v/>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="24">
         <f>IF(Cities!E14&lt;=750,3,IF(Cities!E14&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="24">
+        <f>C14-1</f>
+        <v/>
+      </c>
+      <c r="E14" s="24">
+        <f>C14+D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="24">
         <f>IF(C14&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E14" s="23">
+      <c r="G14" s="24">
         <f>IF(C14&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F14" s="23">
-        <f>C14-E14</f>
-        <v/>
-      </c>
-      <c r="G14" s="23">
+      <c r="H14" s="24">
+        <f>C14-G14</f>
+        <v/>
+      </c>
+      <c r="I14" s="24">
         <f>CEILING(C14/2,1)</f>
         <v/>
       </c>
-      <c r="H14" s="23">
-        <f>E14+F14+G14+1</f>
-        <v/>
-      </c>
-      <c r="I14" s="24">
+      <c r="J14" s="24">
+        <f>G14+H14+I14+1</f>
+        <v/>
+      </c>
+      <c r="K14" s="25">
         <f>VLOOKUP(Cities!D14,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J14" s="25">
+      <c r="L14" s="26">
         <f>VLOOKUP(Cities!D14,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K14" s="25">
+      <c r="M14" s="26">
         <f>VLOOKUP(Cities!D14,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L14" s="25">
+      <c r="N14" s="26">
         <f>VLOOKUP(Cities!D14,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M14" s="25">
+      <c r="O14" s="26">
         <f>VLOOKUP(Cities!D14,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N14" s="25">
-        <f>E14*J14+F14*K14+G14*L14+M14</f>
-        <v/>
-      </c>
-      <c r="O14" s="25">
+      <c r="P14" s="26">
+        <f>G14*L14+H14*M14+I14*N14+O14</f>
+        <v/>
+      </c>
+      <c r="Q14" s="26">
         <f>Cities!J14</f>
         <v/>
       </c>
-      <c r="P14" s="25">
+      <c r="R14" s="26">
         <f>200+C14*80</f>
         <v/>
       </c>
-      <c r="Q14" s="25">
+      <c r="S14" s="26">
         <f>350+C14*50+300+C14*30</f>
         <v/>
       </c>
-      <c r="R14" s="25">
-        <f>O14+N14+P14+Q14</f>
-        <v/>
-      </c>
-      <c r="S14" s="23">
+      <c r="T14" s="26">
+        <f>Cities!U14</f>
+        <v/>
+      </c>
+      <c r="U14" s="26">
+        <f>Cities!L14/60</f>
+        <v/>
+      </c>
+      <c r="V14" s="26">
+        <f>Q14+P14+R14+S14+T14</f>
+        <v/>
+      </c>
+      <c r="W14" s="24">
         <f>C14*Cities!F14*Cities!G14</f>
         <v/>
       </c>
-      <c r="T14" s="23">
-        <f>INT(S14*Cities!O14)</f>
-        <v/>
-      </c>
-      <c r="U14" s="23">
-        <f>INT(S14*Cities!P14)</f>
-        <v/>
-      </c>
-      <c r="V14" s="23">
-        <f>CEILING(R14/(Cities!H14*(1-Cities!I14)),1)</f>
-        <v/>
-      </c>
-      <c r="W14" s="26">
+      <c r="X14" s="24">
+        <f>INT(W14*Cities!O14)</f>
+        <v/>
+      </c>
+      <c r="Y14" s="24">
+        <f>INT(W14*Cities!P14)</f>
+        <v/>
+      </c>
+      <c r="Z14" s="24">
+        <f>CEILING((V14+U14)/AB14,1)</f>
+        <v/>
+      </c>
+      <c r="AA14" s="27">
         <f>Cities!H14*Cities!I14</f>
         <v/>
       </c>
-      <c r="X14" s="26">
-        <f>Cities!H14-W14</f>
-        <v/>
-      </c>
-      <c r="Y14" s="25">
-        <f>(U14*Cities!H14*(1-Cities!I14)-R14)*(1-I14)</f>
-        <v/>
-      </c>
-      <c r="Z14" s="25">
-        <f>FLOOR((Cities!K14+Cities!L14+Cities!M14+Cities!J14*Cities!N14)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA14" s="25">
-        <f>CEILING((Cities!K14+Cities!L14+Cities!M14+Cities!J14*Cities!N14)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB14" s="25">
-        <f>(Z14+AA14)/2</f>
-        <v/>
-      </c>
-      <c r="AC14" s="23">
-        <f>IF(Y14&gt;0,CEILING(AB14/Y14,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD14" s="27">
-        <f>IF(R14&gt;0,Y14/R14,0)</f>
-        <v/>
-      </c>
-      <c r="AE14" s="28">
-        <f>IF(V14&lt;S14*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB14" s="27">
+        <f>Cities!H14-AA14</f>
+        <v/>
+      </c>
+      <c r="AC14" s="26">
+        <f>IF((X14*AB14-V14-U14)&gt;0, (X14*AB14-V14-U14)*(1-K14), X14*AB14-V14-U14)</f>
+        <v/>
+      </c>
+      <c r="AD14" s="26">
+        <f>IF((Y14*AB14-V14-U14)&gt;0, (Y14*AB14-V14-U14)*(1-K14), Y14*AB14-V14-U14)</f>
+        <v/>
+      </c>
+      <c r="AE14" s="26">
+        <f>AC14+U14</f>
+        <v/>
+      </c>
+      <c r="AF14" s="26">
+        <f>AD14+U14</f>
+        <v/>
+      </c>
+      <c r="AG14" s="26">
+        <f>FLOOR((Cities!K14+Cities!L14+Cities!M14+Cities!T14+Cities!J14*Cities!N14)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH14" s="26">
+        <f>CEILING((Cities!K14+Cities!L14+Cities!M14+Cities!T14+Cities!J14*Cities!N14)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI14" s="26">
+        <f>(AG14+AH14)/2</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="24">
+        <f>IF(AE14*12&gt;=AI14, IF(AE14&gt;0,CEILING(AI14/AE14,1),999), IF(AF14&gt;0,12+CEILING((AI14-AE14*12)/AF14,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK14" s="28">
+        <f>IF(V14&gt;0,AD14/V14,0)</f>
+        <v/>
+      </c>
+      <c r="AL14" s="29">
+        <f>IF(Z14&lt;W14*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -5034,120 +5469,148 @@
         <f>Cities!D15</f>
         <v/>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="24">
         <f>IF(Cities!E15&lt;=750,3,IF(Cities!E15&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="24">
+        <f>C15-1</f>
+        <v/>
+      </c>
+      <c r="E15" s="24">
+        <f>C15+D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="24">
         <f>IF(C15&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E15" s="23">
+      <c r="G15" s="24">
         <f>IF(C15&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F15" s="23">
-        <f>C15-E15</f>
-        <v/>
-      </c>
-      <c r="G15" s="23">
+      <c r="H15" s="24">
+        <f>C15-G15</f>
+        <v/>
+      </c>
+      <c r="I15" s="24">
         <f>CEILING(C15/2,1)</f>
         <v/>
       </c>
-      <c r="H15" s="23">
-        <f>E15+F15+G15+1</f>
-        <v/>
-      </c>
-      <c r="I15" s="24">
+      <c r="J15" s="24">
+        <f>G15+H15+I15+1</f>
+        <v/>
+      </c>
+      <c r="K15" s="25">
         <f>VLOOKUP(Cities!D15,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J15" s="25">
+      <c r="L15" s="26">
         <f>VLOOKUP(Cities!D15,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K15" s="25">
+      <c r="M15" s="26">
         <f>VLOOKUP(Cities!D15,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L15" s="25">
+      <c r="N15" s="26">
         <f>VLOOKUP(Cities!D15,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M15" s="25">
+      <c r="O15" s="26">
         <f>VLOOKUP(Cities!D15,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N15" s="25">
-        <f>E15*J15+F15*K15+G15*L15+M15</f>
-        <v/>
-      </c>
-      <c r="O15" s="25">
+      <c r="P15" s="26">
+        <f>G15*L15+H15*M15+I15*N15+O15</f>
+        <v/>
+      </c>
+      <c r="Q15" s="26">
         <f>Cities!J15</f>
         <v/>
       </c>
-      <c r="P15" s="25">
+      <c r="R15" s="26">
         <f>200+C15*80</f>
         <v/>
       </c>
-      <c r="Q15" s="25">
+      <c r="S15" s="26">
         <f>350+C15*50+300+C15*30</f>
         <v/>
       </c>
-      <c r="R15" s="25">
-        <f>O15+N15+P15+Q15</f>
-        <v/>
-      </c>
-      <c r="S15" s="23">
+      <c r="T15" s="26">
+        <f>Cities!U15</f>
+        <v/>
+      </c>
+      <c r="U15" s="26">
+        <f>Cities!L15/60</f>
+        <v/>
+      </c>
+      <c r="V15" s="26">
+        <f>Q15+P15+R15+S15+T15</f>
+        <v/>
+      </c>
+      <c r="W15" s="24">
         <f>C15*Cities!F15*Cities!G15</f>
         <v/>
       </c>
-      <c r="T15" s="23">
-        <f>INT(S15*Cities!O15)</f>
-        <v/>
-      </c>
-      <c r="U15" s="23">
-        <f>INT(S15*Cities!P15)</f>
-        <v/>
-      </c>
-      <c r="V15" s="23">
-        <f>CEILING(R15/(Cities!H15*(1-Cities!I15)),1)</f>
-        <v/>
-      </c>
-      <c r="W15" s="26">
+      <c r="X15" s="24">
+        <f>INT(W15*Cities!O15)</f>
+        <v/>
+      </c>
+      <c r="Y15" s="24">
+        <f>INT(W15*Cities!P15)</f>
+        <v/>
+      </c>
+      <c r="Z15" s="24">
+        <f>CEILING((V15+U15)/AB15,1)</f>
+        <v/>
+      </c>
+      <c r="AA15" s="27">
         <f>Cities!H15*Cities!I15</f>
         <v/>
       </c>
-      <c r="X15" s="26">
-        <f>Cities!H15-W15</f>
-        <v/>
-      </c>
-      <c r="Y15" s="25">
-        <f>(U15*Cities!H15*(1-Cities!I15)-R15)*(1-I15)</f>
-        <v/>
-      </c>
-      <c r="Z15" s="25">
-        <f>FLOOR((Cities!K15+Cities!L15+Cities!M15+Cities!J15*Cities!N15)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA15" s="25">
-        <f>CEILING((Cities!K15+Cities!L15+Cities!M15+Cities!J15*Cities!N15)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB15" s="25">
-        <f>(Z15+AA15)/2</f>
-        <v/>
-      </c>
-      <c r="AC15" s="23">
-        <f>IF(Y15&gt;0,CEILING(AB15/Y15,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD15" s="27">
-        <f>IF(R15&gt;0,Y15/R15,0)</f>
-        <v/>
-      </c>
-      <c r="AE15" s="28">
-        <f>IF(V15&lt;S15*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB15" s="27">
+        <f>Cities!H15-AA15</f>
+        <v/>
+      </c>
+      <c r="AC15" s="26">
+        <f>IF((X15*AB15-V15-U15)&gt;0, (X15*AB15-V15-U15)*(1-K15), X15*AB15-V15-U15)</f>
+        <v/>
+      </c>
+      <c r="AD15" s="26">
+        <f>IF((Y15*AB15-V15-U15)&gt;0, (Y15*AB15-V15-U15)*(1-K15), Y15*AB15-V15-U15)</f>
+        <v/>
+      </c>
+      <c r="AE15" s="26">
+        <f>AC15+U15</f>
+        <v/>
+      </c>
+      <c r="AF15" s="26">
+        <f>AD15+U15</f>
+        <v/>
+      </c>
+      <c r="AG15" s="26">
+        <f>FLOOR((Cities!K15+Cities!L15+Cities!M15+Cities!T15+Cities!J15*Cities!N15)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH15" s="26">
+        <f>CEILING((Cities!K15+Cities!L15+Cities!M15+Cities!T15+Cities!J15*Cities!N15)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI15" s="26">
+        <f>(AG15+AH15)/2</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="24">
+        <f>IF(AE15*12&gt;=AI15, IF(AE15&gt;0,CEILING(AI15/AE15,1),999), IF(AF15&gt;0,12+CEILING((AI15-AE15*12)/AF15,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK15" s="28">
+        <f>IF(V15&gt;0,AD15/V15,0)</f>
+        <v/>
+      </c>
+      <c r="AL15" s="29">
+        <f>IF(Z15&lt;W15*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -5160,120 +5623,148 @@
         <f>Cities!D16</f>
         <v/>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="24">
         <f>IF(Cities!E16&lt;=750,3,IF(Cities!E16&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="24">
+        <f>C16-1</f>
+        <v/>
+      </c>
+      <c r="E16" s="24">
+        <f>C16+D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="24">
         <f>IF(C16&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E16" s="23">
+      <c r="G16" s="24">
         <f>IF(C16&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F16" s="23">
-        <f>C16-E16</f>
-        <v/>
-      </c>
-      <c r="G16" s="23">
+      <c r="H16" s="24">
+        <f>C16-G16</f>
+        <v/>
+      </c>
+      <c r="I16" s="24">
         <f>CEILING(C16/2,1)</f>
         <v/>
       </c>
-      <c r="H16" s="23">
-        <f>E16+F16+G16+1</f>
-        <v/>
-      </c>
-      <c r="I16" s="24">
+      <c r="J16" s="24">
+        <f>G16+H16+I16+1</f>
+        <v/>
+      </c>
+      <c r="K16" s="25">
         <f>VLOOKUP(Cities!D16,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J16" s="25">
+      <c r="L16" s="26">
         <f>VLOOKUP(Cities!D16,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K16" s="25">
+      <c r="M16" s="26">
         <f>VLOOKUP(Cities!D16,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L16" s="25">
+      <c r="N16" s="26">
         <f>VLOOKUP(Cities!D16,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M16" s="25">
+      <c r="O16" s="26">
         <f>VLOOKUP(Cities!D16,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N16" s="25">
-        <f>E16*J16+F16*K16+G16*L16+M16</f>
-        <v/>
-      </c>
-      <c r="O16" s="25">
+      <c r="P16" s="26">
+        <f>G16*L16+H16*M16+I16*N16+O16</f>
+        <v/>
+      </c>
+      <c r="Q16" s="26">
         <f>Cities!J16</f>
         <v/>
       </c>
-      <c r="P16" s="25">
+      <c r="R16" s="26">
         <f>200+C16*80</f>
         <v/>
       </c>
-      <c r="Q16" s="25">
+      <c r="S16" s="26">
         <f>350+C16*50+300+C16*30</f>
         <v/>
       </c>
-      <c r="R16" s="25">
-        <f>O16+N16+P16+Q16</f>
-        <v/>
-      </c>
-      <c r="S16" s="23">
+      <c r="T16" s="26">
+        <f>Cities!U16</f>
+        <v/>
+      </c>
+      <c r="U16" s="26">
+        <f>Cities!L16/60</f>
+        <v/>
+      </c>
+      <c r="V16" s="26">
+        <f>Q16+P16+R16+S16+T16</f>
+        <v/>
+      </c>
+      <c r="W16" s="24">
         <f>C16*Cities!F16*Cities!G16</f>
         <v/>
       </c>
-      <c r="T16" s="23">
-        <f>INT(S16*Cities!O16)</f>
-        <v/>
-      </c>
-      <c r="U16" s="23">
-        <f>INT(S16*Cities!P16)</f>
-        <v/>
-      </c>
-      <c r="V16" s="23">
-        <f>CEILING(R16/(Cities!H16*(1-Cities!I16)),1)</f>
-        <v/>
-      </c>
-      <c r="W16" s="26">
+      <c r="X16" s="24">
+        <f>INT(W16*Cities!O16)</f>
+        <v/>
+      </c>
+      <c r="Y16" s="24">
+        <f>INT(W16*Cities!P16)</f>
+        <v/>
+      </c>
+      <c r="Z16" s="24">
+        <f>CEILING((V16+U16)/AB16,1)</f>
+        <v/>
+      </c>
+      <c r="AA16" s="27">
         <f>Cities!H16*Cities!I16</f>
         <v/>
       </c>
-      <c r="X16" s="26">
-        <f>Cities!H16-W16</f>
-        <v/>
-      </c>
-      <c r="Y16" s="25">
-        <f>(U16*Cities!H16*(1-Cities!I16)-R16)*(1-I16)</f>
-        <v/>
-      </c>
-      <c r="Z16" s="25">
-        <f>FLOOR((Cities!K16+Cities!L16+Cities!M16+Cities!J16*Cities!N16)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA16" s="25">
-        <f>CEILING((Cities!K16+Cities!L16+Cities!M16+Cities!J16*Cities!N16)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB16" s="25">
-        <f>(Z16+AA16)/2</f>
-        <v/>
-      </c>
-      <c r="AC16" s="23">
-        <f>IF(Y16&gt;0,CEILING(AB16/Y16,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD16" s="27">
-        <f>IF(R16&gt;0,Y16/R16,0)</f>
-        <v/>
-      </c>
-      <c r="AE16" s="28">
-        <f>IF(V16&lt;S16*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB16" s="27">
+        <f>Cities!H16-AA16</f>
+        <v/>
+      </c>
+      <c r="AC16" s="26">
+        <f>IF((X16*AB16-V16-U16)&gt;0, (X16*AB16-V16-U16)*(1-K16), X16*AB16-V16-U16)</f>
+        <v/>
+      </c>
+      <c r="AD16" s="26">
+        <f>IF((Y16*AB16-V16-U16)&gt;0, (Y16*AB16-V16-U16)*(1-K16), Y16*AB16-V16-U16)</f>
+        <v/>
+      </c>
+      <c r="AE16" s="26">
+        <f>AC16+U16</f>
+        <v/>
+      </c>
+      <c r="AF16" s="26">
+        <f>AD16+U16</f>
+        <v/>
+      </c>
+      <c r="AG16" s="26">
+        <f>FLOOR((Cities!K16+Cities!L16+Cities!M16+Cities!T16+Cities!J16*Cities!N16)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH16" s="26">
+        <f>CEILING((Cities!K16+Cities!L16+Cities!M16+Cities!T16+Cities!J16*Cities!N16)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI16" s="26">
+        <f>(AG16+AH16)/2</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="24">
+        <f>IF(AE16*12&gt;=AI16, IF(AE16&gt;0,CEILING(AI16/AE16,1),999), IF(AF16&gt;0,12+CEILING((AI16-AE16*12)/AF16,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK16" s="28">
+        <f>IF(V16&gt;0,AD16/V16,0)</f>
+        <v/>
+      </c>
+      <c r="AL16" s="29">
+        <f>IF(Z16&lt;W16*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -5286,120 +5777,148 @@
         <f>Cities!D17</f>
         <v/>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="24">
         <f>IF(Cities!E17&lt;=750,3,IF(Cities!E17&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="24">
+        <f>C17-1</f>
+        <v/>
+      </c>
+      <c r="E17" s="24">
+        <f>C17+D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="24">
         <f>IF(C17&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E17" s="23">
+      <c r="G17" s="24">
         <f>IF(C17&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F17" s="23">
-        <f>C17-E17</f>
-        <v/>
-      </c>
-      <c r="G17" s="23">
+      <c r="H17" s="24">
+        <f>C17-G17</f>
+        <v/>
+      </c>
+      <c r="I17" s="24">
         <f>CEILING(C17/2,1)</f>
         <v/>
       </c>
-      <c r="H17" s="23">
-        <f>E17+F17+G17+1</f>
-        <v/>
-      </c>
-      <c r="I17" s="24">
+      <c r="J17" s="24">
+        <f>G17+H17+I17+1</f>
+        <v/>
+      </c>
+      <c r="K17" s="25">
         <f>VLOOKUP(Cities!D17,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J17" s="25">
+      <c r="L17" s="26">
         <f>VLOOKUP(Cities!D17,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K17" s="25">
+      <c r="M17" s="26">
         <f>VLOOKUP(Cities!D17,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L17" s="25">
+      <c r="N17" s="26">
         <f>VLOOKUP(Cities!D17,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M17" s="25">
+      <c r="O17" s="26">
         <f>VLOOKUP(Cities!D17,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N17" s="25">
-        <f>E17*J17+F17*K17+G17*L17+M17</f>
-        <v/>
-      </c>
-      <c r="O17" s="25">
+      <c r="P17" s="26">
+        <f>G17*L17+H17*M17+I17*N17+O17</f>
+        <v/>
+      </c>
+      <c r="Q17" s="26">
         <f>Cities!J17</f>
         <v/>
       </c>
-      <c r="P17" s="25">
+      <c r="R17" s="26">
         <f>200+C17*80</f>
         <v/>
       </c>
-      <c r="Q17" s="25">
+      <c r="S17" s="26">
         <f>350+C17*50+300+C17*30</f>
         <v/>
       </c>
-      <c r="R17" s="25">
-        <f>O17+N17+P17+Q17</f>
-        <v/>
-      </c>
-      <c r="S17" s="23">
+      <c r="T17" s="26">
+        <f>Cities!U17</f>
+        <v/>
+      </c>
+      <c r="U17" s="26">
+        <f>Cities!L17/60</f>
+        <v/>
+      </c>
+      <c r="V17" s="26">
+        <f>Q17+P17+R17+S17+T17</f>
+        <v/>
+      </c>
+      <c r="W17" s="24">
         <f>C17*Cities!F17*Cities!G17</f>
         <v/>
       </c>
-      <c r="T17" s="23">
-        <f>INT(S17*Cities!O17)</f>
-        <v/>
-      </c>
-      <c r="U17" s="23">
-        <f>INT(S17*Cities!P17)</f>
-        <v/>
-      </c>
-      <c r="V17" s="23">
-        <f>CEILING(R17/(Cities!H17*(1-Cities!I17)),1)</f>
-        <v/>
-      </c>
-      <c r="W17" s="26">
+      <c r="X17" s="24">
+        <f>INT(W17*Cities!O17)</f>
+        <v/>
+      </c>
+      <c r="Y17" s="24">
+        <f>INT(W17*Cities!P17)</f>
+        <v/>
+      </c>
+      <c r="Z17" s="24">
+        <f>CEILING((V17+U17)/AB17,1)</f>
+        <v/>
+      </c>
+      <c r="AA17" s="27">
         <f>Cities!H17*Cities!I17</f>
         <v/>
       </c>
-      <c r="X17" s="26">
-        <f>Cities!H17-W17</f>
-        <v/>
-      </c>
-      <c r="Y17" s="25">
-        <f>(U17*Cities!H17*(1-Cities!I17)-R17)*(1-I17)</f>
-        <v/>
-      </c>
-      <c r="Z17" s="25">
-        <f>FLOOR((Cities!K17+Cities!L17+Cities!M17+Cities!J17*Cities!N17)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA17" s="25">
-        <f>CEILING((Cities!K17+Cities!L17+Cities!M17+Cities!J17*Cities!N17)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB17" s="25">
-        <f>(Z17+AA17)/2</f>
-        <v/>
-      </c>
-      <c r="AC17" s="23">
-        <f>IF(Y17&gt;0,CEILING(AB17/Y17,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD17" s="27">
-        <f>IF(R17&gt;0,Y17/R17,0)</f>
-        <v/>
-      </c>
-      <c r="AE17" s="28">
-        <f>IF(V17&lt;S17*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB17" s="27">
+        <f>Cities!H17-AA17</f>
+        <v/>
+      </c>
+      <c r="AC17" s="26">
+        <f>IF((X17*AB17-V17-U17)&gt;0, (X17*AB17-V17-U17)*(1-K17), X17*AB17-V17-U17)</f>
+        <v/>
+      </c>
+      <c r="AD17" s="26">
+        <f>IF((Y17*AB17-V17-U17)&gt;0, (Y17*AB17-V17-U17)*(1-K17), Y17*AB17-V17-U17)</f>
+        <v/>
+      </c>
+      <c r="AE17" s="26">
+        <f>AC17+U17</f>
+        <v/>
+      </c>
+      <c r="AF17" s="26">
+        <f>AD17+U17</f>
+        <v/>
+      </c>
+      <c r="AG17" s="26">
+        <f>FLOOR((Cities!K17+Cities!L17+Cities!M17+Cities!T17+Cities!J17*Cities!N17)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH17" s="26">
+        <f>CEILING((Cities!K17+Cities!L17+Cities!M17+Cities!T17+Cities!J17*Cities!N17)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI17" s="26">
+        <f>(AG17+AH17)/2</f>
+        <v/>
+      </c>
+      <c r="AJ17" s="24">
+        <f>IF(AE17*12&gt;=AI17, IF(AE17&gt;0,CEILING(AI17/AE17,1),999), IF(AF17&gt;0,12+CEILING((AI17-AE17*12)/AF17,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK17" s="28">
+        <f>IF(V17&gt;0,AD17/V17,0)</f>
+        <v/>
+      </c>
+      <c r="AL17" s="29">
+        <f>IF(Z17&lt;W17*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -5412,120 +5931,148 @@
         <f>Cities!D18</f>
         <v/>
       </c>
-      <c r="C18" s="23">
+      <c r="C18" s="24">
         <f>IF(Cities!E18&lt;=750,3,IF(Cities!E18&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="24">
+        <f>C18-1</f>
+        <v/>
+      </c>
+      <c r="E18" s="24">
+        <f>C18+D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="24">
         <f>IF(C18&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E18" s="23">
+      <c r="G18" s="24">
         <f>IF(C18&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F18" s="23">
-        <f>C18-E18</f>
-        <v/>
-      </c>
-      <c r="G18" s="23">
+      <c r="H18" s="24">
+        <f>C18-G18</f>
+        <v/>
+      </c>
+      <c r="I18" s="24">
         <f>CEILING(C18/2,1)</f>
         <v/>
       </c>
-      <c r="H18" s="23">
-        <f>E18+F18+G18+1</f>
-        <v/>
-      </c>
-      <c r="I18" s="24">
+      <c r="J18" s="24">
+        <f>G18+H18+I18+1</f>
+        <v/>
+      </c>
+      <c r="K18" s="25">
         <f>VLOOKUP(Cities!D18,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J18" s="25">
+      <c r="L18" s="26">
         <f>VLOOKUP(Cities!D18,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K18" s="25">
+      <c r="M18" s="26">
         <f>VLOOKUP(Cities!D18,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L18" s="25">
+      <c r="N18" s="26">
         <f>VLOOKUP(Cities!D18,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M18" s="25">
+      <c r="O18" s="26">
         <f>VLOOKUP(Cities!D18,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N18" s="25">
-        <f>E18*J18+F18*K18+G18*L18+M18</f>
-        <v/>
-      </c>
-      <c r="O18" s="25">
+      <c r="P18" s="26">
+        <f>G18*L18+H18*M18+I18*N18+O18</f>
+        <v/>
+      </c>
+      <c r="Q18" s="26">
         <f>Cities!J18</f>
         <v/>
       </c>
-      <c r="P18" s="25">
+      <c r="R18" s="26">
         <f>200+C18*80</f>
         <v/>
       </c>
-      <c r="Q18" s="25">
+      <c r="S18" s="26">
         <f>350+C18*50+300+C18*30</f>
         <v/>
       </c>
-      <c r="R18" s="25">
-        <f>O18+N18+P18+Q18</f>
-        <v/>
-      </c>
-      <c r="S18" s="23">
+      <c r="T18" s="26">
+        <f>Cities!U18</f>
+        <v/>
+      </c>
+      <c r="U18" s="26">
+        <f>Cities!L18/60</f>
+        <v/>
+      </c>
+      <c r="V18" s="26">
+        <f>Q18+P18+R18+S18+T18</f>
+        <v/>
+      </c>
+      <c r="W18" s="24">
         <f>C18*Cities!F18*Cities!G18</f>
         <v/>
       </c>
-      <c r="T18" s="23">
-        <f>INT(S18*Cities!O18)</f>
-        <v/>
-      </c>
-      <c r="U18" s="23">
-        <f>INT(S18*Cities!P18)</f>
-        <v/>
-      </c>
-      <c r="V18" s="23">
-        <f>CEILING(R18/(Cities!H18*(1-Cities!I18)),1)</f>
-        <v/>
-      </c>
-      <c r="W18" s="26">
+      <c r="X18" s="24">
+        <f>INT(W18*Cities!O18)</f>
+        <v/>
+      </c>
+      <c r="Y18" s="24">
+        <f>INT(W18*Cities!P18)</f>
+        <v/>
+      </c>
+      <c r="Z18" s="24">
+        <f>CEILING((V18+U18)/AB18,1)</f>
+        <v/>
+      </c>
+      <c r="AA18" s="27">
         <f>Cities!H18*Cities!I18</f>
         <v/>
       </c>
-      <c r="X18" s="26">
-        <f>Cities!H18-W18</f>
-        <v/>
-      </c>
-      <c r="Y18" s="25">
-        <f>(U18*Cities!H18*(1-Cities!I18)-R18)*(1-I18)</f>
-        <v/>
-      </c>
-      <c r="Z18" s="25">
-        <f>FLOOR((Cities!K18+Cities!L18+Cities!M18+Cities!J18*Cities!N18)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA18" s="25">
-        <f>CEILING((Cities!K18+Cities!L18+Cities!M18+Cities!J18*Cities!N18)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB18" s="25">
-        <f>(Z18+AA18)/2</f>
-        <v/>
-      </c>
-      <c r="AC18" s="23">
-        <f>IF(Y18&gt;0,CEILING(AB18/Y18,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD18" s="27">
-        <f>IF(R18&gt;0,Y18/R18,0)</f>
-        <v/>
-      </c>
-      <c r="AE18" s="28">
-        <f>IF(V18&lt;S18*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB18" s="27">
+        <f>Cities!H18-AA18</f>
+        <v/>
+      </c>
+      <c r="AC18" s="26">
+        <f>IF((X18*AB18-V18-U18)&gt;0, (X18*AB18-V18-U18)*(1-K18), X18*AB18-V18-U18)</f>
+        <v/>
+      </c>
+      <c r="AD18" s="26">
+        <f>IF((Y18*AB18-V18-U18)&gt;0, (Y18*AB18-V18-U18)*(1-K18), Y18*AB18-V18-U18)</f>
+        <v/>
+      </c>
+      <c r="AE18" s="26">
+        <f>AC18+U18</f>
+        <v/>
+      </c>
+      <c r="AF18" s="26">
+        <f>AD18+U18</f>
+        <v/>
+      </c>
+      <c r="AG18" s="26">
+        <f>FLOOR((Cities!K18+Cities!L18+Cities!M18+Cities!T18+Cities!J18*Cities!N18)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH18" s="26">
+        <f>CEILING((Cities!K18+Cities!L18+Cities!M18+Cities!T18+Cities!J18*Cities!N18)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI18" s="26">
+        <f>(AG18+AH18)/2</f>
+        <v/>
+      </c>
+      <c r="AJ18" s="24">
+        <f>IF(AE18*12&gt;=AI18, IF(AE18&gt;0,CEILING(AI18/AE18,1),999), IF(AF18&gt;0,12+CEILING((AI18-AE18*12)/AF18,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK18" s="28">
+        <f>IF(V18&gt;0,AD18/V18,0)</f>
+        <v/>
+      </c>
+      <c r="AL18" s="29">
+        <f>IF(Z18&lt;W18*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -5538,120 +6085,148 @@
         <f>Cities!D19</f>
         <v/>
       </c>
-      <c r="C19" s="23">
+      <c r="C19" s="24">
         <f>IF(Cities!E19&lt;=750,3,IF(Cities!E19&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="24">
+        <f>C19-1</f>
+        <v/>
+      </c>
+      <c r="E19" s="24">
+        <f>C19+D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="24">
         <f>IF(C19&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E19" s="23">
+      <c r="G19" s="24">
         <f>IF(C19&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F19" s="23">
-        <f>C19-E19</f>
-        <v/>
-      </c>
-      <c r="G19" s="23">
+      <c r="H19" s="24">
+        <f>C19-G19</f>
+        <v/>
+      </c>
+      <c r="I19" s="24">
         <f>CEILING(C19/2,1)</f>
         <v/>
       </c>
-      <c r="H19" s="23">
-        <f>E19+F19+G19+1</f>
-        <v/>
-      </c>
-      <c r="I19" s="24">
+      <c r="J19" s="24">
+        <f>G19+H19+I19+1</f>
+        <v/>
+      </c>
+      <c r="K19" s="25">
         <f>VLOOKUP(Cities!D19,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J19" s="25">
+      <c r="L19" s="26">
         <f>VLOOKUP(Cities!D19,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K19" s="25">
+      <c r="M19" s="26">
         <f>VLOOKUP(Cities!D19,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L19" s="25">
+      <c r="N19" s="26">
         <f>VLOOKUP(Cities!D19,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M19" s="25">
+      <c r="O19" s="26">
         <f>VLOOKUP(Cities!D19,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N19" s="25">
-        <f>E19*J19+F19*K19+G19*L19+M19</f>
-        <v/>
-      </c>
-      <c r="O19" s="25">
+      <c r="P19" s="26">
+        <f>G19*L19+H19*M19+I19*N19+O19</f>
+        <v/>
+      </c>
+      <c r="Q19" s="26">
         <f>Cities!J19</f>
         <v/>
       </c>
-      <c r="P19" s="25">
+      <c r="R19" s="26">
         <f>200+C19*80</f>
         <v/>
       </c>
-      <c r="Q19" s="25">
+      <c r="S19" s="26">
         <f>350+C19*50+300+C19*30</f>
         <v/>
       </c>
-      <c r="R19" s="25">
-        <f>O19+N19+P19+Q19</f>
-        <v/>
-      </c>
-      <c r="S19" s="23">
+      <c r="T19" s="26">
+        <f>Cities!U19</f>
+        <v/>
+      </c>
+      <c r="U19" s="26">
+        <f>Cities!L19/60</f>
+        <v/>
+      </c>
+      <c r="V19" s="26">
+        <f>Q19+P19+R19+S19+T19</f>
+        <v/>
+      </c>
+      <c r="W19" s="24">
         <f>C19*Cities!F19*Cities!G19</f>
         <v/>
       </c>
-      <c r="T19" s="23">
-        <f>INT(S19*Cities!O19)</f>
-        <v/>
-      </c>
-      <c r="U19" s="23">
-        <f>INT(S19*Cities!P19)</f>
-        <v/>
-      </c>
-      <c r="V19" s="23">
-        <f>CEILING(R19/(Cities!H19*(1-Cities!I19)),1)</f>
-        <v/>
-      </c>
-      <c r="W19" s="26">
+      <c r="X19" s="24">
+        <f>INT(W19*Cities!O19)</f>
+        <v/>
+      </c>
+      <c r="Y19" s="24">
+        <f>INT(W19*Cities!P19)</f>
+        <v/>
+      </c>
+      <c r="Z19" s="24">
+        <f>CEILING((V19+U19)/AB19,1)</f>
+        <v/>
+      </c>
+      <c r="AA19" s="27">
         <f>Cities!H19*Cities!I19</f>
         <v/>
       </c>
-      <c r="X19" s="26">
-        <f>Cities!H19-W19</f>
-        <v/>
-      </c>
-      <c r="Y19" s="25">
-        <f>(U19*Cities!H19*(1-Cities!I19)-R19)*(1-I19)</f>
-        <v/>
-      </c>
-      <c r="Z19" s="25">
-        <f>FLOOR((Cities!K19+Cities!L19+Cities!M19+Cities!J19*Cities!N19)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA19" s="25">
-        <f>CEILING((Cities!K19+Cities!L19+Cities!M19+Cities!J19*Cities!N19)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB19" s="25">
-        <f>(Z19+AA19)/2</f>
-        <v/>
-      </c>
-      <c r="AC19" s="23">
-        <f>IF(Y19&gt;0,CEILING(AB19/Y19,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD19" s="27">
-        <f>IF(R19&gt;0,Y19/R19,0)</f>
-        <v/>
-      </c>
-      <c r="AE19" s="28">
-        <f>IF(V19&lt;S19*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB19" s="27">
+        <f>Cities!H19-AA19</f>
+        <v/>
+      </c>
+      <c r="AC19" s="26">
+        <f>IF((X19*AB19-V19-U19)&gt;0, (X19*AB19-V19-U19)*(1-K19), X19*AB19-V19-U19)</f>
+        <v/>
+      </c>
+      <c r="AD19" s="26">
+        <f>IF((Y19*AB19-V19-U19)&gt;0, (Y19*AB19-V19-U19)*(1-K19), Y19*AB19-V19-U19)</f>
+        <v/>
+      </c>
+      <c r="AE19" s="26">
+        <f>AC19+U19</f>
+        <v/>
+      </c>
+      <c r="AF19" s="26">
+        <f>AD19+U19</f>
+        <v/>
+      </c>
+      <c r="AG19" s="26">
+        <f>FLOOR((Cities!K19+Cities!L19+Cities!M19+Cities!T19+Cities!J19*Cities!N19)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH19" s="26">
+        <f>CEILING((Cities!K19+Cities!L19+Cities!M19+Cities!T19+Cities!J19*Cities!N19)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI19" s="26">
+        <f>(AG19+AH19)/2</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="24">
+        <f>IF(AE19*12&gt;=AI19, IF(AE19&gt;0,CEILING(AI19/AE19,1),999), IF(AF19&gt;0,12+CEILING((AI19-AE19*12)/AF19,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK19" s="28">
+        <f>IF(V19&gt;0,AD19/V19,0)</f>
+        <v/>
+      </c>
+      <c r="AL19" s="29">
+        <f>IF(Z19&lt;W19*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -5664,120 +6239,148 @@
         <f>Cities!D20</f>
         <v/>
       </c>
-      <c r="C20" s="23">
+      <c r="C20" s="24">
         <f>IF(Cities!E20&lt;=750,3,IF(Cities!E20&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="24">
+        <f>C20-1</f>
+        <v/>
+      </c>
+      <c r="E20" s="24">
+        <f>C20+D20</f>
+        <v/>
+      </c>
+      <c r="F20" s="24">
         <f>IF(C20&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E20" s="23">
+      <c r="G20" s="24">
         <f>IF(C20&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F20" s="23">
-        <f>C20-E20</f>
-        <v/>
-      </c>
-      <c r="G20" s="23">
+      <c r="H20" s="24">
+        <f>C20-G20</f>
+        <v/>
+      </c>
+      <c r="I20" s="24">
         <f>CEILING(C20/2,1)</f>
         <v/>
       </c>
-      <c r="H20" s="23">
-        <f>E20+F20+G20+1</f>
-        <v/>
-      </c>
-      <c r="I20" s="24">
+      <c r="J20" s="24">
+        <f>G20+H20+I20+1</f>
+        <v/>
+      </c>
+      <c r="K20" s="25">
         <f>VLOOKUP(Cities!D20,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J20" s="25">
+      <c r="L20" s="26">
         <f>VLOOKUP(Cities!D20,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K20" s="25">
+      <c r="M20" s="26">
         <f>VLOOKUP(Cities!D20,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L20" s="25">
+      <c r="N20" s="26">
         <f>VLOOKUP(Cities!D20,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M20" s="25">
+      <c r="O20" s="26">
         <f>VLOOKUP(Cities!D20,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N20" s="25">
-        <f>E20*J20+F20*K20+G20*L20+M20</f>
-        <v/>
-      </c>
-      <c r="O20" s="25">
+      <c r="P20" s="26">
+        <f>G20*L20+H20*M20+I20*N20+O20</f>
+        <v/>
+      </c>
+      <c r="Q20" s="26">
         <f>Cities!J20</f>
         <v/>
       </c>
-      <c r="P20" s="25">
+      <c r="R20" s="26">
         <f>200+C20*80</f>
         <v/>
       </c>
-      <c r="Q20" s="25">
+      <c r="S20" s="26">
         <f>350+C20*50+300+C20*30</f>
         <v/>
       </c>
-      <c r="R20" s="25">
-        <f>O20+N20+P20+Q20</f>
-        <v/>
-      </c>
-      <c r="S20" s="23">
+      <c r="T20" s="26">
+        <f>Cities!U20</f>
+        <v/>
+      </c>
+      <c r="U20" s="26">
+        <f>Cities!L20/60</f>
+        <v/>
+      </c>
+      <c r="V20" s="26">
+        <f>Q20+P20+R20+S20+T20</f>
+        <v/>
+      </c>
+      <c r="W20" s="24">
         <f>C20*Cities!F20*Cities!G20</f>
         <v/>
       </c>
-      <c r="T20" s="23">
-        <f>INT(S20*Cities!O20)</f>
-        <v/>
-      </c>
-      <c r="U20" s="23">
-        <f>INT(S20*Cities!P20)</f>
-        <v/>
-      </c>
-      <c r="V20" s="23">
-        <f>CEILING(R20/(Cities!H20*(1-Cities!I20)),1)</f>
-        <v/>
-      </c>
-      <c r="W20" s="26">
+      <c r="X20" s="24">
+        <f>INT(W20*Cities!O20)</f>
+        <v/>
+      </c>
+      <c r="Y20" s="24">
+        <f>INT(W20*Cities!P20)</f>
+        <v/>
+      </c>
+      <c r="Z20" s="24">
+        <f>CEILING((V20+U20)/AB20,1)</f>
+        <v/>
+      </c>
+      <c r="AA20" s="27">
         <f>Cities!H20*Cities!I20</f>
         <v/>
       </c>
-      <c r="X20" s="26">
-        <f>Cities!H20-W20</f>
-        <v/>
-      </c>
-      <c r="Y20" s="25">
-        <f>(U20*Cities!H20*(1-Cities!I20)-R20)*(1-I20)</f>
-        <v/>
-      </c>
-      <c r="Z20" s="25">
-        <f>FLOOR((Cities!K20+Cities!L20+Cities!M20+Cities!J20*Cities!N20)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA20" s="25">
-        <f>CEILING((Cities!K20+Cities!L20+Cities!M20+Cities!J20*Cities!N20)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB20" s="25">
-        <f>(Z20+AA20)/2</f>
-        <v/>
-      </c>
-      <c r="AC20" s="23">
-        <f>IF(Y20&gt;0,CEILING(AB20/Y20,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD20" s="27">
-        <f>IF(R20&gt;0,Y20/R20,0)</f>
-        <v/>
-      </c>
-      <c r="AE20" s="28">
-        <f>IF(V20&lt;S20*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB20" s="27">
+        <f>Cities!H20-AA20</f>
+        <v/>
+      </c>
+      <c r="AC20" s="26">
+        <f>IF((X20*AB20-V20-U20)&gt;0, (X20*AB20-V20-U20)*(1-K20), X20*AB20-V20-U20)</f>
+        <v/>
+      </c>
+      <c r="AD20" s="26">
+        <f>IF((Y20*AB20-V20-U20)&gt;0, (Y20*AB20-V20-U20)*(1-K20), Y20*AB20-V20-U20)</f>
+        <v/>
+      </c>
+      <c r="AE20" s="26">
+        <f>AC20+U20</f>
+        <v/>
+      </c>
+      <c r="AF20" s="26">
+        <f>AD20+U20</f>
+        <v/>
+      </c>
+      <c r="AG20" s="26">
+        <f>FLOOR((Cities!K20+Cities!L20+Cities!M20+Cities!T20+Cities!J20*Cities!N20)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH20" s="26">
+        <f>CEILING((Cities!K20+Cities!L20+Cities!M20+Cities!T20+Cities!J20*Cities!N20)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI20" s="26">
+        <f>(AG20+AH20)/2</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="24">
+        <f>IF(AE20*12&gt;=AI20, IF(AE20&gt;0,CEILING(AI20/AE20,1),999), IF(AF20&gt;0,12+CEILING((AI20-AE20*12)/AF20,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK20" s="28">
+        <f>IF(V20&gt;0,AD20/V20,0)</f>
+        <v/>
+      </c>
+      <c r="AL20" s="29">
+        <f>IF(Z20&lt;W20*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -5790,120 +6393,148 @@
         <f>Cities!D21</f>
         <v/>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="24">
         <f>IF(Cities!E21&lt;=750,3,IF(Cities!E21&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="24">
+        <f>C21-1</f>
+        <v/>
+      </c>
+      <c r="E21" s="24">
+        <f>C21+D21</f>
+        <v/>
+      </c>
+      <c r="F21" s="24">
         <f>IF(C21&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E21" s="23">
+      <c r="G21" s="24">
         <f>IF(C21&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F21" s="23">
-        <f>C21-E21</f>
-        <v/>
-      </c>
-      <c r="G21" s="23">
+      <c r="H21" s="24">
+        <f>C21-G21</f>
+        <v/>
+      </c>
+      <c r="I21" s="24">
         <f>CEILING(C21/2,1)</f>
         <v/>
       </c>
-      <c r="H21" s="23">
-        <f>E21+F21+G21+1</f>
-        <v/>
-      </c>
-      <c r="I21" s="24">
+      <c r="J21" s="24">
+        <f>G21+H21+I21+1</f>
+        <v/>
+      </c>
+      <c r="K21" s="25">
         <f>VLOOKUP(Cities!D21,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J21" s="25">
+      <c r="L21" s="26">
         <f>VLOOKUP(Cities!D21,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K21" s="25">
+      <c r="M21" s="26">
         <f>VLOOKUP(Cities!D21,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L21" s="25">
+      <c r="N21" s="26">
         <f>VLOOKUP(Cities!D21,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M21" s="25">
+      <c r="O21" s="26">
         <f>VLOOKUP(Cities!D21,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N21" s="25">
-        <f>E21*J21+F21*K21+G21*L21+M21</f>
-        <v/>
-      </c>
-      <c r="O21" s="25">
+      <c r="P21" s="26">
+        <f>G21*L21+H21*M21+I21*N21+O21</f>
+        <v/>
+      </c>
+      <c r="Q21" s="26">
         <f>Cities!J21</f>
         <v/>
       </c>
-      <c r="P21" s="25">
+      <c r="R21" s="26">
         <f>200+C21*80</f>
         <v/>
       </c>
-      <c r="Q21" s="25">
+      <c r="S21" s="26">
         <f>350+C21*50+300+C21*30</f>
         <v/>
       </c>
-      <c r="R21" s="25">
-        <f>O21+N21+P21+Q21</f>
-        <v/>
-      </c>
-      <c r="S21" s="23">
+      <c r="T21" s="26">
+        <f>Cities!U21</f>
+        <v/>
+      </c>
+      <c r="U21" s="26">
+        <f>Cities!L21/60</f>
+        <v/>
+      </c>
+      <c r="V21" s="26">
+        <f>Q21+P21+R21+S21+T21</f>
+        <v/>
+      </c>
+      <c r="W21" s="24">
         <f>C21*Cities!F21*Cities!G21</f>
         <v/>
       </c>
-      <c r="T21" s="23">
-        <f>INT(S21*Cities!O21)</f>
-        <v/>
-      </c>
-      <c r="U21" s="23">
-        <f>INT(S21*Cities!P21)</f>
-        <v/>
-      </c>
-      <c r="V21" s="23">
-        <f>CEILING(R21/(Cities!H21*(1-Cities!I21)),1)</f>
-        <v/>
-      </c>
-      <c r="W21" s="26">
+      <c r="X21" s="24">
+        <f>INT(W21*Cities!O21)</f>
+        <v/>
+      </c>
+      <c r="Y21" s="24">
+        <f>INT(W21*Cities!P21)</f>
+        <v/>
+      </c>
+      <c r="Z21" s="24">
+        <f>CEILING((V21+U21)/AB21,1)</f>
+        <v/>
+      </c>
+      <c r="AA21" s="27">
         <f>Cities!H21*Cities!I21</f>
         <v/>
       </c>
-      <c r="X21" s="26">
-        <f>Cities!H21-W21</f>
-        <v/>
-      </c>
-      <c r="Y21" s="25">
-        <f>(U21*Cities!H21*(1-Cities!I21)-R21)*(1-I21)</f>
-        <v/>
-      </c>
-      <c r="Z21" s="25">
-        <f>FLOOR((Cities!K21+Cities!L21+Cities!M21+Cities!J21*Cities!N21)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA21" s="25">
-        <f>CEILING((Cities!K21+Cities!L21+Cities!M21+Cities!J21*Cities!N21)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB21" s="25">
-        <f>(Z21+AA21)/2</f>
-        <v/>
-      </c>
-      <c r="AC21" s="23">
-        <f>IF(Y21&gt;0,CEILING(AB21/Y21,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD21" s="27">
-        <f>IF(R21&gt;0,Y21/R21,0)</f>
-        <v/>
-      </c>
-      <c r="AE21" s="28">
-        <f>IF(V21&lt;S21*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB21" s="27">
+        <f>Cities!H21-AA21</f>
+        <v/>
+      </c>
+      <c r="AC21" s="26">
+        <f>IF((X21*AB21-V21-U21)&gt;0, (X21*AB21-V21-U21)*(1-K21), X21*AB21-V21-U21)</f>
+        <v/>
+      </c>
+      <c r="AD21" s="26">
+        <f>IF((Y21*AB21-V21-U21)&gt;0, (Y21*AB21-V21-U21)*(1-K21), Y21*AB21-V21-U21)</f>
+        <v/>
+      </c>
+      <c r="AE21" s="26">
+        <f>AC21+U21</f>
+        <v/>
+      </c>
+      <c r="AF21" s="26">
+        <f>AD21+U21</f>
+        <v/>
+      </c>
+      <c r="AG21" s="26">
+        <f>FLOOR((Cities!K21+Cities!L21+Cities!M21+Cities!T21+Cities!J21*Cities!N21)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH21" s="26">
+        <f>CEILING((Cities!K21+Cities!L21+Cities!M21+Cities!T21+Cities!J21*Cities!N21)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI21" s="26">
+        <f>(AG21+AH21)/2</f>
+        <v/>
+      </c>
+      <c r="AJ21" s="24">
+        <f>IF(AE21*12&gt;=AI21, IF(AE21&gt;0,CEILING(AI21/AE21,1),999), IF(AF21&gt;0,12+CEILING((AI21-AE21*12)/AF21,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK21" s="28">
+        <f>IF(V21&gt;0,AD21/V21,0)</f>
+        <v/>
+      </c>
+      <c r="AL21" s="29">
+        <f>IF(Z21&lt;W21*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -5916,120 +6547,148 @@
         <f>Cities!D22</f>
         <v/>
       </c>
-      <c r="C22" s="23">
+      <c r="C22" s="24">
         <f>IF(Cities!E22&lt;=750,3,IF(Cities!E22&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="24">
+        <f>C22-1</f>
+        <v/>
+      </c>
+      <c r="E22" s="24">
+        <f>C22+D22</f>
+        <v/>
+      </c>
+      <c r="F22" s="24">
         <f>IF(C22&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E22" s="23">
+      <c r="G22" s="24">
         <f>IF(C22&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F22" s="23">
-        <f>C22-E22</f>
-        <v/>
-      </c>
-      <c r="G22" s="23">
+      <c r="H22" s="24">
+        <f>C22-G22</f>
+        <v/>
+      </c>
+      <c r="I22" s="24">
         <f>CEILING(C22/2,1)</f>
         <v/>
       </c>
-      <c r="H22" s="23">
-        <f>E22+F22+G22+1</f>
-        <v/>
-      </c>
-      <c r="I22" s="24">
+      <c r="J22" s="24">
+        <f>G22+H22+I22+1</f>
+        <v/>
+      </c>
+      <c r="K22" s="25">
         <f>VLOOKUP(Cities!D22,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J22" s="25">
+      <c r="L22" s="26">
         <f>VLOOKUP(Cities!D22,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K22" s="25">
+      <c r="M22" s="26">
         <f>VLOOKUP(Cities!D22,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L22" s="25">
+      <c r="N22" s="26">
         <f>VLOOKUP(Cities!D22,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M22" s="25">
+      <c r="O22" s="26">
         <f>VLOOKUP(Cities!D22,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N22" s="25">
-        <f>E22*J22+F22*K22+G22*L22+M22</f>
-        <v/>
-      </c>
-      <c r="O22" s="25">
+      <c r="P22" s="26">
+        <f>G22*L22+H22*M22+I22*N22+O22</f>
+        <v/>
+      </c>
+      <c r="Q22" s="26">
         <f>Cities!J22</f>
         <v/>
       </c>
-      <c r="P22" s="25">
+      <c r="R22" s="26">
         <f>200+C22*80</f>
         <v/>
       </c>
-      <c r="Q22" s="25">
+      <c r="S22" s="26">
         <f>350+C22*50+300+C22*30</f>
         <v/>
       </c>
-      <c r="R22" s="25">
-        <f>O22+N22+P22+Q22</f>
-        <v/>
-      </c>
-      <c r="S22" s="23">
+      <c r="T22" s="26">
+        <f>Cities!U22</f>
+        <v/>
+      </c>
+      <c r="U22" s="26">
+        <f>Cities!L22/60</f>
+        <v/>
+      </c>
+      <c r="V22" s="26">
+        <f>Q22+P22+R22+S22+T22</f>
+        <v/>
+      </c>
+      <c r="W22" s="24">
         <f>C22*Cities!F22*Cities!G22</f>
         <v/>
       </c>
-      <c r="T22" s="23">
-        <f>INT(S22*Cities!O22)</f>
-        <v/>
-      </c>
-      <c r="U22" s="23">
-        <f>INT(S22*Cities!P22)</f>
-        <v/>
-      </c>
-      <c r="V22" s="23">
-        <f>CEILING(R22/(Cities!H22*(1-Cities!I22)),1)</f>
-        <v/>
-      </c>
-      <c r="W22" s="26">
+      <c r="X22" s="24">
+        <f>INT(W22*Cities!O22)</f>
+        <v/>
+      </c>
+      <c r="Y22" s="24">
+        <f>INT(W22*Cities!P22)</f>
+        <v/>
+      </c>
+      <c r="Z22" s="24">
+        <f>CEILING((V22+U22)/AB22,1)</f>
+        <v/>
+      </c>
+      <c r="AA22" s="27">
         <f>Cities!H22*Cities!I22</f>
         <v/>
       </c>
-      <c r="X22" s="26">
-        <f>Cities!H22-W22</f>
-        <v/>
-      </c>
-      <c r="Y22" s="25">
-        <f>(U22*Cities!H22*(1-Cities!I22)-R22)*(1-I22)</f>
-        <v/>
-      </c>
-      <c r="Z22" s="25">
-        <f>FLOOR((Cities!K22+Cities!L22+Cities!M22+Cities!J22*Cities!N22)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA22" s="25">
-        <f>CEILING((Cities!K22+Cities!L22+Cities!M22+Cities!J22*Cities!N22)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB22" s="25">
-        <f>(Z22+AA22)/2</f>
-        <v/>
-      </c>
-      <c r="AC22" s="23">
-        <f>IF(Y22&gt;0,CEILING(AB22/Y22,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD22" s="27">
-        <f>IF(R22&gt;0,Y22/R22,0)</f>
-        <v/>
-      </c>
-      <c r="AE22" s="28">
-        <f>IF(V22&lt;S22*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB22" s="27">
+        <f>Cities!H22-AA22</f>
+        <v/>
+      </c>
+      <c r="AC22" s="26">
+        <f>IF((X22*AB22-V22-U22)&gt;0, (X22*AB22-V22-U22)*(1-K22), X22*AB22-V22-U22)</f>
+        <v/>
+      </c>
+      <c r="AD22" s="26">
+        <f>IF((Y22*AB22-V22-U22)&gt;0, (Y22*AB22-V22-U22)*(1-K22), Y22*AB22-V22-U22)</f>
+        <v/>
+      </c>
+      <c r="AE22" s="26">
+        <f>AC22+U22</f>
+        <v/>
+      </c>
+      <c r="AF22" s="26">
+        <f>AD22+U22</f>
+        <v/>
+      </c>
+      <c r="AG22" s="26">
+        <f>FLOOR((Cities!K22+Cities!L22+Cities!M22+Cities!T22+Cities!J22*Cities!N22)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH22" s="26">
+        <f>CEILING((Cities!K22+Cities!L22+Cities!M22+Cities!T22+Cities!J22*Cities!N22)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI22" s="26">
+        <f>(AG22+AH22)/2</f>
+        <v/>
+      </c>
+      <c r="AJ22" s="24">
+        <f>IF(AE22*12&gt;=AI22, IF(AE22&gt;0,CEILING(AI22/AE22,1),999), IF(AF22&gt;0,12+CEILING((AI22-AE22*12)/AF22,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK22" s="28">
+        <f>IF(V22&gt;0,AD22/V22,0)</f>
+        <v/>
+      </c>
+      <c r="AL22" s="29">
+        <f>IF(Z22&lt;W22*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -6042,120 +6701,148 @@
         <f>Cities!D23</f>
         <v/>
       </c>
-      <c r="C23" s="23">
+      <c r="C23" s="24">
         <f>IF(Cities!E23&lt;=750,3,IF(Cities!E23&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="24">
+        <f>C23-1</f>
+        <v/>
+      </c>
+      <c r="E23" s="24">
+        <f>C23+D23</f>
+        <v/>
+      </c>
+      <c r="F23" s="24">
         <f>IF(C23&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E23" s="23">
+      <c r="G23" s="24">
         <f>IF(C23&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F23" s="23">
-        <f>C23-E23</f>
-        <v/>
-      </c>
-      <c r="G23" s="23">
+      <c r="H23" s="24">
+        <f>C23-G23</f>
+        <v/>
+      </c>
+      <c r="I23" s="24">
         <f>CEILING(C23/2,1)</f>
         <v/>
       </c>
-      <c r="H23" s="23">
-        <f>E23+F23+G23+1</f>
-        <v/>
-      </c>
-      <c r="I23" s="24">
+      <c r="J23" s="24">
+        <f>G23+H23+I23+1</f>
+        <v/>
+      </c>
+      <c r="K23" s="25">
         <f>VLOOKUP(Cities!D23,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J23" s="25">
+      <c r="L23" s="26">
         <f>VLOOKUP(Cities!D23,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K23" s="25">
+      <c r="M23" s="26">
         <f>VLOOKUP(Cities!D23,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L23" s="25">
+      <c r="N23" s="26">
         <f>VLOOKUP(Cities!D23,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M23" s="25">
+      <c r="O23" s="26">
         <f>VLOOKUP(Cities!D23,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N23" s="25">
-        <f>E23*J23+F23*K23+G23*L23+M23</f>
-        <v/>
-      </c>
-      <c r="O23" s="25">
+      <c r="P23" s="26">
+        <f>G23*L23+H23*M23+I23*N23+O23</f>
+        <v/>
+      </c>
+      <c r="Q23" s="26">
         <f>Cities!J23</f>
         <v/>
       </c>
-      <c r="P23" s="25">
+      <c r="R23" s="26">
         <f>200+C23*80</f>
         <v/>
       </c>
-      <c r="Q23" s="25">
+      <c r="S23" s="26">
         <f>350+C23*50+300+C23*30</f>
         <v/>
       </c>
-      <c r="R23" s="25">
-        <f>O23+N23+P23+Q23</f>
-        <v/>
-      </c>
-      <c r="S23" s="23">
+      <c r="T23" s="26">
+        <f>Cities!U23</f>
+        <v/>
+      </c>
+      <c r="U23" s="26">
+        <f>Cities!L23/60</f>
+        <v/>
+      </c>
+      <c r="V23" s="26">
+        <f>Q23+P23+R23+S23+T23</f>
+        <v/>
+      </c>
+      <c r="W23" s="24">
         <f>C23*Cities!F23*Cities!G23</f>
         <v/>
       </c>
-      <c r="T23" s="23">
-        <f>INT(S23*Cities!O23)</f>
-        <v/>
-      </c>
-      <c r="U23" s="23">
-        <f>INT(S23*Cities!P23)</f>
-        <v/>
-      </c>
-      <c r="V23" s="23">
-        <f>CEILING(R23/(Cities!H23*(1-Cities!I23)),1)</f>
-        <v/>
-      </c>
-      <c r="W23" s="26">
+      <c r="X23" s="24">
+        <f>INT(W23*Cities!O23)</f>
+        <v/>
+      </c>
+      <c r="Y23" s="24">
+        <f>INT(W23*Cities!P23)</f>
+        <v/>
+      </c>
+      <c r="Z23" s="24">
+        <f>CEILING((V23+U23)/AB23,1)</f>
+        <v/>
+      </c>
+      <c r="AA23" s="27">
         <f>Cities!H23*Cities!I23</f>
         <v/>
       </c>
-      <c r="X23" s="26">
-        <f>Cities!H23-W23</f>
-        <v/>
-      </c>
-      <c r="Y23" s="25">
-        <f>(U23*Cities!H23*(1-Cities!I23)-R23)*(1-I23)</f>
-        <v/>
-      </c>
-      <c r="Z23" s="25">
-        <f>FLOOR((Cities!K23+Cities!L23+Cities!M23+Cities!J23*Cities!N23)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA23" s="25">
-        <f>CEILING((Cities!K23+Cities!L23+Cities!M23+Cities!J23*Cities!N23)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB23" s="25">
-        <f>(Z23+AA23)/2</f>
-        <v/>
-      </c>
-      <c r="AC23" s="23">
-        <f>IF(Y23&gt;0,CEILING(AB23/Y23,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD23" s="27">
-        <f>IF(R23&gt;0,Y23/R23,0)</f>
-        <v/>
-      </c>
-      <c r="AE23" s="28">
-        <f>IF(V23&lt;S23*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB23" s="27">
+        <f>Cities!H23-AA23</f>
+        <v/>
+      </c>
+      <c r="AC23" s="26">
+        <f>IF((X23*AB23-V23-U23)&gt;0, (X23*AB23-V23-U23)*(1-K23), X23*AB23-V23-U23)</f>
+        <v/>
+      </c>
+      <c r="AD23" s="26">
+        <f>IF((Y23*AB23-V23-U23)&gt;0, (Y23*AB23-V23-U23)*(1-K23), Y23*AB23-V23-U23)</f>
+        <v/>
+      </c>
+      <c r="AE23" s="26">
+        <f>AC23+U23</f>
+        <v/>
+      </c>
+      <c r="AF23" s="26">
+        <f>AD23+U23</f>
+        <v/>
+      </c>
+      <c r="AG23" s="26">
+        <f>FLOOR((Cities!K23+Cities!L23+Cities!M23+Cities!T23+Cities!J23*Cities!N23)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH23" s="26">
+        <f>CEILING((Cities!K23+Cities!L23+Cities!M23+Cities!T23+Cities!J23*Cities!N23)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI23" s="26">
+        <f>(AG23+AH23)/2</f>
+        <v/>
+      </c>
+      <c r="AJ23" s="24">
+        <f>IF(AE23*12&gt;=AI23, IF(AE23&gt;0,CEILING(AI23/AE23,1),999), IF(AF23&gt;0,12+CEILING((AI23-AE23*12)/AF23,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK23" s="28">
+        <f>IF(V23&gt;0,AD23/V23,0)</f>
+        <v/>
+      </c>
+      <c r="AL23" s="29">
+        <f>IF(Z23&lt;W23*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -6168,120 +6855,148 @@
         <f>Cities!D24</f>
         <v/>
       </c>
-      <c r="C24" s="23">
+      <c r="C24" s="24">
         <f>IF(Cities!E24&lt;=750,3,IF(Cities!E24&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="24">
+        <f>C24-1</f>
+        <v/>
+      </c>
+      <c r="E24" s="24">
+        <f>C24+D24</f>
+        <v/>
+      </c>
+      <c r="F24" s="24">
         <f>IF(C24&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E24" s="23">
+      <c r="G24" s="24">
         <f>IF(C24&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F24" s="23">
-        <f>C24-E24</f>
-        <v/>
-      </c>
-      <c r="G24" s="23">
+      <c r="H24" s="24">
+        <f>C24-G24</f>
+        <v/>
+      </c>
+      <c r="I24" s="24">
         <f>CEILING(C24/2,1)</f>
         <v/>
       </c>
-      <c r="H24" s="23">
-        <f>E24+F24+G24+1</f>
-        <v/>
-      </c>
-      <c r="I24" s="24">
+      <c r="J24" s="24">
+        <f>G24+H24+I24+1</f>
+        <v/>
+      </c>
+      <c r="K24" s="25">
         <f>VLOOKUP(Cities!D24,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J24" s="25">
+      <c r="L24" s="26">
         <f>VLOOKUP(Cities!D24,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K24" s="25">
+      <c r="M24" s="26">
         <f>VLOOKUP(Cities!D24,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L24" s="25">
+      <c r="N24" s="26">
         <f>VLOOKUP(Cities!D24,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M24" s="25">
+      <c r="O24" s="26">
         <f>VLOOKUP(Cities!D24,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N24" s="25">
-        <f>E24*J24+F24*K24+G24*L24+M24</f>
-        <v/>
-      </c>
-      <c r="O24" s="25">
+      <c r="P24" s="26">
+        <f>G24*L24+H24*M24+I24*N24+O24</f>
+        <v/>
+      </c>
+      <c r="Q24" s="26">
         <f>Cities!J24</f>
         <v/>
       </c>
-      <c r="P24" s="25">
+      <c r="R24" s="26">
         <f>200+C24*80</f>
         <v/>
       </c>
-      <c r="Q24" s="25">
+      <c r="S24" s="26">
         <f>350+C24*50+300+C24*30</f>
         <v/>
       </c>
-      <c r="R24" s="25">
-        <f>O24+N24+P24+Q24</f>
-        <v/>
-      </c>
-      <c r="S24" s="23">
+      <c r="T24" s="26">
+        <f>Cities!U24</f>
+        <v/>
+      </c>
+      <c r="U24" s="26">
+        <f>Cities!L24/60</f>
+        <v/>
+      </c>
+      <c r="V24" s="26">
+        <f>Q24+P24+R24+S24+T24</f>
+        <v/>
+      </c>
+      <c r="W24" s="24">
         <f>C24*Cities!F24*Cities!G24</f>
         <v/>
       </c>
-      <c r="T24" s="23">
-        <f>INT(S24*Cities!O24)</f>
-        <v/>
-      </c>
-      <c r="U24" s="23">
-        <f>INT(S24*Cities!P24)</f>
-        <v/>
-      </c>
-      <c r="V24" s="23">
-        <f>CEILING(R24/(Cities!H24*(1-Cities!I24)),1)</f>
-        <v/>
-      </c>
-      <c r="W24" s="26">
+      <c r="X24" s="24">
+        <f>INT(W24*Cities!O24)</f>
+        <v/>
+      </c>
+      <c r="Y24" s="24">
+        <f>INT(W24*Cities!P24)</f>
+        <v/>
+      </c>
+      <c r="Z24" s="24">
+        <f>CEILING((V24+U24)/AB24,1)</f>
+        <v/>
+      </c>
+      <c r="AA24" s="27">
         <f>Cities!H24*Cities!I24</f>
         <v/>
       </c>
-      <c r="X24" s="26">
-        <f>Cities!H24-W24</f>
-        <v/>
-      </c>
-      <c r="Y24" s="25">
-        <f>(U24*Cities!H24*(1-Cities!I24)-R24)*(1-I24)</f>
-        <v/>
-      </c>
-      <c r="Z24" s="25">
-        <f>FLOOR((Cities!K24+Cities!L24+Cities!M24+Cities!J24*Cities!N24)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA24" s="25">
-        <f>CEILING((Cities!K24+Cities!L24+Cities!M24+Cities!J24*Cities!N24)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB24" s="25">
-        <f>(Z24+AA24)/2</f>
-        <v/>
-      </c>
-      <c r="AC24" s="23">
-        <f>IF(Y24&gt;0,CEILING(AB24/Y24,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD24" s="27">
-        <f>IF(R24&gt;0,Y24/R24,0)</f>
-        <v/>
-      </c>
-      <c r="AE24" s="28">
-        <f>IF(V24&lt;S24*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB24" s="27">
+        <f>Cities!H24-AA24</f>
+        <v/>
+      </c>
+      <c r="AC24" s="26">
+        <f>IF((X24*AB24-V24-U24)&gt;0, (X24*AB24-V24-U24)*(1-K24), X24*AB24-V24-U24)</f>
+        <v/>
+      </c>
+      <c r="AD24" s="26">
+        <f>IF((Y24*AB24-V24-U24)&gt;0, (Y24*AB24-V24-U24)*(1-K24), Y24*AB24-V24-U24)</f>
+        <v/>
+      </c>
+      <c r="AE24" s="26">
+        <f>AC24+U24</f>
+        <v/>
+      </c>
+      <c r="AF24" s="26">
+        <f>AD24+U24</f>
+        <v/>
+      </c>
+      <c r="AG24" s="26">
+        <f>FLOOR((Cities!K24+Cities!L24+Cities!M24+Cities!T24+Cities!J24*Cities!N24)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH24" s="26">
+        <f>CEILING((Cities!K24+Cities!L24+Cities!M24+Cities!T24+Cities!J24*Cities!N24)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI24" s="26">
+        <f>(AG24+AH24)/2</f>
+        <v/>
+      </c>
+      <c r="AJ24" s="24">
+        <f>IF(AE24*12&gt;=AI24, IF(AE24&gt;0,CEILING(AI24/AE24,1),999), IF(AF24&gt;0,12+CEILING((AI24-AE24*12)/AF24,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK24" s="28">
+        <f>IF(V24&gt;0,AD24/V24,0)</f>
+        <v/>
+      </c>
+      <c r="AL24" s="29">
+        <f>IF(Z24&lt;W24*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -6294,120 +7009,148 @@
         <f>Cities!D25</f>
         <v/>
       </c>
-      <c r="C25" s="23">
+      <c r="C25" s="24">
         <f>IF(Cities!E25&lt;=750,3,IF(Cities!E25&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="24">
+        <f>C25-1</f>
+        <v/>
+      </c>
+      <c r="E25" s="24">
+        <f>C25+D25</f>
+        <v/>
+      </c>
+      <c r="F25" s="24">
         <f>IF(C25&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E25" s="23">
+      <c r="G25" s="24">
         <f>IF(C25&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F25" s="23">
-        <f>C25-E25</f>
-        <v/>
-      </c>
-      <c r="G25" s="23">
+      <c r="H25" s="24">
+        <f>C25-G25</f>
+        <v/>
+      </c>
+      <c r="I25" s="24">
         <f>CEILING(C25/2,1)</f>
         <v/>
       </c>
-      <c r="H25" s="23">
-        <f>E25+F25+G25+1</f>
-        <v/>
-      </c>
-      <c r="I25" s="24">
+      <c r="J25" s="24">
+        <f>G25+H25+I25+1</f>
+        <v/>
+      </c>
+      <c r="K25" s="25">
         <f>VLOOKUP(Cities!D25,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J25" s="25">
+      <c r="L25" s="26">
         <f>VLOOKUP(Cities!D25,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K25" s="25">
+      <c r="M25" s="26">
         <f>VLOOKUP(Cities!D25,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L25" s="25">
+      <c r="N25" s="26">
         <f>VLOOKUP(Cities!D25,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M25" s="25">
+      <c r="O25" s="26">
         <f>VLOOKUP(Cities!D25,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N25" s="25">
-        <f>E25*J25+F25*K25+G25*L25+M25</f>
-        <v/>
-      </c>
-      <c r="O25" s="25">
+      <c r="P25" s="26">
+        <f>G25*L25+H25*M25+I25*N25+O25</f>
+        <v/>
+      </c>
+      <c r="Q25" s="26">
         <f>Cities!J25</f>
         <v/>
       </c>
-      <c r="P25" s="25">
+      <c r="R25" s="26">
         <f>200+C25*80</f>
         <v/>
       </c>
-      <c r="Q25" s="25">
+      <c r="S25" s="26">
         <f>350+C25*50+300+C25*30</f>
         <v/>
       </c>
-      <c r="R25" s="25">
-        <f>O25+N25+P25+Q25</f>
-        <v/>
-      </c>
-      <c r="S25" s="23">
+      <c r="T25" s="26">
+        <f>Cities!U25</f>
+        <v/>
+      </c>
+      <c r="U25" s="26">
+        <f>Cities!L25/60</f>
+        <v/>
+      </c>
+      <c r="V25" s="26">
+        <f>Q25+P25+R25+S25+T25</f>
+        <v/>
+      </c>
+      <c r="W25" s="24">
         <f>C25*Cities!F25*Cities!G25</f>
         <v/>
       </c>
-      <c r="T25" s="23">
-        <f>INT(S25*Cities!O25)</f>
-        <v/>
-      </c>
-      <c r="U25" s="23">
-        <f>INT(S25*Cities!P25)</f>
-        <v/>
-      </c>
-      <c r="V25" s="23">
-        <f>CEILING(R25/(Cities!H25*(1-Cities!I25)),1)</f>
-        <v/>
-      </c>
-      <c r="W25" s="26">
+      <c r="X25" s="24">
+        <f>INT(W25*Cities!O25)</f>
+        <v/>
+      </c>
+      <c r="Y25" s="24">
+        <f>INT(W25*Cities!P25)</f>
+        <v/>
+      </c>
+      <c r="Z25" s="24">
+        <f>CEILING((V25+U25)/AB25,1)</f>
+        <v/>
+      </c>
+      <c r="AA25" s="27">
         <f>Cities!H25*Cities!I25</f>
         <v/>
       </c>
-      <c r="X25" s="26">
-        <f>Cities!H25-W25</f>
-        <v/>
-      </c>
-      <c r="Y25" s="25">
-        <f>(U25*Cities!H25*(1-Cities!I25)-R25)*(1-I25)</f>
-        <v/>
-      </c>
-      <c r="Z25" s="25">
-        <f>FLOOR((Cities!K25+Cities!L25+Cities!M25+Cities!J25*Cities!N25)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA25" s="25">
-        <f>CEILING((Cities!K25+Cities!L25+Cities!M25+Cities!J25*Cities!N25)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB25" s="25">
-        <f>(Z25+AA25)/2</f>
-        <v/>
-      </c>
-      <c r="AC25" s="23">
-        <f>IF(Y25&gt;0,CEILING(AB25/Y25,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD25" s="27">
-        <f>IF(R25&gt;0,Y25/R25,0)</f>
-        <v/>
-      </c>
-      <c r="AE25" s="28">
-        <f>IF(V25&lt;S25*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB25" s="27">
+        <f>Cities!H25-AA25</f>
+        <v/>
+      </c>
+      <c r="AC25" s="26">
+        <f>IF((X25*AB25-V25-U25)&gt;0, (X25*AB25-V25-U25)*(1-K25), X25*AB25-V25-U25)</f>
+        <v/>
+      </c>
+      <c r="AD25" s="26">
+        <f>IF((Y25*AB25-V25-U25)&gt;0, (Y25*AB25-V25-U25)*(1-K25), Y25*AB25-V25-U25)</f>
+        <v/>
+      </c>
+      <c r="AE25" s="26">
+        <f>AC25+U25</f>
+        <v/>
+      </c>
+      <c r="AF25" s="26">
+        <f>AD25+U25</f>
+        <v/>
+      </c>
+      <c r="AG25" s="26">
+        <f>FLOOR((Cities!K25+Cities!L25+Cities!M25+Cities!T25+Cities!J25*Cities!N25)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH25" s="26">
+        <f>CEILING((Cities!K25+Cities!L25+Cities!M25+Cities!T25+Cities!J25*Cities!N25)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI25" s="26">
+        <f>(AG25+AH25)/2</f>
+        <v/>
+      </c>
+      <c r="AJ25" s="24">
+        <f>IF(AE25*12&gt;=AI25, IF(AE25&gt;0,CEILING(AI25/AE25,1),999), IF(AF25&gt;0,12+CEILING((AI25-AE25*12)/AF25,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK25" s="28">
+        <f>IF(V25&gt;0,AD25/V25,0)</f>
+        <v/>
+      </c>
+      <c r="AL25" s="29">
+        <f>IF(Z25&lt;W25*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -6420,120 +7163,148 @@
         <f>Cities!D26</f>
         <v/>
       </c>
-      <c r="C26" s="23">
+      <c r="C26" s="24">
         <f>IF(Cities!E26&lt;=750,3,IF(Cities!E26&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="24">
+        <f>C26-1</f>
+        <v/>
+      </c>
+      <c r="E26" s="24">
+        <f>C26+D26</f>
+        <v/>
+      </c>
+      <c r="F26" s="24">
         <f>IF(C26&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E26" s="23">
+      <c r="G26" s="24">
         <f>IF(C26&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F26" s="23">
-        <f>C26-E26</f>
-        <v/>
-      </c>
-      <c r="G26" s="23">
+      <c r="H26" s="24">
+        <f>C26-G26</f>
+        <v/>
+      </c>
+      <c r="I26" s="24">
         <f>CEILING(C26/2,1)</f>
         <v/>
       </c>
-      <c r="H26" s="23">
-        <f>E26+F26+G26+1</f>
-        <v/>
-      </c>
-      <c r="I26" s="24">
+      <c r="J26" s="24">
+        <f>G26+H26+I26+1</f>
+        <v/>
+      </c>
+      <c r="K26" s="25">
         <f>VLOOKUP(Cities!D26,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J26" s="25">
+      <c r="L26" s="26">
         <f>VLOOKUP(Cities!D26,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K26" s="25">
+      <c r="M26" s="26">
         <f>VLOOKUP(Cities!D26,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L26" s="25">
+      <c r="N26" s="26">
         <f>VLOOKUP(Cities!D26,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M26" s="25">
+      <c r="O26" s="26">
         <f>VLOOKUP(Cities!D26,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N26" s="25">
-        <f>E26*J26+F26*K26+G26*L26+M26</f>
-        <v/>
-      </c>
-      <c r="O26" s="25">
+      <c r="P26" s="26">
+        <f>G26*L26+H26*M26+I26*N26+O26</f>
+        <v/>
+      </c>
+      <c r="Q26" s="26">
         <f>Cities!J26</f>
         <v/>
       </c>
-      <c r="P26" s="25">
+      <c r="R26" s="26">
         <f>200+C26*80</f>
         <v/>
       </c>
-      <c r="Q26" s="25">
+      <c r="S26" s="26">
         <f>350+C26*50+300+C26*30</f>
         <v/>
       </c>
-      <c r="R26" s="25">
-        <f>O26+N26+P26+Q26</f>
-        <v/>
-      </c>
-      <c r="S26" s="23">
+      <c r="T26" s="26">
+        <f>Cities!U26</f>
+        <v/>
+      </c>
+      <c r="U26" s="26">
+        <f>Cities!L26/60</f>
+        <v/>
+      </c>
+      <c r="V26" s="26">
+        <f>Q26+P26+R26+S26+T26</f>
+        <v/>
+      </c>
+      <c r="W26" s="24">
         <f>C26*Cities!F26*Cities!G26</f>
         <v/>
       </c>
-      <c r="T26" s="23">
-        <f>INT(S26*Cities!O26)</f>
-        <v/>
-      </c>
-      <c r="U26" s="23">
-        <f>INT(S26*Cities!P26)</f>
-        <v/>
-      </c>
-      <c r="V26" s="23">
-        <f>CEILING(R26/(Cities!H26*(1-Cities!I26)),1)</f>
-        <v/>
-      </c>
-      <c r="W26" s="26">
+      <c r="X26" s="24">
+        <f>INT(W26*Cities!O26)</f>
+        <v/>
+      </c>
+      <c r="Y26" s="24">
+        <f>INT(W26*Cities!P26)</f>
+        <v/>
+      </c>
+      <c r="Z26" s="24">
+        <f>CEILING((V26+U26)/AB26,1)</f>
+        <v/>
+      </c>
+      <c r="AA26" s="27">
         <f>Cities!H26*Cities!I26</f>
         <v/>
       </c>
-      <c r="X26" s="26">
-        <f>Cities!H26-W26</f>
-        <v/>
-      </c>
-      <c r="Y26" s="25">
-        <f>(U26*Cities!H26*(1-Cities!I26)-R26)*(1-I26)</f>
-        <v/>
-      </c>
-      <c r="Z26" s="25">
-        <f>FLOOR((Cities!K26+Cities!L26+Cities!M26+Cities!J26*Cities!N26)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA26" s="25">
-        <f>CEILING((Cities!K26+Cities!L26+Cities!M26+Cities!J26*Cities!N26)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB26" s="25">
-        <f>(Z26+AA26)/2</f>
-        <v/>
-      </c>
-      <c r="AC26" s="23">
-        <f>IF(Y26&gt;0,CEILING(AB26/Y26,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD26" s="27">
-        <f>IF(R26&gt;0,Y26/R26,0)</f>
-        <v/>
-      </c>
-      <c r="AE26" s="28">
-        <f>IF(V26&lt;S26*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB26" s="27">
+        <f>Cities!H26-AA26</f>
+        <v/>
+      </c>
+      <c r="AC26" s="26">
+        <f>IF((X26*AB26-V26-U26)&gt;0, (X26*AB26-V26-U26)*(1-K26), X26*AB26-V26-U26)</f>
+        <v/>
+      </c>
+      <c r="AD26" s="26">
+        <f>IF((Y26*AB26-V26-U26)&gt;0, (Y26*AB26-V26-U26)*(1-K26), Y26*AB26-V26-U26)</f>
+        <v/>
+      </c>
+      <c r="AE26" s="26">
+        <f>AC26+U26</f>
+        <v/>
+      </c>
+      <c r="AF26" s="26">
+        <f>AD26+U26</f>
+        <v/>
+      </c>
+      <c r="AG26" s="26">
+        <f>FLOOR((Cities!K26+Cities!L26+Cities!M26+Cities!T26+Cities!J26*Cities!N26)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH26" s="26">
+        <f>CEILING((Cities!K26+Cities!L26+Cities!M26+Cities!T26+Cities!J26*Cities!N26)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI26" s="26">
+        <f>(AG26+AH26)/2</f>
+        <v/>
+      </c>
+      <c r="AJ26" s="24">
+        <f>IF(AE26*12&gt;=AI26, IF(AE26&gt;0,CEILING(AI26/AE26,1),999), IF(AF26&gt;0,12+CEILING((AI26-AE26*12)/AF26,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK26" s="28">
+        <f>IF(V26&gt;0,AD26/V26,0)</f>
+        <v/>
+      </c>
+      <c r="AL26" s="29">
+        <f>IF(Z26&lt;W26*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -6546,120 +7317,148 @@
         <f>Cities!D27</f>
         <v/>
       </c>
-      <c r="C27" s="23">
+      <c r="C27" s="24">
         <f>IF(Cities!E27&lt;=750,3,IF(Cities!E27&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="24">
+        <f>C27-1</f>
+        <v/>
+      </c>
+      <c r="E27" s="24">
+        <f>C27+D27</f>
+        <v/>
+      </c>
+      <c r="F27" s="24">
         <f>IF(C27&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E27" s="23">
+      <c r="G27" s="24">
         <f>IF(C27&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F27" s="23">
-        <f>C27-E27</f>
-        <v/>
-      </c>
-      <c r="G27" s="23">
+      <c r="H27" s="24">
+        <f>C27-G27</f>
+        <v/>
+      </c>
+      <c r="I27" s="24">
         <f>CEILING(C27/2,1)</f>
         <v/>
       </c>
-      <c r="H27" s="23">
-        <f>E27+F27+G27+1</f>
-        <v/>
-      </c>
-      <c r="I27" s="24">
+      <c r="J27" s="24">
+        <f>G27+H27+I27+1</f>
+        <v/>
+      </c>
+      <c r="K27" s="25">
         <f>VLOOKUP(Cities!D27,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J27" s="25">
+      <c r="L27" s="26">
         <f>VLOOKUP(Cities!D27,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K27" s="25">
+      <c r="M27" s="26">
         <f>VLOOKUP(Cities!D27,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L27" s="25">
+      <c r="N27" s="26">
         <f>VLOOKUP(Cities!D27,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M27" s="25">
+      <c r="O27" s="26">
         <f>VLOOKUP(Cities!D27,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N27" s="25">
-        <f>E27*J27+F27*K27+G27*L27+M27</f>
-        <v/>
-      </c>
-      <c r="O27" s="25">
+      <c r="P27" s="26">
+        <f>G27*L27+H27*M27+I27*N27+O27</f>
+        <v/>
+      </c>
+      <c r="Q27" s="26">
         <f>Cities!J27</f>
         <v/>
       </c>
-      <c r="P27" s="25">
+      <c r="R27" s="26">
         <f>200+C27*80</f>
         <v/>
       </c>
-      <c r="Q27" s="25">
+      <c r="S27" s="26">
         <f>350+C27*50+300+C27*30</f>
         <v/>
       </c>
-      <c r="R27" s="25">
-        <f>O27+N27+P27+Q27</f>
-        <v/>
-      </c>
-      <c r="S27" s="23">
+      <c r="T27" s="26">
+        <f>Cities!U27</f>
+        <v/>
+      </c>
+      <c r="U27" s="26">
+        <f>Cities!L27/60</f>
+        <v/>
+      </c>
+      <c r="V27" s="26">
+        <f>Q27+P27+R27+S27+T27</f>
+        <v/>
+      </c>
+      <c r="W27" s="24">
         <f>C27*Cities!F27*Cities!G27</f>
         <v/>
       </c>
-      <c r="T27" s="23">
-        <f>INT(S27*Cities!O27)</f>
-        <v/>
-      </c>
-      <c r="U27" s="23">
-        <f>INT(S27*Cities!P27)</f>
-        <v/>
-      </c>
-      <c r="V27" s="23">
-        <f>CEILING(R27/(Cities!H27*(1-Cities!I27)),1)</f>
-        <v/>
-      </c>
-      <c r="W27" s="26">
+      <c r="X27" s="24">
+        <f>INT(W27*Cities!O27)</f>
+        <v/>
+      </c>
+      <c r="Y27" s="24">
+        <f>INT(W27*Cities!P27)</f>
+        <v/>
+      </c>
+      <c r="Z27" s="24">
+        <f>CEILING((V27+U27)/AB27,1)</f>
+        <v/>
+      </c>
+      <c r="AA27" s="27">
         <f>Cities!H27*Cities!I27</f>
         <v/>
       </c>
-      <c r="X27" s="26">
-        <f>Cities!H27-W27</f>
-        <v/>
-      </c>
-      <c r="Y27" s="25">
-        <f>(U27*Cities!H27*(1-Cities!I27)-R27)*(1-I27)</f>
-        <v/>
-      </c>
-      <c r="Z27" s="25">
-        <f>FLOOR((Cities!K27+Cities!L27+Cities!M27+Cities!J27*Cities!N27)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA27" s="25">
-        <f>CEILING((Cities!K27+Cities!L27+Cities!M27+Cities!J27*Cities!N27)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB27" s="25">
-        <f>(Z27+AA27)/2</f>
-        <v/>
-      </c>
-      <c r="AC27" s="23">
-        <f>IF(Y27&gt;0,CEILING(AB27/Y27,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD27" s="27">
-        <f>IF(R27&gt;0,Y27/R27,0)</f>
-        <v/>
-      </c>
-      <c r="AE27" s="28">
-        <f>IF(V27&lt;S27*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB27" s="27">
+        <f>Cities!H27-AA27</f>
+        <v/>
+      </c>
+      <c r="AC27" s="26">
+        <f>IF((X27*AB27-V27-U27)&gt;0, (X27*AB27-V27-U27)*(1-K27), X27*AB27-V27-U27)</f>
+        <v/>
+      </c>
+      <c r="AD27" s="26">
+        <f>IF((Y27*AB27-V27-U27)&gt;0, (Y27*AB27-V27-U27)*(1-K27), Y27*AB27-V27-U27)</f>
+        <v/>
+      </c>
+      <c r="AE27" s="26">
+        <f>AC27+U27</f>
+        <v/>
+      </c>
+      <c r="AF27" s="26">
+        <f>AD27+U27</f>
+        <v/>
+      </c>
+      <c r="AG27" s="26">
+        <f>FLOOR((Cities!K27+Cities!L27+Cities!M27+Cities!T27+Cities!J27*Cities!N27)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH27" s="26">
+        <f>CEILING((Cities!K27+Cities!L27+Cities!M27+Cities!T27+Cities!J27*Cities!N27)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI27" s="26">
+        <f>(AG27+AH27)/2</f>
+        <v/>
+      </c>
+      <c r="AJ27" s="24">
+        <f>IF(AE27*12&gt;=AI27, IF(AE27&gt;0,CEILING(AI27/AE27,1),999), IF(AF27&gt;0,12+CEILING((AI27-AE27*12)/AF27,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK27" s="28">
+        <f>IF(V27&gt;0,AD27/V27,0)</f>
+        <v/>
+      </c>
+      <c r="AL27" s="29">
+        <f>IF(Z27&lt;W27*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -6672,120 +7471,148 @@
         <f>Cities!D28</f>
         <v/>
       </c>
-      <c r="C28" s="23">
+      <c r="C28" s="24">
         <f>IF(Cities!E28&lt;=750,3,IF(Cities!E28&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D28" s="23">
+      <c r="D28" s="24">
+        <f>C28-1</f>
+        <v/>
+      </c>
+      <c r="E28" s="24">
+        <f>C28+D28</f>
+        <v/>
+      </c>
+      <c r="F28" s="24">
         <f>IF(C28&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E28" s="23">
+      <c r="G28" s="24">
         <f>IF(C28&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F28" s="23">
-        <f>C28-E28</f>
-        <v/>
-      </c>
-      <c r="G28" s="23">
+      <c r="H28" s="24">
+        <f>C28-G28</f>
+        <v/>
+      </c>
+      <c r="I28" s="24">
         <f>CEILING(C28/2,1)</f>
         <v/>
       </c>
-      <c r="H28" s="23">
-        <f>E28+F28+G28+1</f>
-        <v/>
-      </c>
-      <c r="I28" s="24">
+      <c r="J28" s="24">
+        <f>G28+H28+I28+1</f>
+        <v/>
+      </c>
+      <c r="K28" s="25">
         <f>VLOOKUP(Cities!D28,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J28" s="25">
+      <c r="L28" s="26">
         <f>VLOOKUP(Cities!D28,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K28" s="25">
+      <c r="M28" s="26">
         <f>VLOOKUP(Cities!D28,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L28" s="25">
+      <c r="N28" s="26">
         <f>VLOOKUP(Cities!D28,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M28" s="25">
+      <c r="O28" s="26">
         <f>VLOOKUP(Cities!D28,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N28" s="25">
-        <f>E28*J28+F28*K28+G28*L28+M28</f>
-        <v/>
-      </c>
-      <c r="O28" s="25">
+      <c r="P28" s="26">
+        <f>G28*L28+H28*M28+I28*N28+O28</f>
+        <v/>
+      </c>
+      <c r="Q28" s="26">
         <f>Cities!J28</f>
         <v/>
       </c>
-      <c r="P28" s="25">
+      <c r="R28" s="26">
         <f>200+C28*80</f>
         <v/>
       </c>
-      <c r="Q28" s="25">
+      <c r="S28" s="26">
         <f>350+C28*50+300+C28*30</f>
         <v/>
       </c>
-      <c r="R28" s="25">
-        <f>O28+N28+P28+Q28</f>
-        <v/>
-      </c>
-      <c r="S28" s="23">
+      <c r="T28" s="26">
+        <f>Cities!U28</f>
+        <v/>
+      </c>
+      <c r="U28" s="26">
+        <f>Cities!L28/60</f>
+        <v/>
+      </c>
+      <c r="V28" s="26">
+        <f>Q28+P28+R28+S28+T28</f>
+        <v/>
+      </c>
+      <c r="W28" s="24">
         <f>C28*Cities!F28*Cities!G28</f>
         <v/>
       </c>
-      <c r="T28" s="23">
-        <f>INT(S28*Cities!O28)</f>
-        <v/>
-      </c>
-      <c r="U28" s="23">
-        <f>INT(S28*Cities!P28)</f>
-        <v/>
-      </c>
-      <c r="V28" s="23">
-        <f>CEILING(R28/(Cities!H28*(1-Cities!I28)),1)</f>
-        <v/>
-      </c>
-      <c r="W28" s="26">
+      <c r="X28" s="24">
+        <f>INT(W28*Cities!O28)</f>
+        <v/>
+      </c>
+      <c r="Y28" s="24">
+        <f>INT(W28*Cities!P28)</f>
+        <v/>
+      </c>
+      <c r="Z28" s="24">
+        <f>CEILING((V28+U28)/AB28,1)</f>
+        <v/>
+      </c>
+      <c r="AA28" s="27">
         <f>Cities!H28*Cities!I28</f>
         <v/>
       </c>
-      <c r="X28" s="26">
-        <f>Cities!H28-W28</f>
-        <v/>
-      </c>
-      <c r="Y28" s="25">
-        <f>(U28*Cities!H28*(1-Cities!I28)-R28)*(1-I28)</f>
-        <v/>
-      </c>
-      <c r="Z28" s="25">
-        <f>FLOOR((Cities!K28+Cities!L28+Cities!M28+Cities!J28*Cities!N28)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA28" s="25">
-        <f>CEILING((Cities!K28+Cities!L28+Cities!M28+Cities!J28*Cities!N28)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB28" s="25">
-        <f>(Z28+AA28)/2</f>
-        <v/>
-      </c>
-      <c r="AC28" s="23">
-        <f>IF(Y28&gt;0,CEILING(AB28/Y28,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD28" s="27">
-        <f>IF(R28&gt;0,Y28/R28,0)</f>
-        <v/>
-      </c>
-      <c r="AE28" s="28">
-        <f>IF(V28&lt;S28*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB28" s="27">
+        <f>Cities!H28-AA28</f>
+        <v/>
+      </c>
+      <c r="AC28" s="26">
+        <f>IF((X28*AB28-V28-U28)&gt;0, (X28*AB28-V28-U28)*(1-K28), X28*AB28-V28-U28)</f>
+        <v/>
+      </c>
+      <c r="AD28" s="26">
+        <f>IF((Y28*AB28-V28-U28)&gt;0, (Y28*AB28-V28-U28)*(1-K28), Y28*AB28-V28-U28)</f>
+        <v/>
+      </c>
+      <c r="AE28" s="26">
+        <f>AC28+U28</f>
+        <v/>
+      </c>
+      <c r="AF28" s="26">
+        <f>AD28+U28</f>
+        <v/>
+      </c>
+      <c r="AG28" s="26">
+        <f>FLOOR((Cities!K28+Cities!L28+Cities!M28+Cities!T28+Cities!J28*Cities!N28)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH28" s="26">
+        <f>CEILING((Cities!K28+Cities!L28+Cities!M28+Cities!T28+Cities!J28*Cities!N28)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI28" s="26">
+        <f>(AG28+AH28)/2</f>
+        <v/>
+      </c>
+      <c r="AJ28" s="24">
+        <f>IF(AE28*12&gt;=AI28, IF(AE28&gt;0,CEILING(AI28/AE28,1),999), IF(AF28&gt;0,12+CEILING((AI28-AE28*12)/AF28,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK28" s="28">
+        <f>IF(V28&gt;0,AD28/V28,0)</f>
+        <v/>
+      </c>
+      <c r="AL28" s="29">
+        <f>IF(Z28&lt;W28*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -6798,120 +7625,148 @@
         <f>Cities!D29</f>
         <v/>
       </c>
-      <c r="C29" s="23">
+      <c r="C29" s="24">
         <f>IF(Cities!E29&lt;=750,3,IF(Cities!E29&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="24">
+        <f>C29-1</f>
+        <v/>
+      </c>
+      <c r="E29" s="24">
+        <f>C29+D29</f>
+        <v/>
+      </c>
+      <c r="F29" s="24">
         <f>IF(C29&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E29" s="23">
+      <c r="G29" s="24">
         <f>IF(C29&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F29" s="23">
-        <f>C29-E29</f>
-        <v/>
-      </c>
-      <c r="G29" s="23">
+      <c r="H29" s="24">
+        <f>C29-G29</f>
+        <v/>
+      </c>
+      <c r="I29" s="24">
         <f>CEILING(C29/2,1)</f>
         <v/>
       </c>
-      <c r="H29" s="23">
-        <f>E29+F29+G29+1</f>
-        <v/>
-      </c>
-      <c r="I29" s="24">
+      <c r="J29" s="24">
+        <f>G29+H29+I29+1</f>
+        <v/>
+      </c>
+      <c r="K29" s="25">
         <f>VLOOKUP(Cities!D29,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J29" s="25">
+      <c r="L29" s="26">
         <f>VLOOKUP(Cities!D29,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K29" s="25">
+      <c r="M29" s="26">
         <f>VLOOKUP(Cities!D29,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L29" s="25">
+      <c r="N29" s="26">
         <f>VLOOKUP(Cities!D29,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M29" s="25">
+      <c r="O29" s="26">
         <f>VLOOKUP(Cities!D29,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N29" s="25">
-        <f>E29*J29+F29*K29+G29*L29+M29</f>
-        <v/>
-      </c>
-      <c r="O29" s="25">
+      <c r="P29" s="26">
+        <f>G29*L29+H29*M29+I29*N29+O29</f>
+        <v/>
+      </c>
+      <c r="Q29" s="26">
         <f>Cities!J29</f>
         <v/>
       </c>
-      <c r="P29" s="25">
+      <c r="R29" s="26">
         <f>200+C29*80</f>
         <v/>
       </c>
-      <c r="Q29" s="25">
+      <c r="S29" s="26">
         <f>350+C29*50+300+C29*30</f>
         <v/>
       </c>
-      <c r="R29" s="25">
-        <f>O29+N29+P29+Q29</f>
-        <v/>
-      </c>
-      <c r="S29" s="23">
+      <c r="T29" s="26">
+        <f>Cities!U29</f>
+        <v/>
+      </c>
+      <c r="U29" s="26">
+        <f>Cities!L29/60</f>
+        <v/>
+      </c>
+      <c r="V29" s="26">
+        <f>Q29+P29+R29+S29+T29</f>
+        <v/>
+      </c>
+      <c r="W29" s="24">
         <f>C29*Cities!F29*Cities!G29</f>
         <v/>
       </c>
-      <c r="T29" s="23">
-        <f>INT(S29*Cities!O29)</f>
-        <v/>
-      </c>
-      <c r="U29" s="23">
-        <f>INT(S29*Cities!P29)</f>
-        <v/>
-      </c>
-      <c r="V29" s="23">
-        <f>CEILING(R29/(Cities!H29*(1-Cities!I29)),1)</f>
-        <v/>
-      </c>
-      <c r="W29" s="26">
+      <c r="X29" s="24">
+        <f>INT(W29*Cities!O29)</f>
+        <v/>
+      </c>
+      <c r="Y29" s="24">
+        <f>INT(W29*Cities!P29)</f>
+        <v/>
+      </c>
+      <c r="Z29" s="24">
+        <f>CEILING((V29+U29)/AB29,1)</f>
+        <v/>
+      </c>
+      <c r="AA29" s="27">
         <f>Cities!H29*Cities!I29</f>
         <v/>
       </c>
-      <c r="X29" s="26">
-        <f>Cities!H29-W29</f>
-        <v/>
-      </c>
-      <c r="Y29" s="25">
-        <f>(U29*Cities!H29*(1-Cities!I29)-R29)*(1-I29)</f>
-        <v/>
-      </c>
-      <c r="Z29" s="25">
-        <f>FLOOR((Cities!K29+Cities!L29+Cities!M29+Cities!J29*Cities!N29)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA29" s="25">
-        <f>CEILING((Cities!K29+Cities!L29+Cities!M29+Cities!J29*Cities!N29)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB29" s="25">
-        <f>(Z29+AA29)/2</f>
-        <v/>
-      </c>
-      <c r="AC29" s="23">
-        <f>IF(Y29&gt;0,CEILING(AB29/Y29,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD29" s="27">
-        <f>IF(R29&gt;0,Y29/R29,0)</f>
-        <v/>
-      </c>
-      <c r="AE29" s="28">
-        <f>IF(V29&lt;S29*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB29" s="27">
+        <f>Cities!H29-AA29</f>
+        <v/>
+      </c>
+      <c r="AC29" s="26">
+        <f>IF((X29*AB29-V29-U29)&gt;0, (X29*AB29-V29-U29)*(1-K29), X29*AB29-V29-U29)</f>
+        <v/>
+      </c>
+      <c r="AD29" s="26">
+        <f>IF((Y29*AB29-V29-U29)&gt;0, (Y29*AB29-V29-U29)*(1-K29), Y29*AB29-V29-U29)</f>
+        <v/>
+      </c>
+      <c r="AE29" s="26">
+        <f>AC29+U29</f>
+        <v/>
+      </c>
+      <c r="AF29" s="26">
+        <f>AD29+U29</f>
+        <v/>
+      </c>
+      <c r="AG29" s="26">
+        <f>FLOOR((Cities!K29+Cities!L29+Cities!M29+Cities!T29+Cities!J29*Cities!N29)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH29" s="26">
+        <f>CEILING((Cities!K29+Cities!L29+Cities!M29+Cities!T29+Cities!J29*Cities!N29)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI29" s="26">
+        <f>(AG29+AH29)/2</f>
+        <v/>
+      </c>
+      <c r="AJ29" s="24">
+        <f>IF(AE29*12&gt;=AI29, IF(AE29&gt;0,CEILING(AI29/AE29,1),999), IF(AF29&gt;0,12+CEILING((AI29-AE29*12)/AF29,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK29" s="28">
+        <f>IF(V29&gt;0,AD29/V29,0)</f>
+        <v/>
+      </c>
+      <c r="AL29" s="29">
+        <f>IF(Z29&lt;W29*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -6924,120 +7779,148 @@
         <f>Cities!D30</f>
         <v/>
       </c>
-      <c r="C30" s="23">
+      <c r="C30" s="24">
         <f>IF(Cities!E30&lt;=750,3,IF(Cities!E30&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="24">
+        <f>C30-1</f>
+        <v/>
+      </c>
+      <c r="E30" s="24">
+        <f>C30+D30</f>
+        <v/>
+      </c>
+      <c r="F30" s="24">
         <f>IF(C30&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E30" s="23">
+      <c r="G30" s="24">
         <f>IF(C30&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F30" s="23">
-        <f>C30-E30</f>
-        <v/>
-      </c>
-      <c r="G30" s="23">
+      <c r="H30" s="24">
+        <f>C30-G30</f>
+        <v/>
+      </c>
+      <c r="I30" s="24">
         <f>CEILING(C30/2,1)</f>
         <v/>
       </c>
-      <c r="H30" s="23">
-        <f>E30+F30+G30+1</f>
-        <v/>
-      </c>
-      <c r="I30" s="24">
+      <c r="J30" s="24">
+        <f>G30+H30+I30+1</f>
+        <v/>
+      </c>
+      <c r="K30" s="25">
         <f>VLOOKUP(Cities!D30,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J30" s="25">
+      <c r="L30" s="26">
         <f>VLOOKUP(Cities!D30,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K30" s="25">
+      <c r="M30" s="26">
         <f>VLOOKUP(Cities!D30,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L30" s="25">
+      <c r="N30" s="26">
         <f>VLOOKUP(Cities!D30,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M30" s="25">
+      <c r="O30" s="26">
         <f>VLOOKUP(Cities!D30,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N30" s="25">
-        <f>E30*J30+F30*K30+G30*L30+M30</f>
-        <v/>
-      </c>
-      <c r="O30" s="25">
+      <c r="P30" s="26">
+        <f>G30*L30+H30*M30+I30*N30+O30</f>
+        <v/>
+      </c>
+      <c r="Q30" s="26">
         <f>Cities!J30</f>
         <v/>
       </c>
-      <c r="P30" s="25">
+      <c r="R30" s="26">
         <f>200+C30*80</f>
         <v/>
       </c>
-      <c r="Q30" s="25">
+      <c r="S30" s="26">
         <f>350+C30*50+300+C30*30</f>
         <v/>
       </c>
-      <c r="R30" s="25">
-        <f>O30+N30+P30+Q30</f>
-        <v/>
-      </c>
-      <c r="S30" s="23">
+      <c r="T30" s="26">
+        <f>Cities!U30</f>
+        <v/>
+      </c>
+      <c r="U30" s="26">
+        <f>Cities!L30/60</f>
+        <v/>
+      </c>
+      <c r="V30" s="26">
+        <f>Q30+P30+R30+S30+T30</f>
+        <v/>
+      </c>
+      <c r="W30" s="24">
         <f>C30*Cities!F30*Cities!G30</f>
         <v/>
       </c>
-      <c r="T30" s="23">
-        <f>INT(S30*Cities!O30)</f>
-        <v/>
-      </c>
-      <c r="U30" s="23">
-        <f>INT(S30*Cities!P30)</f>
-        <v/>
-      </c>
-      <c r="V30" s="23">
-        <f>CEILING(R30/(Cities!H30*(1-Cities!I30)),1)</f>
-        <v/>
-      </c>
-      <c r="W30" s="26">
+      <c r="X30" s="24">
+        <f>INT(W30*Cities!O30)</f>
+        <v/>
+      </c>
+      <c r="Y30" s="24">
+        <f>INT(W30*Cities!P30)</f>
+        <v/>
+      </c>
+      <c r="Z30" s="24">
+        <f>CEILING((V30+U30)/AB30,1)</f>
+        <v/>
+      </c>
+      <c r="AA30" s="27">
         <f>Cities!H30*Cities!I30</f>
         <v/>
       </c>
-      <c r="X30" s="26">
-        <f>Cities!H30-W30</f>
-        <v/>
-      </c>
-      <c r="Y30" s="25">
-        <f>(U30*Cities!H30*(1-Cities!I30)-R30)*(1-I30)</f>
-        <v/>
-      </c>
-      <c r="Z30" s="25">
-        <f>FLOOR((Cities!K30+Cities!L30+Cities!M30+Cities!J30*Cities!N30)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA30" s="25">
-        <f>CEILING((Cities!K30+Cities!L30+Cities!M30+Cities!J30*Cities!N30)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB30" s="25">
-        <f>(Z30+AA30)/2</f>
-        <v/>
-      </c>
-      <c r="AC30" s="23">
-        <f>IF(Y30&gt;0,CEILING(AB30/Y30,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD30" s="27">
-        <f>IF(R30&gt;0,Y30/R30,0)</f>
-        <v/>
-      </c>
-      <c r="AE30" s="28">
-        <f>IF(V30&lt;S30*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB30" s="27">
+        <f>Cities!H30-AA30</f>
+        <v/>
+      </c>
+      <c r="AC30" s="26">
+        <f>IF((X30*AB30-V30-U30)&gt;0, (X30*AB30-V30-U30)*(1-K30), X30*AB30-V30-U30)</f>
+        <v/>
+      </c>
+      <c r="AD30" s="26">
+        <f>IF((Y30*AB30-V30-U30)&gt;0, (Y30*AB30-V30-U30)*(1-K30), Y30*AB30-V30-U30)</f>
+        <v/>
+      </c>
+      <c r="AE30" s="26">
+        <f>AC30+U30</f>
+        <v/>
+      </c>
+      <c r="AF30" s="26">
+        <f>AD30+U30</f>
+        <v/>
+      </c>
+      <c r="AG30" s="26">
+        <f>FLOOR((Cities!K30+Cities!L30+Cities!M30+Cities!T30+Cities!J30*Cities!N30)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH30" s="26">
+        <f>CEILING((Cities!K30+Cities!L30+Cities!M30+Cities!T30+Cities!J30*Cities!N30)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI30" s="26">
+        <f>(AG30+AH30)/2</f>
+        <v/>
+      </c>
+      <c r="AJ30" s="24">
+        <f>IF(AE30*12&gt;=AI30, IF(AE30&gt;0,CEILING(AI30/AE30,1),999), IF(AF30&gt;0,12+CEILING((AI30-AE30*12)/AF30,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK30" s="28">
+        <f>IF(V30&gt;0,AD30/V30,0)</f>
+        <v/>
+      </c>
+      <c r="AL30" s="29">
+        <f>IF(Z30&lt;W30*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
@@ -7050,138 +7933,169 @@
         <f>Cities!D31</f>
         <v/>
       </c>
-      <c r="C31" s="23">
+      <c r="C31" s="24">
         <f>IF(Cities!E31&lt;=750,3,IF(Cities!E31&lt;=850,4,5))</f>
         <v/>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="24">
+        <f>C31-1</f>
+        <v/>
+      </c>
+      <c r="E31" s="24">
+        <f>C31+D31</f>
+        <v/>
+      </c>
+      <c r="F31" s="24">
         <f>IF(C31&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="E31" s="23">
+      <c r="G31" s="24">
         <f>IF(C31&lt;=4,2,3)</f>
         <v/>
       </c>
-      <c r="F31" s="23">
-        <f>C31-E31</f>
-        <v/>
-      </c>
-      <c r="G31" s="23">
+      <c r="H31" s="24">
+        <f>C31-G31</f>
+        <v/>
+      </c>
+      <c r="I31" s="24">
         <f>CEILING(C31/2,1)</f>
         <v/>
       </c>
-      <c r="H31" s="23">
-        <f>E31+F31+G31+1</f>
-        <v/>
-      </c>
-      <c r="I31" s="24">
+      <c r="J31" s="24">
+        <f>G31+H31+I31+1</f>
+        <v/>
+      </c>
+      <c r="K31" s="25">
         <f>VLOOKUP(Cities!D31,Country!$A$4:$H$14,3,FALSE)</f>
         <v/>
       </c>
-      <c r="J31" s="25">
+      <c r="L31" s="26">
         <f>VLOOKUP(Cities!D31,Country!$A$4:$H$14,5,FALSE)</f>
         <v/>
       </c>
-      <c r="K31" s="25">
+      <c r="M31" s="26">
         <f>VLOOKUP(Cities!D31,Country!$A$4:$H$14,6,FALSE)</f>
         <v/>
       </c>
-      <c r="L31" s="25">
+      <c r="N31" s="26">
         <f>VLOOKUP(Cities!D31,Country!$A$4:$H$14,7,FALSE)</f>
         <v/>
       </c>
-      <c r="M31" s="25">
+      <c r="O31" s="26">
         <f>VLOOKUP(Cities!D31,Country!$A$4:$H$14,8,FALSE)</f>
         <v/>
       </c>
-      <c r="N31" s="25">
-        <f>E31*J31+F31*K31+G31*L31+M31</f>
-        <v/>
-      </c>
-      <c r="O31" s="25">
+      <c r="P31" s="26">
+        <f>G31*L31+H31*M31+I31*N31+O31</f>
+        <v/>
+      </c>
+      <c r="Q31" s="26">
         <f>Cities!J31</f>
         <v/>
       </c>
-      <c r="P31" s="25">
+      <c r="R31" s="26">
         <f>200+C31*80</f>
         <v/>
       </c>
-      <c r="Q31" s="25">
+      <c r="S31" s="26">
         <f>350+C31*50+300+C31*30</f>
         <v/>
       </c>
-      <c r="R31" s="25">
-        <f>O31+N31+P31+Q31</f>
-        <v/>
-      </c>
-      <c r="S31" s="23">
+      <c r="T31" s="26">
+        <f>Cities!U31</f>
+        <v/>
+      </c>
+      <c r="U31" s="26">
+        <f>Cities!L31/60</f>
+        <v/>
+      </c>
+      <c r="V31" s="26">
+        <f>Q31+P31+R31+S31+T31</f>
+        <v/>
+      </c>
+      <c r="W31" s="24">
         <f>C31*Cities!F31*Cities!G31</f>
         <v/>
       </c>
-      <c r="T31" s="23">
-        <f>INT(S31*Cities!O31)</f>
-        <v/>
-      </c>
-      <c r="U31" s="23">
-        <f>INT(S31*Cities!P31)</f>
-        <v/>
-      </c>
-      <c r="V31" s="23">
-        <f>CEILING(R31/(Cities!H31*(1-Cities!I31)),1)</f>
-        <v/>
-      </c>
-      <c r="W31" s="26">
+      <c r="X31" s="24">
+        <f>INT(W31*Cities!O31)</f>
+        <v/>
+      </c>
+      <c r="Y31" s="24">
+        <f>INT(W31*Cities!P31)</f>
+        <v/>
+      </c>
+      <c r="Z31" s="24">
+        <f>CEILING((V31+U31)/AB31,1)</f>
+        <v/>
+      </c>
+      <c r="AA31" s="27">
         <f>Cities!H31*Cities!I31</f>
         <v/>
       </c>
-      <c r="X31" s="26">
-        <f>Cities!H31-W31</f>
-        <v/>
-      </c>
-      <c r="Y31" s="25">
-        <f>(U31*Cities!H31*(1-Cities!I31)-R31)*(1-I31)</f>
-        <v/>
-      </c>
-      <c r="Z31" s="25">
-        <f>FLOOR((Cities!K31+Cities!L31+Cities!M31+Cities!J31*Cities!N31)*0.92,5000)</f>
-        <v/>
-      </c>
-      <c r="AA31" s="25">
-        <f>CEILING((Cities!K31+Cities!L31+Cities!M31+Cities!J31*Cities!N31)*1.08,5000)</f>
-        <v/>
-      </c>
-      <c r="AB31" s="25">
-        <f>(Z31+AA31)/2</f>
-        <v/>
-      </c>
-      <c r="AC31" s="23">
-        <f>IF(Y31&gt;0,CEILING(AB31/Y31,1),999)</f>
-        <v/>
-      </c>
-      <c r="AD31" s="27">
-        <f>IF(R31&gt;0,Y31/R31,0)</f>
-        <v/>
-      </c>
-      <c r="AE31" s="28">
-        <f>IF(V31&lt;S31*0.8,"✓ YES","⚠ TIGHT")</f>
+      <c r="AB31" s="27">
+        <f>Cities!H31-AA31</f>
+        <v/>
+      </c>
+      <c r="AC31" s="26">
+        <f>IF((X31*AB31-V31-U31)&gt;0, (X31*AB31-V31-U31)*(1-K31), X31*AB31-V31-U31)</f>
+        <v/>
+      </c>
+      <c r="AD31" s="26">
+        <f>IF((Y31*AB31-V31-U31)&gt;0, (Y31*AB31-V31-U31)*(1-K31), Y31*AB31-V31-U31)</f>
+        <v/>
+      </c>
+      <c r="AE31" s="26">
+        <f>AC31+U31</f>
+        <v/>
+      </c>
+      <c r="AF31" s="26">
+        <f>AD31+U31</f>
+        <v/>
+      </c>
+      <c r="AG31" s="26">
+        <f>FLOOR((Cities!K31+Cities!L31+Cities!M31+Cities!T31+Cities!J31*Cities!N31)*0.92,5000)</f>
+        <v/>
+      </c>
+      <c r="AH31" s="26">
+        <f>CEILING((Cities!K31+Cities!L31+Cities!M31+Cities!T31+Cities!J31*Cities!N31)*1.08,5000)</f>
+        <v/>
+      </c>
+      <c r="AI31" s="26">
+        <f>(AG31+AH31)/2</f>
+        <v/>
+      </c>
+      <c r="AJ31" s="24">
+        <f>IF(AE31*12&gt;=AI31, IF(AE31&gt;0,CEILING(AI31/AE31,1),999), IF(AF31&gt;0,12+CEILING((AI31-AE31*12)/AF31,1),999))</f>
+        <v/>
+      </c>
+      <c r="AK31" s="28">
+        <f>IF(V31&gt;0,AD31/V31,0)</f>
+        <v/>
+      </c>
+      <c r="AL31" s="29">
+        <f>IF(Z31&lt;W31*0.8,"✓ YES","⚠ TIGHT")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="Z3:AD3"/>
-    <mergeCell ref="A2:AE2"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="N3"/>
-    <mergeCell ref="AE3"/>
-    <mergeCell ref="O3:R3"/>
-    <mergeCell ref="A1:AE1"/>
-    <mergeCell ref="S3:U3"/>
-    <mergeCell ref="C3:H3"/>
+  <mergeCells count="14">
+    <mergeCell ref="K3:O3"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="P3"/>
+    <mergeCell ref="W3:Y3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AJ3"/>
+    <mergeCell ref="AK3"/>
+    <mergeCell ref="AL3"/>
+    <mergeCell ref="A1:AL1"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="Z3:AB3"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="Q3:V3"/>
+    <mergeCell ref="A2:AL2"/>
   </mergeCells>
-  <conditionalFormatting sqref="AE5:AE31">
+  <conditionalFormatting sqref="AL5:AL31">
     <cfRule type="cellIs" priority="1" operator="containsText" dxfId="0">
       <formula>"✓"</formula>
     </cfRule>

--- a/salon_data.xlsx
+++ b/salon_data.xlsx
@@ -2064,7 +2064,7 @@
         <v>0.1</v>
       </c>
       <c r="J11" s="20" t="n">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="K11" s="20" t="n">
         <v>33000</v>
@@ -2794,7 +2794,7 @@
         <v>0.1</v>
       </c>
       <c r="J21" s="20" t="n">
-        <v>2200</v>
+        <v>3400</v>
       </c>
       <c r="K21" s="20" t="n">
         <v>55800</v>
@@ -2867,7 +2867,7 @@
         <v>0.1</v>
       </c>
       <c r="J22" s="20" t="n">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="K22" s="20" t="n">
         <v>46500</v>
@@ -2940,7 +2940,7 @@
         <v>0.1</v>
       </c>
       <c r="J23" s="20" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="K23" s="20" t="n">
         <v>37200</v>
@@ -3013,7 +3013,7 @@
         <v>0.1</v>
       </c>
       <c r="J24" s="20" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="K24" s="20" t="n">
         <v>34100</v>

--- a/salon_data.xlsx
+++ b/salon_data.xlsx
@@ -123,7 +123,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -145,11 +145,55 @@
         <color rgb="00BBBBBB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -236,6 +280,8 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1390,7 +1436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:U49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1436,36 +1482,50 @@
           <t>IDENTITY</t>
         </is>
       </c>
+      <c r="B3" s="30" t="n"/>
+      <c r="C3" s="30" t="n"/>
+      <c r="D3" s="31" t="n"/>
       <c r="E3" s="14" t="inlineStr">
         <is>
           <t>SPACE &amp; TIME</t>
         </is>
       </c>
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="31" t="n"/>
       <c r="H3" s="14" t="inlineStr">
         <is>
           <t>PRICING</t>
         </is>
       </c>
+      <c r="I3" s="31" t="n"/>
       <c r="J3" s="14" t="inlineStr">
         <is>
           <t>COSTS &amp; CAPEX</t>
         </is>
       </c>
+      <c r="K3" s="30" t="n"/>
+      <c r="L3" s="30" t="n"/>
+      <c r="M3" s="30" t="n"/>
+      <c r="N3" s="31" t="n"/>
       <c r="O3" s="14" t="inlineStr">
         <is>
           <t>UTILISATION</t>
         </is>
       </c>
+      <c r="P3" s="31" t="n"/>
       <c r="Q3" s="14" t="inlineStr">
         <is>
           <t>GEOGRAPHY</t>
         </is>
       </c>
+      <c r="R3" s="30" t="n"/>
+      <c r="S3" s="31" t="n"/>
       <c r="T3" s="14" t="inlineStr">
         <is>
           <t>BUSINESS FEES &amp; ADMIN</t>
         </is>
       </c>
+      <c r="U3" s="31" t="n"/>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
@@ -1656,7 +1716,7 @@
         <v>65</v>
       </c>
       <c r="T5" s="20" t="n">
-        <v>2500</v>
+        <v>6500</v>
       </c>
       <c r="U5" s="20" t="n">
         <v>200</v>
@@ -1729,7 +1789,7 @@
         <v>55</v>
       </c>
       <c r="T6" s="20" t="n">
-        <v>2500</v>
+        <v>6500</v>
       </c>
       <c r="U6" s="20" t="n">
         <v>200</v>
@@ -1802,7 +1862,7 @@
         <v>70</v>
       </c>
       <c r="T7" s="20" t="n">
-        <v>1500</v>
+        <v>6500</v>
       </c>
       <c r="U7" s="20" t="n">
         <v>200</v>
@@ -1875,7 +1935,7 @@
         <v>72</v>
       </c>
       <c r="T8" s="20" t="n">
-        <v>1500</v>
+        <v>6500</v>
       </c>
       <c r="U8" s="20" t="n">
         <v>200</v>
@@ -1948,7 +2008,7 @@
         <v>75</v>
       </c>
       <c r="T9" s="20" t="n">
-        <v>1500</v>
+        <v>6500</v>
       </c>
       <c r="U9" s="20" t="n">
         <v>200</v>
@@ -2021,7 +2081,7 @@
         <v>73</v>
       </c>
       <c r="T10" s="20" t="n">
-        <v>1500</v>
+        <v>6500</v>
       </c>
       <c r="U10" s="20" t="n">
         <v>200</v>
@@ -2094,7 +2154,7 @@
         <v>40</v>
       </c>
       <c r="T11" s="20" t="n">
-        <v>1500</v>
+        <v>7500</v>
       </c>
       <c r="U11" s="20" t="n">
         <v>200</v>
@@ -2167,7 +2227,7 @@
         <v>55</v>
       </c>
       <c r="T12" s="20" t="n">
-        <v>1500</v>
+        <v>7500</v>
       </c>
       <c r="U12" s="20" t="n">
         <v>200</v>
@@ -2240,7 +2300,7 @@
         <v>50</v>
       </c>
       <c r="T13" s="20" t="n">
-        <v>1000</v>
+        <v>7500</v>
       </c>
       <c r="U13" s="20" t="n">
         <v>200</v>
@@ -2313,7 +2373,7 @@
         <v>68</v>
       </c>
       <c r="T14" s="20" t="n">
-        <v>1000</v>
+        <v>7500</v>
       </c>
       <c r="U14" s="20" t="n">
         <v>200</v>
@@ -2386,7 +2446,7 @@
         <v>65</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>1000</v>
+        <v>7500</v>
       </c>
       <c r="U15" s="20" t="n">
         <v>200</v>
@@ -2459,7 +2519,7 @@
         <v>25</v>
       </c>
       <c r="T16" s="20" t="n">
-        <v>1500</v>
+        <v>4000</v>
       </c>
       <c r="U16" s="20" t="n">
         <v>300</v>
@@ -2532,7 +2592,7 @@
         <v>22</v>
       </c>
       <c r="T17" s="20" t="n">
-        <v>1200</v>
+        <v>3500</v>
       </c>
       <c r="U17" s="20" t="n">
         <v>300</v>
@@ -2605,7 +2665,7 @@
         <v>45</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>2000</v>
+        <v>6500</v>
       </c>
       <c r="U18" s="20" t="n">
         <v>200</v>
@@ -2678,7 +2738,7 @@
         <v>38</v>
       </c>
       <c r="T19" s="20" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="U19" s="20" t="n">
         <v>300</v>
@@ -2751,7 +2811,7 @@
         <v>30</v>
       </c>
       <c r="T20" s="20" t="n">
-        <v>6000</v>
+        <v>8500</v>
       </c>
       <c r="U20" s="20" t="n">
         <v>300</v>
@@ -2824,7 +2884,7 @@
         <v>35</v>
       </c>
       <c r="T21" s="20" t="n">
-        <v>1800</v>
+        <v>5500</v>
       </c>
       <c r="U21" s="20" t="n">
         <v>200</v>
@@ -2897,7 +2957,7 @@
         <v>42</v>
       </c>
       <c r="T22" s="20" t="n">
-        <v>1800</v>
+        <v>5500</v>
       </c>
       <c r="U22" s="20" t="n">
         <v>200</v>
@@ -2970,7 +3030,7 @@
         <v>48</v>
       </c>
       <c r="T23" s="20" t="n">
-        <v>1800</v>
+        <v>5500</v>
       </c>
       <c r="U23" s="20" t="n">
         <v>200</v>
@@ -3043,7 +3103,7 @@
         <v>55</v>
       </c>
       <c r="T24" s="20" t="n">
-        <v>1800</v>
+        <v>5500</v>
       </c>
       <c r="U24" s="20" t="n">
         <v>200</v>
@@ -3116,7 +3176,7 @@
         <v>38</v>
       </c>
       <c r="T25" s="20" t="n">
-        <v>2500</v>
+        <v>7500</v>
       </c>
       <c r="U25" s="20" t="n">
         <v>300</v>
@@ -3189,7 +3249,7 @@
         <v>52</v>
       </c>
       <c r="T26" s="20" t="n">
-        <v>2500</v>
+        <v>7500</v>
       </c>
       <c r="U26" s="20" t="n">
         <v>300</v>
@@ -3262,7 +3322,7 @@
         <v>45</v>
       </c>
       <c r="T27" s="20" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="U27" s="20" t="n">
         <v>300</v>
@@ -3335,7 +3395,7 @@
         <v>30</v>
       </c>
       <c r="T28" s="20" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="U28" s="20" t="n">
         <v>300</v>
@@ -3408,7 +3468,7 @@
         <v>32</v>
       </c>
       <c r="T29" s="20" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="U29" s="20" t="n">
         <v>300</v>
@@ -3481,7 +3541,7 @@
         <v>36</v>
       </c>
       <c r="T30" s="20" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="U30" s="20" t="n">
         <v>300</v>
@@ -3554,12 +3614,30 @@
         <v>38</v>
       </c>
       <c r="T31" s="20" t="n">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="U31" s="20" t="n">
         <v>300</v>
       </c>
     </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="O3:P3"/>
@@ -3645,21 +3723,32 @@
           <t>IDENTITY</t>
         </is>
       </c>
+      <c r="B3" s="31" t="n"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
           <t>SPACE &amp; SEATS</t>
         </is>
       </c>
+      <c r="D3" s="30" t="n"/>
+      <c r="E3" s="31" t="n"/>
       <c r="F3" s="14" t="inlineStr">
         <is>
           <t>STAFFING MODEL</t>
         </is>
       </c>
+      <c r="G3" s="30" t="n"/>
+      <c r="H3" s="30" t="n"/>
+      <c r="I3" s="30" t="n"/>
+      <c r="J3" s="31" t="n"/>
       <c r="K3" s="14" t="inlineStr">
         <is>
           <t>COUNTRY RATES</t>
         </is>
       </c>
+      <c r="L3" s="30" t="n"/>
+      <c r="M3" s="30" t="n"/>
+      <c r="N3" s="30" t="n"/>
+      <c r="O3" s="31" t="n"/>
       <c r="P3" s="14" t="inlineStr">
         <is>
           <t>STAFF COST</t>
@@ -3670,26 +3759,41 @@
           <t>MONTHLY OPEX</t>
         </is>
       </c>
+      <c r="R3" s="30" t="n"/>
+      <c r="S3" s="30" t="n"/>
+      <c r="T3" s="30" t="n"/>
+      <c r="U3" s="30" t="n"/>
+      <c r="V3" s="31" t="n"/>
       <c r="W3" s="14" t="inlineStr">
         <is>
           <t>CAPACITY</t>
         </is>
       </c>
+      <c r="X3" s="30" t="n"/>
+      <c r="Y3" s="31" t="n"/>
       <c r="Z3" s="14" t="inlineStr">
         <is>
           <t>UNIT ECONOMICS</t>
         </is>
       </c>
+      <c r="AA3" s="30" t="n"/>
+      <c r="AB3" s="31" t="n"/>
       <c r="AC3" s="14" t="inlineStr">
         <is>
           <t>PROFIT &amp; CASH FLOW</t>
         </is>
       </c>
+      <c r="AD3" s="30" t="n"/>
+      <c r="AE3" s="30" t="n"/>
+      <c r="AF3" s="31" t="n"/>
       <c r="AG3" s="14" t="inlineStr">
         <is>
           <t>CAPEX &amp; PAYBACK</t>
         </is>
       </c>
+      <c r="AH3" s="30" t="n"/>
+      <c r="AI3" s="30" t="n"/>
+      <c r="AJ3" s="31" t="n"/>
       <c r="AK3" s="14" t="inlineStr">
         <is>
           <t>RATIO</t>

--- a/salon_data.xlsx
+++ b/salon_data.xlsx
@@ -1436,7 +1436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U49"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2589,7 +2589,7 @@
         <v>114.165</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="T17" s="20" t="n">
         <v>3500</v>
@@ -3620,24 +3620,6 @@
         <v>300</v>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="O3:P3"/>

--- a/salon_data.xlsx
+++ b/salon_data.xlsx
@@ -2370,7 +2370,7 @@
         <v>116.073</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="T14" s="20" t="n">
         <v>7500</v>

--- a/salon_data.xlsx
+++ b/salon_data.xlsx
@@ -13,6 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAPEX_Details" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPEX_Details" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment_Sourcing" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock_Details" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -990,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1415,7 +1417,6 @@
         <v>3808</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
@@ -1423,10 +1424,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A16:H16"/>
@@ -1443,7 +1440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U50"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3627,25 +3624,6 @@
         <v>300</v>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="O3:P3"/>
@@ -24496,4 +24474,1500 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Equipment Type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Import Model</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Import Base Cost (USD)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Logistics &amp; Duty (USD)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Total Import Cost (USD)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Local Supplier Model</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Local Supplier Cost (USD)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Cheaper Option</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Sourcing References &amp; Quotes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Styling Chair</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Foshan Grand Hydraulic</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>180</v>
+      </c>
+      <c r="E2" t="n">
+        <v>129</v>
+      </c>
+      <c r="F2" t="n">
+        <v>309</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Hieu Salon Equipment Saigon</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>450</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Foshan factory quote &amp; local customs broker clearance estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Shampoo Backwash Unit</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Premium Relax Basin Unit</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>350</v>
+      </c>
+      <c r="E3" t="n">
+        <v>255</v>
+      </c>
+      <c r="F3" t="n">
+        <v>605</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hieu Salon Equipment Saigon</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>800</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Vietnam Customs tariff (20% import duty + 10% VAT) + sea LCL shipping</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Styling Chair</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Foshan Grand Hydraulic</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>180</v>
+      </c>
+      <c r="E4" t="n">
+        <v>107</v>
+      </c>
+      <c r="F4" t="n">
+        <v>287</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Excel Salon Furniture KL</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>500</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Malaysia customs clearing (5% duty + 10% SST) + Port Klang sea freight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Shampoo Backwash Unit</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Premium Relax Basin Unit</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>350</v>
+      </c>
+      <c r="E5" t="n">
+        <v>212</v>
+      </c>
+      <c r="F5" t="n">
+        <v>562</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Excel Salon Furniture KL</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>950</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Port Klang sea LCL shipping + SST clearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Styling Chair</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Foshan Grand Hydraulic</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>180</v>
+      </c>
+      <c r="E6" t="n">
+        <v>106</v>
+      </c>
+      <c r="F6" t="n">
+        <v>286</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Premium Salon Supplies SG</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>800</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Singapore 9% GST + Keppel Port sea freight logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Shampoo Backwash Unit</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Premium Relax Basin Unit</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>350</v>
+      </c>
+      <c r="E7" t="n">
+        <v>211</v>
+      </c>
+      <c r="F7" t="n">
+        <v>561</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Premium Salon Supplies SG</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Singapore sea LCL shipping + GST clearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Styling Chair</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Foshan Grand Hydraulic</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>180</v>
+      </c>
+      <c r="E8" t="n">
+        <v>70</v>
+      </c>
+      <c r="F8" t="n">
+        <v>250</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Takara Belmont HK Agent</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>700</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0% import duties/VAT, local truck logistics from Shenzhen port</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Shampoo Backwash Unit</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Premium Relax Basin Unit</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>350</v>
+      </c>
+      <c r="E9" t="n">
+        <v>150</v>
+      </c>
+      <c r="F9" t="n">
+        <v>500</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Takara Belmont HK Agent</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0% duties, sea LCL shipping + Kwai Chung port handling</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Styling Chair</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Foshan Grand Hydraulic</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>180</v>
+      </c>
+      <c r="E10" t="n">
+        <v>75</v>
+      </c>
+      <c r="F10" t="n">
+        <v>255</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Macau Salon Distributor</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>750</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Macau 0% import duty, local logistics from HK port transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Shampoo Backwash Unit</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Premium Relax Basin Unit</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>350</v>
+      </c>
+      <c r="E11" t="n">
+        <v>150</v>
+      </c>
+      <c r="F11" t="n">
+        <v>500</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Macau Salon Distributor</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1350</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sea LCL shipping + Macau customs handling</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Styling Chair</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Foshan Grand Hydraulic</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>180</v>
+      </c>
+      <c r="E12" t="n">
+        <v>113</v>
+      </c>
+      <c r="F12" t="n">
+        <v>293</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Taipei Salon Design Depot</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>600</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Taiwan Customs tariff (5% duty + 5% VAT) + Keelung port shipping</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Shampoo Backwash Unit</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Premium Relax Basin Unit</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>350</v>
+      </c>
+      <c r="E13" t="n">
+        <v>215</v>
+      </c>
+      <c r="F13" t="n">
+        <v>565</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Taipei Salon Design Depot</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Taiwan sea LCL shipping + import customs clearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Styling Chair</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Foshan Grand Hydraulic</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>180</v>
+      </c>
+      <c r="E14" t="n">
+        <v>128</v>
+      </c>
+      <c r="F14" t="n">
+        <v>308</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Takara Belmont Domestic</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>750</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Japan 10% consumption tax + Yokohama port shipping &amp; customs broker</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Shampoo Backwash Unit</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Premium Relax Basin Unit</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>350</v>
+      </c>
+      <c r="E15" t="n">
+        <v>235</v>
+      </c>
+      <c r="F15" t="n">
+        <v>585</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Takara Belmont Domestic</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Japan customs clearance + sea LCL logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Styling Chair</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Foshan Grand Hydraulic</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>180</v>
+      </c>
+      <c r="E16" t="n">
+        <v>142</v>
+      </c>
+      <c r="F16" t="n">
+        <v>322</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Takara Belmont Korea</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>750</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Korea Customs tariff (8% duty + 10% VAT) + Busan port LCL shipping</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Shampoo Backwash Unit</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Premium Relax Basin Unit</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>350</v>
+      </c>
+      <c r="E17" t="n">
+        <v>263</v>
+      </c>
+      <c r="F17" t="n">
+        <v>613</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Takara Belmont Korea</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Korea import clearance + sea freight logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Styling Chair</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Foshan Grand Hydraulic</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>180</v>
+      </c>
+      <c r="E18" t="n">
+        <v>188</v>
+      </c>
+      <c r="F18" t="n">
+        <v>368</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>EEM Salon Supplies Dubai</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>950</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>UAE Customs (5% duty + 5% VAT) + Jebel Ali port logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Shampoo Backwash Unit</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Premium Relax Basin Unit</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>350</v>
+      </c>
+      <c r="E19" t="n">
+        <v>335</v>
+      </c>
+      <c r="F19" t="n">
+        <v>685</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>EEM Salon Supplies Dubai</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1900</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Dubai LCL sea freight + local warehouse delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Styling Chair</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Foshan Grand Hydraulic</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>180</v>
+      </c>
+      <c r="E20" t="n">
+        <v>257</v>
+      </c>
+      <c r="F20" t="n">
+        <v>437</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Comfortel Premium Australia</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>850</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Australian Border Force tariff (5% duty + 10% GST) + Port Botany freight</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Shampoo Backwash Unit</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Premium Relax Basin Unit</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>350</v>
+      </c>
+      <c r="E21" t="n">
+        <v>402</v>
+      </c>
+      <c r="F21" t="n">
+        <v>752</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Comfortel Premium Australia</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Australian Customs broker clearance + LCL sea cargo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Styling Chair</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Foshan Grand Hydraulic</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>180</v>
+      </c>
+      <c r="E22" t="n">
+        <v>133</v>
+      </c>
+      <c r="F22" t="n">
+        <v>313</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Bangkok Salon Supply</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>550</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Thailand Customs tariff (20% duty + 7% VAT) + Laem Chabang port logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Shampoo Backwash Unit</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Premium Relax Basin Unit</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>350</v>
+      </c>
+      <c r="E23" t="n">
+        <v>254</v>
+      </c>
+      <c r="F23" t="n">
+        <v>604</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Bangkok Salon Supply</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>950</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Laem Chabang sea freight + customs clearance</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Brand / Item Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Wholesale Unit Price (USD)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Base Qty (4-Station Salon)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Total Cost (USD)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Reference / Distributor Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Color &amp; Chemical</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Wella Koleston Perfect Permanent Color Tube (60ml)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Wella Professionals Distributor B2B Catalog 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Color &amp; Chemical</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Wella Welloxon Perfect Developer (1000ml)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E3" t="n">
+        <v>480</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Wella Professionals Distributor B2B Catalog 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Color &amp; Chemical</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Wella Blondor Multi-Blonde Bleach Powder (800g)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Wella Professionals Distributor B2B Catalog 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Color &amp; Chemical</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Olaplex Salon Intro Kit (Bond Multiplier No. 1 + Bond Perfector No. 2)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>150</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>750</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Olaplex Professional Partner B2B Pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Backwash Care</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kérastase Bain Chroma Respect (Color-treated, 1000ml)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>42</v>
+      </c>
+      <c r="D6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" t="n">
+        <v>630</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>L'Oreal Division Professionnelle Trade Pricing 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Backwash Care</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kérastase Bain Fluidealiste (Frizz control, 1000ml)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>42</v>
+      </c>
+      <c r="D7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" t="n">
+        <v>630</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>L'Oreal Division Professionnelle Trade Pricing 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Backwash Care</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kérastase Bain Densifique (Thinning/volume, 1000ml)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>42</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>420</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>L'Oreal Division Professionnelle Trade Pricing 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Backwash Care</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kérastase Fondant Chroma Respect Conditioner (1000ml)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>48</v>
+      </c>
+      <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>576</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>L'Oreal Division Professionnelle Trade Pricing 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Backwash Care</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kérastase Fondant Fluidealiste Conditioner (1000ml)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>48</v>
+      </c>
+      <c r="D10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" t="n">
+        <v>576</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>L'Oreal Division Professionnelle Trade Pricing 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Retail Stock</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Oribe Gold Lust Repair &amp; Restore Shampoo (250ml)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>40</v>
+      </c>
+      <c r="E11" t="n">
+        <v>980</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Oribe Salon Partner Program B2B Price List 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Retail Stock</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Oribe Gold Lust Repair &amp; Restore Conditioner (200ml)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>26</v>
+      </c>
+      <c r="D12" t="n">
+        <v>40</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Oribe Salon Partner Program B2B Price List 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Retail Stock</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Oribe Dry Texturizing Spray (300ml)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>24</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>720</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Oribe Salon Partner Program B2B Price List 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Retail Stock</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kérastase Elixir Ultime Hair Oil (100ml)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>26</v>
+      </c>
+      <c r="D14" t="n">
+        <v>40</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>L'Oreal Division Professionnelle Trade Pricing 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Backstation Essentials</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Oribe Royal Blowout Heat Styling Spray (175ml)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>34</v>
+      </c>
+      <c r="D15" t="n">
+        <v>15</v>
+      </c>
+      <c r="E15" t="n">
+        <v>510</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Oribe Salon Partner Program B2B Price List 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Backstation Essentials</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Oribe Gold Lust Dry Shampoo (250ml)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>24</v>
+      </c>
+      <c r="D16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" t="n">
+        <v>480</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Oribe Salon Partner Program B2B Price List 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Backstation Essentials</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Miscellaneous color bowls, brushes, foils, gloves, capes, towels (Lot)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Salon Essentials Wholesale Distributor Lot Price 2025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>